--- a/nbench/list2026.xlsx
+++ b/nbench/list2026.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\archive\github\benchmark\nbench\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00E8BB2-AEBF-4029-B746-2D21ECC4CBC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97879D0-3740-4811-9015-BD9A29C21C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="540" yWindow="615" windowWidth="23790" windowHeight="15165" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28905" yWindow="180" windowWidth="26505" windowHeight="15705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="2025" sheetId="6" r:id="rId1"/>
-    <sheet name="2024" sheetId="5" r:id="rId2"/>
-    <sheet name="2023" sheetId="4" r:id="rId3"/>
-    <sheet name="2022" sheetId="3" r:id="rId4"/>
-    <sheet name="2020" sheetId="2" r:id="rId5"/>
-    <sheet name="2019" sheetId="1" r:id="rId6"/>
+    <sheet name="2026" sheetId="7" r:id="rId1"/>
+    <sheet name="2025" sheetId="6" r:id="rId2"/>
+    <sheet name="2024" sheetId="5" r:id="rId3"/>
+    <sheet name="2023" sheetId="4" r:id="rId4"/>
+    <sheet name="2022" sheetId="3" r:id="rId5"/>
+    <sheet name="2020" sheetId="2" r:id="rId6"/>
+    <sheet name="2019" sheetId="1" r:id="rId7"/>
+    <sheet name="csv" sheetId="8" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,12 +36,15 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="960" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="264">
   <si>
     <t>CPU</t>
   </si>
@@ -753,6 +758,84 @@
   </si>
   <si>
     <t>i3-6100</t>
+  </si>
+  <si>
+    <t>ISA</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>mem</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>INT_o</t>
+  </si>
+  <si>
+    <t>FLOAT_o</t>
+  </si>
+  <si>
+    <t>Galaxy Note 8</t>
+  </si>
+  <si>
+    <t>Galaxy Note 20</t>
+  </si>
+  <si>
+    <t>Exynos 8895</t>
+  </si>
+  <si>
+    <t>termux, 4.4.111, clang</t>
+  </si>
+  <si>
+    <t>Snapdragon 865</t>
+  </si>
+  <si>
+    <t>ARMv8.2-A</t>
+  </si>
+  <si>
+    <t>termux, 4.19.113, clang 21.1.8</t>
+  </si>
+  <si>
+    <t>termux, 6.1.138, clang 21.1.8</t>
+  </si>
+  <si>
+    <t>Galaxy S24</t>
+  </si>
+  <si>
+    <t>Exynos 2400</t>
+  </si>
+  <si>
+    <t>ARMv9.2-A</t>
+  </si>
+  <si>
+    <t>6.12.75, gcc 14.2.0</t>
+  </si>
+  <si>
+    <t>Regular PC</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Mobile Phone</t>
+  </si>
+  <si>
+    <t>Network Device (router, NAS)</t>
+  </si>
+  <si>
+    <t>SBC Single Board Computer</t>
+  </si>
+  <si>
+    <t>Network device (NAS, router)</t>
+  </si>
+  <si>
+    <t>regular PC</t>
   </si>
 </sst>
 </file>
@@ -765,7 +848,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -795,8 +878,34 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF606C71"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF606C71"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -857,8 +966,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -866,12 +987,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFE9EBEC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFE9EBEC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFE9EBEC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFE9EBEC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -910,6 +1061,22 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -922,11 +1089,25 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="167" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Link" xfId="1" builtinId="8"/>
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1202,10 +1383,4016 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="0" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{81E641BF-AA9C-48BE-927A-FF2C936C13E0}">
+  <we:reference id="wa200005502" version="1.0.0.12" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200005502" version="1.0.0.12" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+  <we:extLst>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{D87F86FE-615C-45B5-9D79-34F1136793EB}">
+      <we:containsCustomFunctions/>
+    </a:ext>
+    <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uri="{7C84B067-C214-45C3-A712-C9D94CD141B2}">
+      <we:customFunctionIdList>
+        <we:customFunctionIds>_xldudf_GPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CREATE_PROMPT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_LIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HLIST</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CLASSIFY</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TRANSLATE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EXTRACT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TAG</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_CONVERT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FORMAT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SUMMARIZE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_TABLE</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_FILL</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_SPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_HSPLIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_EDIT</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_MATCH</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_VISION</we:customFunctionIds>
+        <we:customFunctionIds>_xldudf_GPT_WEB</we:customFunctionIds>
+      </we:customFunctionIdList>
+    </a:ext>
+  </we:extLst>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BCFD32-DD89-45D1-9DAB-60CCE8B3399A}">
+  <dimension ref="A1:AC63"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.85546875" customWidth="1"/>
+    <col min="5" max="5" width="8.28515625" customWidth="1"/>
+    <col min="6" max="6" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" customWidth="1"/>
+    <col min="12" max="12" width="27.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" customWidth="1"/>
+    <col min="19" max="19" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.85546875" customWidth="1"/>
+    <col min="21" max="21" width="20.85546875" customWidth="1"/>
+    <col min="22" max="22" width="9" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="9" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" s="6" customFormat="1" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="O1" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="P1" s="6" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q1" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="T1" s="23"/>
+      <c r="U1" s="23"/>
+      <c r="V1" s="23"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="Z1" s="23"/>
+      <c r="AA1" s="23"/>
+      <c r="AB1" s="23"/>
+      <c r="AC1" s="23"/>
+    </row>
+    <row r="2" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>667</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="E2" s="19">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.126</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3</v>
+      </c>
+      <c r="H2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="13">
+        <v>40892</v>
+      </c>
+      <c r="K2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M2" s="18">
+        <f>D2*1000</f>
+        <v>541</v>
+      </c>
+      <c r="N2" s="18">
+        <f>E2*1000</f>
+        <v>959</v>
+      </c>
+      <c r="O2" s="18">
+        <f>F2*1000</f>
+        <v>126</v>
+      </c>
+      <c r="P2" s="18">
+        <f>G2*1000</f>
+        <v>3000</v>
+      </c>
+      <c r="Q2" s="18">
+        <f>H2*1000</f>
+        <v>200</v>
+      </c>
+      <c r="T2" s="30"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
+      <c r="AA2" s="24"/>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="25"/>
+    </row>
+    <row r="3" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3">
+        <v>233</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1.238</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1.33</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2.4089999999999998</v>
+      </c>
+      <c r="G3" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H3" s="11">
+        <v>4.3</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="13">
+        <v>41122</v>
+      </c>
+      <c r="K3" t="s">
+        <v>225</v>
+      </c>
+      <c r="M3" s="18">
+        <f t="shared" ref="M3:Q55" si="0">D3*1000</f>
+        <v>1238</v>
+      </c>
+      <c r="N3" s="18">
+        <f t="shared" si="0"/>
+        <v>1330</v>
+      </c>
+      <c r="O3" s="18">
+        <f t="shared" si="0"/>
+        <v>2409</v>
+      </c>
+      <c r="P3" s="18">
+        <f t="shared" si="0"/>
+        <v>5100</v>
+      </c>
+      <c r="Q3" s="18">
+        <f t="shared" si="0"/>
+        <v>4300</v>
+      </c>
+      <c r="R3" s="18"/>
+      <c r="T3" s="30"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="25"/>
+    </row>
+    <row r="4" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4">
+        <v>600</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1.04</v>
+      </c>
+      <c r="E4" s="19">
+        <v>1.6850000000000001</v>
+      </c>
+      <c r="F4" s="10">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G4" s="11">
+        <v>5.5</v>
+      </c>
+      <c r="H4" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13">
+        <v>41487</v>
+      </c>
+      <c r="K4" t="s">
+        <v>228</v>
+      </c>
+      <c r="M4" s="18">
+        <f t="shared" si="0"/>
+        <v>1040</v>
+      </c>
+      <c r="N4" s="18">
+        <f t="shared" si="0"/>
+        <v>1685</v>
+      </c>
+      <c r="O4" s="18">
+        <f t="shared" si="0"/>
+        <v>228</v>
+      </c>
+      <c r="P4" s="18">
+        <f t="shared" si="0"/>
+        <v>5500</v>
+      </c>
+      <c r="Q4" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="R4" s="18"/>
+      <c r="T4" s="30"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="25"/>
+    </row>
+    <row r="5" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="17">
+        <v>400</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1.379</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1.712</v>
+      </c>
+      <c r="F5" s="10">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G5" s="11">
+        <v>6.3</v>
+      </c>
+      <c r="H5" s="11">
+        <v>0.06</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="13">
+        <v>41489</v>
+      </c>
+      <c r="K5" t="s">
+        <v>229</v>
+      </c>
+      <c r="M5" s="18">
+        <f t="shared" si="0"/>
+        <v>1379</v>
+      </c>
+      <c r="N5" s="18">
+        <f t="shared" si="0"/>
+        <v>1712</v>
+      </c>
+      <c r="O5" s="18">
+        <f t="shared" si="0"/>
+        <v>35</v>
+      </c>
+      <c r="P5" s="18">
+        <f t="shared" si="0"/>
+        <v>6300</v>
+      </c>
+      <c r="Q5" s="18">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="R5" s="18"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="25"/>
+    </row>
+    <row r="6" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6">
+        <v>667</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1.024</v>
+      </c>
+      <c r="E6" s="19">
+        <v>1.821</v>
+      </c>
+      <c r="F6" s="10">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="G6" s="11">
+        <v>5.7</v>
+      </c>
+      <c r="H6" s="11">
+        <v>0.4</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="13">
+        <v>41122</v>
+      </c>
+      <c r="K6" t="s">
+        <v>228</v>
+      </c>
+      <c r="M6" s="18">
+        <f t="shared" si="0"/>
+        <v>1024</v>
+      </c>
+      <c r="N6" s="18">
+        <f t="shared" si="0"/>
+        <v>1821</v>
+      </c>
+      <c r="O6" s="18">
+        <f t="shared" si="0"/>
+        <v>238</v>
+      </c>
+      <c r="P6" s="18">
+        <f t="shared" si="0"/>
+        <v>5700</v>
+      </c>
+      <c r="Q6" s="18">
+        <f t="shared" si="0"/>
+        <v>400</v>
+      </c>
+      <c r="R6" s="18"/>
+      <c r="T6" s="30"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="25"/>
+    </row>
+    <row r="7" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="36">
+        <v>700</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2.456</v>
+      </c>
+      <c r="E7" s="19">
+        <v>3.1059999999999999</v>
+      </c>
+      <c r="F7" s="10">
+        <v>2.0289999999999999</v>
+      </c>
+      <c r="G7" s="11">
+        <v>11.3</v>
+      </c>
+      <c r="H7" s="11">
+        <v>3.66</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13"/>
+      <c r="K7" t="s">
+        <v>226</v>
+      </c>
+      <c r="M7" s="18">
+        <f t="shared" si="0"/>
+        <v>2456</v>
+      </c>
+      <c r="N7" s="18">
+        <f t="shared" si="0"/>
+        <v>3106</v>
+      </c>
+      <c r="O7" s="18">
+        <f t="shared" si="0"/>
+        <v>2029</v>
+      </c>
+      <c r="P7" s="18">
+        <f t="shared" si="0"/>
+        <v>11300</v>
+      </c>
+      <c r="Q7" s="18">
+        <f t="shared" si="0"/>
+        <v>3660</v>
+      </c>
+      <c r="R7" s="18"/>
+      <c r="T7" s="30"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="25"/>
+    </row>
+    <row r="8" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8">
+        <v>800</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="E8" s="19">
+        <v>3.282</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="G8" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="H8" s="11">
+        <v>6.69</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K8" t="s">
+        <v>227</v>
+      </c>
+      <c r="M8" s="18">
+        <f t="shared" si="0"/>
+        <v>2748</v>
+      </c>
+      <c r="N8" s="18">
+        <f t="shared" si="0"/>
+        <v>3282</v>
+      </c>
+      <c r="O8" s="18">
+        <f t="shared" si="0"/>
+        <v>3711</v>
+      </c>
+      <c r="P8" s="18">
+        <f t="shared" si="0"/>
+        <v>12800</v>
+      </c>
+      <c r="Q8" s="18">
+        <f t="shared" si="0"/>
+        <v>6690</v>
+      </c>
+      <c r="R8" s="18"/>
+      <c r="T8" s="30"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="25"/>
+    </row>
+    <row r="9" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9" s="16">
+        <v>933</v>
+      </c>
+      <c r="D9" s="10">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="E9" s="19">
+        <v>5.1639999999999997</v>
+      </c>
+      <c r="F9" s="10">
+        <v>8.9160000000000004</v>
+      </c>
+      <c r="G9" s="11">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H9" s="11">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K9" t="s">
+        <v>225</v>
+      </c>
+      <c r="M9" s="18">
+        <f t="shared" si="0"/>
+        <v>4709</v>
+      </c>
+      <c r="N9" s="18">
+        <f t="shared" si="0"/>
+        <v>5164</v>
+      </c>
+      <c r="O9" s="18">
+        <f t="shared" si="0"/>
+        <v>8916</v>
+      </c>
+      <c r="P9" s="18">
+        <f t="shared" si="0"/>
+        <v>19900</v>
+      </c>
+      <c r="Q9" s="18">
+        <f t="shared" si="0"/>
+        <v>16100.000000000002</v>
+      </c>
+      <c r="R9" s="18"/>
+      <c r="T9" s="30"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="25"/>
+    </row>
+    <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10">
+        <v>1008</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3.665</v>
+      </c>
+      <c r="E10" s="19">
+        <v>5.46</v>
+      </c>
+      <c r="F10" s="10">
+        <v>4.6849999999999996</v>
+      </c>
+      <c r="G10" s="11">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H10" s="11">
+        <v>8.4499999999999993</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K10" t="s">
+        <v>227</v>
+      </c>
+      <c r="M10" s="18">
+        <f t="shared" si="0"/>
+        <v>3665</v>
+      </c>
+      <c r="N10" s="18">
+        <f t="shared" si="0"/>
+        <v>5460</v>
+      </c>
+      <c r="O10" s="18">
+        <f t="shared" si="0"/>
+        <v>4685</v>
+      </c>
+      <c r="P10" s="18">
+        <f t="shared" si="0"/>
+        <v>18400</v>
+      </c>
+      <c r="Q10" s="18">
+        <f t="shared" si="0"/>
+        <v>8450</v>
+      </c>
+      <c r="R10" s="18"/>
+      <c r="T10" s="30"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="25"/>
+    </row>
+    <row r="11" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="36">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="10">
+        <v>4.665</v>
+      </c>
+      <c r="E11" s="19">
+        <v>6.4809999999999999</v>
+      </c>
+      <c r="F11" s="10">
+        <v>5.0590000000000002</v>
+      </c>
+      <c r="G11" s="11">
+        <v>22.6</v>
+      </c>
+      <c r="H11" s="11">
+        <v>9.1</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K11" t="s">
+        <v>227</v>
+      </c>
+      <c r="M11" s="18">
+        <f t="shared" si="0"/>
+        <v>4665</v>
+      </c>
+      <c r="N11" s="18">
+        <f t="shared" si="0"/>
+        <v>6481</v>
+      </c>
+      <c r="O11" s="18">
+        <f t="shared" si="0"/>
+        <v>5059</v>
+      </c>
+      <c r="P11" s="18">
+        <f t="shared" si="0"/>
+        <v>22600</v>
+      </c>
+      <c r="Q11" s="18">
+        <f t="shared" si="0"/>
+        <v>9100</v>
+      </c>
+      <c r="R11" s="18"/>
+      <c r="T11" s="30"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="25"/>
+    </row>
+    <row r="12" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12">
+        <v>988</v>
+      </c>
+      <c r="D12" s="10">
+        <v>5.7990000000000004</v>
+      </c>
+      <c r="E12" s="19">
+        <v>6.7169999999999996</v>
+      </c>
+      <c r="F12" s="10">
+        <v>8.0549999999999997</v>
+      </c>
+      <c r="G12" s="11">
+        <v>25.3</v>
+      </c>
+      <c r="H12" s="11">
+        <v>14.5</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="13">
+        <v>42217</v>
+      </c>
+      <c r="K12" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="M12" s="18">
+        <f t="shared" si="0"/>
+        <v>5799</v>
+      </c>
+      <c r="N12" s="18">
+        <f t="shared" si="0"/>
+        <v>6717</v>
+      </c>
+      <c r="O12" s="18">
+        <f t="shared" si="0"/>
+        <v>8055</v>
+      </c>
+      <c r="P12" s="18">
+        <f t="shared" si="0"/>
+        <v>25300</v>
+      </c>
+      <c r="Q12" s="18">
+        <f t="shared" si="0"/>
+        <v>14500</v>
+      </c>
+      <c r="R12" s="18"/>
+      <c r="T12" s="30"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="25"/>
+    </row>
+    <row r="13" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13" s="16">
+        <v>1200</v>
+      </c>
+      <c r="D13" s="10">
+        <v>6.21</v>
+      </c>
+      <c r="E13" s="19">
+        <v>7.0469999999999997</v>
+      </c>
+      <c r="F13" s="10">
+        <v>12.384</v>
+      </c>
+      <c r="G13" s="11">
+        <v>26.4</v>
+      </c>
+      <c r="H13" s="11">
+        <v>22</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="13">
+        <v>41797</v>
+      </c>
+      <c r="K13" t="s">
+        <v>225</v>
+      </c>
+      <c r="M13" s="18">
+        <f t="shared" si="0"/>
+        <v>6210</v>
+      </c>
+      <c r="N13" s="18">
+        <f t="shared" si="0"/>
+        <v>7047</v>
+      </c>
+      <c r="O13" s="18">
+        <f t="shared" si="0"/>
+        <v>12384</v>
+      </c>
+      <c r="P13" s="18">
+        <f t="shared" si="0"/>
+        <v>26400</v>
+      </c>
+      <c r="Q13" s="18">
+        <f t="shared" si="0"/>
+        <v>22000</v>
+      </c>
+      <c r="R13" s="18"/>
+      <c r="T13" s="30"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="25"/>
+    </row>
+    <row r="14" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="16">
+        <v>1666</v>
+      </c>
+      <c r="D14" s="10">
+        <v>7.2430000000000003</v>
+      </c>
+      <c r="E14" s="19">
+        <v>7.109</v>
+      </c>
+      <c r="F14" s="10">
+        <v>7.351</v>
+      </c>
+      <c r="G14" s="11">
+        <v>28.6</v>
+      </c>
+      <c r="H14" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="13">
+        <v>40269</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14" s="5"/>
+      <c r="M14" s="18">
+        <f t="shared" si="0"/>
+        <v>7243</v>
+      </c>
+      <c r="N14" s="18">
+        <f t="shared" si="0"/>
+        <v>7109</v>
+      </c>
+      <c r="O14" s="18">
+        <f t="shared" si="0"/>
+        <v>7351</v>
+      </c>
+      <c r="P14" s="18">
+        <f t="shared" si="0"/>
+        <v>28600</v>
+      </c>
+      <c r="Q14" s="18">
+        <f t="shared" si="0"/>
+        <v>12800</v>
+      </c>
+      <c r="R14" s="18"/>
+      <c r="T14" s="30"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="25"/>
+    </row>
+    <row r="15" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15">
+        <v>2000</v>
+      </c>
+      <c r="D15" s="10">
+        <v>9.3940000000000001</v>
+      </c>
+      <c r="E15" s="19">
+        <v>7.5289999999999999</v>
+      </c>
+      <c r="F15" s="10">
+        <v>13.164</v>
+      </c>
+      <c r="G15" s="11">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="H15" s="11">
+        <v>23.7</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="13">
+        <v>40017</v>
+      </c>
+      <c r="K15" t="s">
+        <v>225</v>
+      </c>
+      <c r="M15" s="18">
+        <f t="shared" si="0"/>
+        <v>9394</v>
+      </c>
+      <c r="N15" s="18">
+        <f t="shared" si="0"/>
+        <v>7529</v>
+      </c>
+      <c r="O15" s="18">
+        <f t="shared" si="0"/>
+        <v>13164</v>
+      </c>
+      <c r="P15" s="18">
+        <f t="shared" si="0"/>
+        <v>33200</v>
+      </c>
+      <c r="Q15" s="18">
+        <f t="shared" si="0"/>
+        <v>23700</v>
+      </c>
+      <c r="R15" s="18"/>
+      <c r="T15" s="30"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="25"/>
+    </row>
+    <row r="16" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" s="16">
+        <v>1600</v>
+      </c>
+      <c r="D16" s="10">
+        <v>7.7519999999999998</v>
+      </c>
+      <c r="E16" s="19">
+        <v>7.5789999999999997</v>
+      </c>
+      <c r="F16" s="10">
+        <v>7.0679999999999996</v>
+      </c>
+      <c r="G16" s="11">
+        <v>30.6</v>
+      </c>
+      <c r="H16" s="11">
+        <v>12.8</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="13">
+        <v>40026</v>
+      </c>
+      <c r="K16" t="s">
+        <v>225</v>
+      </c>
+      <c r="M16" s="18">
+        <f t="shared" si="0"/>
+        <v>7752</v>
+      </c>
+      <c r="N16" s="18">
+        <f t="shared" si="0"/>
+        <v>7579</v>
+      </c>
+      <c r="O16" s="18">
+        <f t="shared" si="0"/>
+        <v>7068</v>
+      </c>
+      <c r="P16" s="18">
+        <f t="shared" si="0"/>
+        <v>30600</v>
+      </c>
+      <c r="Q16" s="18">
+        <f t="shared" si="0"/>
+        <v>12800</v>
+      </c>
+      <c r="R16" s="18"/>
+      <c r="T16" s="30"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="25"/>
+    </row>
+    <row r="17" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17" s="16">
+        <v>1666</v>
+      </c>
+      <c r="D17" s="10">
+        <v>9.3859999999999992</v>
+      </c>
+      <c r="E17" s="19">
+        <v>8.39</v>
+      </c>
+      <c r="F17" s="10">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="G17" s="11">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="H17" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="13">
+        <v>41496</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17" s="18">
+        <f t="shared" si="0"/>
+        <v>9386</v>
+      </c>
+      <c r="N17" s="18">
+        <f t="shared" si="0"/>
+        <v>8390</v>
+      </c>
+      <c r="O17" s="18">
+        <f t="shared" si="0"/>
+        <v>7313</v>
+      </c>
+      <c r="P17" s="18">
+        <f t="shared" si="0"/>
+        <v>35300</v>
+      </c>
+      <c r="Q17" s="18">
+        <f t="shared" si="0"/>
+        <v>13200</v>
+      </c>
+      <c r="R17" s="18"/>
+      <c r="T17" s="30"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="25"/>
+    </row>
+    <row r="18" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="36" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="36">
+        <v>1200</v>
+      </c>
+      <c r="D18" s="10">
+        <v>6.78</v>
+      </c>
+      <c r="E18" s="19">
+        <v>9.5239999999999991</v>
+      </c>
+      <c r="F18" s="10">
+        <v>9.1739999999999995</v>
+      </c>
+      <c r="G18" s="11">
+        <v>33</v>
+      </c>
+      <c r="H18" s="11">
+        <v>16.5</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="13">
+        <v>45298</v>
+      </c>
+      <c r="K18" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="M18" s="18">
+        <f t="shared" si="0"/>
+        <v>6780</v>
+      </c>
+      <c r="N18" s="18">
+        <f t="shared" si="0"/>
+        <v>9524</v>
+      </c>
+      <c r="O18" s="18">
+        <f t="shared" si="0"/>
+        <v>9174</v>
+      </c>
+      <c r="P18" s="18">
+        <f t="shared" si="0"/>
+        <v>33000</v>
+      </c>
+      <c r="Q18" s="18">
+        <f t="shared" si="0"/>
+        <v>16500</v>
+      </c>
+      <c r="R18" s="18"/>
+      <c r="T18" s="30"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="25"/>
+    </row>
+    <row r="19" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19">
+        <v>1512</v>
+      </c>
+      <c r="D19" s="10">
+        <v>4.5910000000000002</v>
+      </c>
+      <c r="E19" s="19">
+        <v>9.8949999999999996</v>
+      </c>
+      <c r="F19" s="10">
+        <v>9.0860000000000003</v>
+      </c>
+      <c r="G19" s="11">
+        <v>28.5</v>
+      </c>
+      <c r="H19" s="11">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="13">
+        <v>42031</v>
+      </c>
+      <c r="K19" t="s">
+        <v>227</v>
+      </c>
+      <c r="M19" s="18">
+        <f t="shared" si="0"/>
+        <v>4591</v>
+      </c>
+      <c r="N19" s="18">
+        <f t="shared" si="0"/>
+        <v>9895</v>
+      </c>
+      <c r="O19" s="18">
+        <f t="shared" si="0"/>
+        <v>9086</v>
+      </c>
+      <c r="P19" s="18">
+        <f t="shared" si="0"/>
+        <v>28500</v>
+      </c>
+      <c r="Q19" s="18">
+        <f t="shared" si="0"/>
+        <v>16400</v>
+      </c>
+      <c r="R19" s="18"/>
+      <c r="T19" s="30"/>
+      <c r="U19" s="24"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="24"/>
+      <c r="X19" s="24"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="24"/>
+      <c r="AA19" s="24"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="25"/>
+    </row>
+    <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="36" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20" s="36">
+        <v>1200</v>
+      </c>
+      <c r="D20" s="10">
+        <v>8.68</v>
+      </c>
+      <c r="E20" s="19">
+        <v>10.948</v>
+      </c>
+      <c r="F20" s="10">
+        <v>10.154999999999999</v>
+      </c>
+      <c r="G20" s="11">
+        <v>39.718000000000004</v>
+      </c>
+      <c r="H20" s="11">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="13">
+        <v>45319</v>
+      </c>
+      <c r="K20" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="0"/>
+        <v>8680</v>
+      </c>
+      <c r="N20" s="18">
+        <f t="shared" si="0"/>
+        <v>10948</v>
+      </c>
+      <c r="O20" s="18">
+        <f t="shared" si="0"/>
+        <v>10155</v>
+      </c>
+      <c r="P20" s="18">
+        <f t="shared" si="0"/>
+        <v>39718</v>
+      </c>
+      <c r="Q20" s="18">
+        <f t="shared" si="0"/>
+        <v>18310</v>
+      </c>
+      <c r="R20" s="18"/>
+      <c r="T20" s="31"/>
+    </row>
+    <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21">
+        <v>1800</v>
+      </c>
+      <c r="D21" s="10">
+        <v>11.269</v>
+      </c>
+      <c r="E21" s="19">
+        <v>11.927</v>
+      </c>
+      <c r="F21" s="10">
+        <v>20.516999999999999</v>
+      </c>
+      <c r="G21" s="11">
+        <v>46.6</v>
+      </c>
+      <c r="H21" s="11">
+        <v>37</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="13">
+        <v>40672</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21" s="18">
+        <f t="shared" si="0"/>
+        <v>11269</v>
+      </c>
+      <c r="N21" s="18">
+        <f t="shared" si="0"/>
+        <v>11927</v>
+      </c>
+      <c r="O21" s="18">
+        <f t="shared" si="0"/>
+        <v>20517</v>
+      </c>
+      <c r="P21" s="18">
+        <f t="shared" si="0"/>
+        <v>46600</v>
+      </c>
+      <c r="Q21" s="18">
+        <f t="shared" si="0"/>
+        <v>37000</v>
+      </c>
+      <c r="R21" s="18"/>
+      <c r="T21" s="30"/>
+      <c r="U21" s="24"/>
+      <c r="V21" s="24"/>
+      <c r="W21" s="24"/>
+      <c r="X21" s="24"/>
+      <c r="Y21" s="24"/>
+      <c r="Z21" s="24"/>
+      <c r="AA21" s="24"/>
+      <c r="AB21" s="24"/>
+      <c r="AC21" s="25"/>
+    </row>
+    <row r="22" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22" s="16">
+        <v>2000</v>
+      </c>
+      <c r="D22" s="10">
+        <v>12.138</v>
+      </c>
+      <c r="E22" s="19">
+        <v>12.568</v>
+      </c>
+      <c r="F22" s="10">
+        <v>21.143999999999998</v>
+      </c>
+      <c r="G22" s="11">
+        <v>49.6</v>
+      </c>
+      <c r="H22" s="11">
+        <v>38.1</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="J22" s="13">
+        <v>39919</v>
+      </c>
+      <c r="K22" t="s">
+        <v>225</v>
+      </c>
+      <c r="M22" s="18">
+        <f t="shared" si="0"/>
+        <v>12138</v>
+      </c>
+      <c r="N22" s="18">
+        <f t="shared" si="0"/>
+        <v>12568</v>
+      </c>
+      <c r="O22" s="18">
+        <f t="shared" si="0"/>
+        <v>21144</v>
+      </c>
+      <c r="P22" s="18">
+        <f t="shared" si="0"/>
+        <v>49600</v>
+      </c>
+      <c r="Q22" s="18">
+        <f t="shared" si="0"/>
+        <v>38100</v>
+      </c>
+      <c r="R22" s="18"/>
+      <c r="T22" s="30"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="25"/>
+    </row>
+    <row r="23" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="16">
+        <v>1860</v>
+      </c>
+      <c r="D23" s="10">
+        <v>18.433</v>
+      </c>
+      <c r="E23" s="19">
+        <v>15.15</v>
+      </c>
+      <c r="F23" s="10">
+        <v>16.635999999999999</v>
+      </c>
+      <c r="G23" s="11">
+        <v>66</v>
+      </c>
+      <c r="H23" s="11">
+        <v>30</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="13">
+        <v>41788</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L23" s="5"/>
+      <c r="M23" s="18">
+        <f t="shared" si="0"/>
+        <v>18433</v>
+      </c>
+      <c r="N23" s="18">
+        <f t="shared" si="0"/>
+        <v>15150</v>
+      </c>
+      <c r="O23" s="18">
+        <f t="shared" si="0"/>
+        <v>16636</v>
+      </c>
+      <c r="P23" s="18">
+        <f t="shared" si="0"/>
+        <v>66000</v>
+      </c>
+      <c r="Q23" s="18">
+        <f t="shared" si="0"/>
+        <v>30000</v>
+      </c>
+      <c r="R23" s="18"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="25"/>
+    </row>
+    <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24" s="36">
+        <v>1400</v>
+      </c>
+      <c r="D24" s="10">
+        <v>14.398999999999999</v>
+      </c>
+      <c r="E24" s="19">
+        <v>15.946999999999999</v>
+      </c>
+      <c r="F24" s="10">
+        <v>17.788</v>
+      </c>
+      <c r="G24" s="11">
+        <v>61.170999999999999</v>
+      </c>
+      <c r="H24" s="11">
+        <v>32.072000000000003</v>
+      </c>
+      <c r="I24" s="8"/>
+      <c r="J24" s="13">
+        <v>45772</v>
+      </c>
+      <c r="K24" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="L24" s="5"/>
+      <c r="M24" s="18">
+        <f t="shared" si="0"/>
+        <v>14399</v>
+      </c>
+      <c r="N24" s="18">
+        <f t="shared" si="0"/>
+        <v>15947</v>
+      </c>
+      <c r="O24" s="18">
+        <f t="shared" si="0"/>
+        <v>17788</v>
+      </c>
+      <c r="P24" s="18">
+        <f t="shared" si="0"/>
+        <v>61171</v>
+      </c>
+      <c r="Q24" s="18">
+        <f t="shared" si="0"/>
+        <v>32072.000000000004</v>
+      </c>
+      <c r="R24" s="18"/>
+      <c r="T24" s="31"/>
+    </row>
+    <row r="25" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25">
+        <v>1800</v>
+      </c>
+      <c r="D25" s="10">
+        <v>13.595000000000001</v>
+      </c>
+      <c r="E25" s="19">
+        <v>16.120999999999999</v>
+      </c>
+      <c r="F25" s="10">
+        <v>19.565999999999999</v>
+      </c>
+      <c r="G25" s="11">
+        <v>59.9</v>
+      </c>
+      <c r="H25" s="11">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" s="13">
+        <v>40672</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L25" s="5"/>
+      <c r="M25" s="18">
+        <f t="shared" si="0"/>
+        <v>13595</v>
+      </c>
+      <c r="N25" s="18">
+        <f t="shared" si="0"/>
+        <v>16120.999999999998</v>
+      </c>
+      <c r="O25" s="18">
+        <f t="shared" si="0"/>
+        <v>19566</v>
+      </c>
+      <c r="P25" s="18">
+        <f t="shared" si="0"/>
+        <v>59900</v>
+      </c>
+      <c r="Q25" s="18">
+        <f t="shared" si="0"/>
+        <v>35300</v>
+      </c>
+      <c r="R25" s="18"/>
+      <c r="T25" s="30"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="25"/>
+    </row>
+    <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" s="16">
+        <v>1580</v>
+      </c>
+      <c r="D26" s="10">
+        <v>19.981000000000002</v>
+      </c>
+      <c r="E26" s="19">
+        <v>16.207000000000001</v>
+      </c>
+      <c r="F26" s="10">
+        <v>18.001000000000001</v>
+      </c>
+      <c r="G26" s="11">
+        <v>71</v>
+      </c>
+      <c r="H26" s="11">
+        <v>32.5</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="13">
+        <v>41851</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L26" s="5"/>
+      <c r="M26" s="18">
+        <f t="shared" si="0"/>
+        <v>19981</v>
+      </c>
+      <c r="N26" s="18">
+        <f t="shared" si="0"/>
+        <v>16207</v>
+      </c>
+      <c r="O26" s="18">
+        <f t="shared" si="0"/>
+        <v>18001</v>
+      </c>
+      <c r="P26" s="18">
+        <f t="shared" si="0"/>
+        <v>71000</v>
+      </c>
+      <c r="Q26" s="18">
+        <f t="shared" si="0"/>
+        <v>32500</v>
+      </c>
+      <c r="R26" s="18"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="24"/>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="24"/>
+      <c r="AB26" s="24"/>
+      <c r="AC26" s="25"/>
+    </row>
+    <row r="27" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27" s="16">
+        <v>1299</v>
+      </c>
+      <c r="D27" s="10">
+        <v>19.050999999999998</v>
+      </c>
+      <c r="E27" s="19">
+        <v>17.286000000000001</v>
+      </c>
+      <c r="F27" s="10">
+        <v>25.289000000000001</v>
+      </c>
+      <c r="G27" s="11">
+        <v>72.2</v>
+      </c>
+      <c r="H27" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L27" s="5"/>
+      <c r="M27" s="18">
+        <f t="shared" si="0"/>
+        <v>19051</v>
+      </c>
+      <c r="N27" s="18">
+        <f t="shared" si="0"/>
+        <v>17286</v>
+      </c>
+      <c r="O27" s="18">
+        <f t="shared" si="0"/>
+        <v>25289</v>
+      </c>
+      <c r="P27" s="18">
+        <f t="shared" si="0"/>
+        <v>72200</v>
+      </c>
+      <c r="Q27" s="18">
+        <f t="shared" si="0"/>
+        <v>45600</v>
+      </c>
+      <c r="R27" s="18"/>
+      <c r="T27" s="30"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="25"/>
+    </row>
+    <row r="28" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28">
+        <v>2527</v>
+      </c>
+      <c r="D28" s="10">
+        <v>28.488</v>
+      </c>
+      <c r="E28" s="19">
+        <v>17.780999999999999</v>
+      </c>
+      <c r="F28" s="10">
+        <v>36.673000000000002</v>
+      </c>
+      <c r="G28" s="11">
+        <v>87.2</v>
+      </c>
+      <c r="H28" s="11">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" s="13">
+        <v>41457</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L28" s="5"/>
+      <c r="M28" s="18">
+        <f t="shared" si="0"/>
+        <v>28488</v>
+      </c>
+      <c r="N28" s="18">
+        <f t="shared" si="0"/>
+        <v>17781</v>
+      </c>
+      <c r="O28" s="18">
+        <f t="shared" si="0"/>
+        <v>36673</v>
+      </c>
+      <c r="P28" s="18">
+        <f t="shared" si="0"/>
+        <v>87200</v>
+      </c>
+      <c r="Q28" s="18">
+        <f t="shared" si="0"/>
+        <v>66100</v>
+      </c>
+      <c r="R28" s="18"/>
+      <c r="T28" s="30"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="24"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="24"/>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
+      <c r="AB28" s="24"/>
+      <c r="AC28" s="25"/>
+    </row>
+    <row r="29" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29" s="17">
+        <v>1600</v>
+      </c>
+      <c r="D29" s="10">
+        <v>23.695</v>
+      </c>
+      <c r="E29" s="19">
+        <v>17.817</v>
+      </c>
+      <c r="F29" s="10">
+        <v>25.515999999999998</v>
+      </c>
+      <c r="G29" s="11">
+        <v>80.7</v>
+      </c>
+      <c r="H29" s="11">
+        <v>46</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="J29" s="13">
+        <v>44089</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L29" s="5"/>
+      <c r="M29" s="18">
+        <f t="shared" si="0"/>
+        <v>23695</v>
+      </c>
+      <c r="N29" s="18">
+        <f t="shared" si="0"/>
+        <v>17817</v>
+      </c>
+      <c r="O29" s="18">
+        <f t="shared" si="0"/>
+        <v>25516</v>
+      </c>
+      <c r="P29" s="18">
+        <f t="shared" si="0"/>
+        <v>80700</v>
+      </c>
+      <c r="Q29" s="18">
+        <f t="shared" si="0"/>
+        <v>46000</v>
+      </c>
+      <c r="R29" s="18"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="24"/>
+      <c r="V29" s="24"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="24"/>
+      <c r="AB29" s="24"/>
+      <c r="AC29" s="25"/>
+    </row>
+    <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" s="16">
+        <v>1400</v>
+      </c>
+      <c r="D30" s="10">
+        <v>18.776</v>
+      </c>
+      <c r="E30" s="19">
+        <v>17.878</v>
+      </c>
+      <c r="F30" s="10">
+        <v>29.106000000000002</v>
+      </c>
+      <c r="G30" s="11">
+        <v>73.2</v>
+      </c>
+      <c r="H30" s="11">
+        <v>52.5</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="13">
+        <v>43641</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L30" s="5"/>
+      <c r="M30" s="18">
+        <f t="shared" si="0"/>
+        <v>18776</v>
+      </c>
+      <c r="N30" s="18">
+        <f t="shared" si="0"/>
+        <v>17878</v>
+      </c>
+      <c r="O30" s="18">
+        <f t="shared" si="0"/>
+        <v>29106</v>
+      </c>
+      <c r="P30" s="18">
+        <f t="shared" si="0"/>
+        <v>73200</v>
+      </c>
+      <c r="Q30" s="18">
+        <f t="shared" si="0"/>
+        <v>52500</v>
+      </c>
+      <c r="R30" s="18"/>
+      <c r="T30" s="30"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24"/>
+      <c r="X30" s="24"/>
+      <c r="Y30" s="24"/>
+      <c r="Z30" s="24"/>
+      <c r="AA30" s="24"/>
+      <c r="AB30" s="24"/>
+      <c r="AC30" s="25"/>
+    </row>
+    <row r="31" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="36">
+        <v>1500</v>
+      </c>
+      <c r="D31" s="10">
+        <v>15.319000000000001</v>
+      </c>
+      <c r="E31" s="19">
+        <v>18.061</v>
+      </c>
+      <c r="F31" s="10">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="G31" s="11">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="H31" s="11">
+        <v>62.4</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K31" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="L31" t="s">
+        <v>256</v>
+      </c>
+      <c r="M31" s="18">
+        <f t="shared" si="0"/>
+        <v>15319</v>
+      </c>
+      <c r="N31" s="18">
+        <f t="shared" si="0"/>
+        <v>18061</v>
+      </c>
+      <c r="O31" s="18">
+        <f t="shared" si="0"/>
+        <v>34620</v>
+      </c>
+      <c r="P31" s="18">
+        <f t="shared" si="0"/>
+        <v>67400</v>
+      </c>
+      <c r="Q31" s="18">
+        <f t="shared" si="0"/>
+        <v>62400</v>
+      </c>
+      <c r="R31" s="18"/>
+      <c r="T31" s="30"/>
+      <c r="U31" s="24"/>
+      <c r="V31" s="24"/>
+      <c r="W31" s="24"/>
+      <c r="X31" s="24"/>
+      <c r="Y31" s="24"/>
+      <c r="Z31" s="24"/>
+      <c r="AA31" s="24"/>
+      <c r="AB31" s="24"/>
+      <c r="AC31" s="25"/>
+    </row>
+    <row r="32" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32">
+        <v>2607</v>
+      </c>
+      <c r="D32" s="10">
+        <v>18.265000000000001</v>
+      </c>
+      <c r="E32" s="19">
+        <v>18.957999999999998</v>
+      </c>
+      <c r="F32" s="10">
+        <v>31.843</v>
+      </c>
+      <c r="G32" s="11">
+        <v>74.8</v>
+      </c>
+      <c r="H32" s="11">
+        <v>57.4</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="J32" s="13">
+        <v>41151</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32" s="5"/>
+      <c r="M32" s="18">
+        <f t="shared" si="0"/>
+        <v>18265</v>
+      </c>
+      <c r="N32" s="18">
+        <f t="shared" si="0"/>
+        <v>18958</v>
+      </c>
+      <c r="O32" s="18">
+        <f t="shared" si="0"/>
+        <v>31843</v>
+      </c>
+      <c r="P32" s="18">
+        <f t="shared" si="0"/>
+        <v>74800</v>
+      </c>
+      <c r="Q32" s="18">
+        <f t="shared" si="0"/>
+        <v>57400</v>
+      </c>
+      <c r="R32" s="18"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="24"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="24"/>
+      <c r="Z32" s="24"/>
+      <c r="AA32" s="24"/>
+      <c r="AB32" s="24"/>
+      <c r="AC32" s="25"/>
+    </row>
+    <row r="33" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33">
+        <v>2100</v>
+      </c>
+      <c r="D33" s="10">
+        <v>14.395</v>
+      </c>
+      <c r="E33" s="19">
+        <v>19.298999999999999</v>
+      </c>
+      <c r="F33" s="10">
+        <v>23.132000000000001</v>
+      </c>
+      <c r="G33" s="11">
+        <v>68.2</v>
+      </c>
+      <c r="H33" s="11">
+        <v>41.7</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="13">
+        <v>40060</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L33" s="5"/>
+      <c r="M33" s="18">
+        <f t="shared" si="0"/>
+        <v>14395</v>
+      </c>
+      <c r="N33" s="18">
+        <f t="shared" si="0"/>
+        <v>19299</v>
+      </c>
+      <c r="O33" s="18">
+        <f t="shared" si="0"/>
+        <v>23132</v>
+      </c>
+      <c r="P33" s="18">
+        <f t="shared" si="0"/>
+        <v>68200</v>
+      </c>
+      <c r="Q33" s="18">
+        <f t="shared" si="0"/>
+        <v>41700</v>
+      </c>
+      <c r="R33" s="18"/>
+      <c r="T33" s="30"/>
+      <c r="U33" s="24"/>
+      <c r="V33" s="24"/>
+      <c r="W33" s="24"/>
+      <c r="X33" s="24"/>
+      <c r="Y33" s="24"/>
+      <c r="Z33" s="24"/>
+      <c r="AA33" s="24"/>
+      <c r="AB33" s="24"/>
+      <c r="AC33" s="25"/>
+    </row>
+    <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34" s="16">
+        <v>2266</v>
+      </c>
+      <c r="D34" s="10">
+        <v>28.631</v>
+      </c>
+      <c r="E34" s="19">
+        <v>19.780999999999999</v>
+      </c>
+      <c r="F34" s="10">
+        <v>31.140999999999998</v>
+      </c>
+      <c r="G34" s="11">
+        <v>92.9</v>
+      </c>
+      <c r="H34" s="11">
+        <v>56.1</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J34" s="13">
+        <v>42713</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L34" s="5"/>
+      <c r="M34" s="18">
+        <f t="shared" si="0"/>
+        <v>28631</v>
+      </c>
+      <c r="N34" s="18">
+        <f t="shared" si="0"/>
+        <v>19781</v>
+      </c>
+      <c r="O34" s="18">
+        <f t="shared" si="0"/>
+        <v>31141</v>
+      </c>
+      <c r="P34" s="18">
+        <f t="shared" si="0"/>
+        <v>92900</v>
+      </c>
+      <c r="Q34" s="18">
+        <f t="shared" si="0"/>
+        <v>56100</v>
+      </c>
+      <c r="R34" s="18"/>
+      <c r="T34" s="30"/>
+      <c r="U34" s="24"/>
+      <c r="V34" s="24"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="24"/>
+      <c r="Y34" s="24"/>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="24"/>
+      <c r="AB34" s="24"/>
+      <c r="AC34" s="25"/>
+    </row>
+    <row r="35" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35" s="15">
+        <v>2400</v>
+      </c>
+      <c r="D35" s="10">
+        <v>23.448</v>
+      </c>
+      <c r="E35" s="19">
+        <v>32.408000000000001</v>
+      </c>
+      <c r="F35" s="10">
+        <v>50.741999999999997</v>
+      </c>
+      <c r="G35" s="11">
+        <v>113.1</v>
+      </c>
+      <c r="H35" s="11">
+        <v>91.5</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="13">
+        <v>46116</v>
+      </c>
+      <c r="K35" s="33" t="s">
+        <v>224</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="M35" s="18">
+        <f t="shared" ref="M35:Q35" si="1">D35*1000</f>
+        <v>23448</v>
+      </c>
+      <c r="N35" s="18">
+        <f t="shared" si="1"/>
+        <v>32408</v>
+      </c>
+      <c r="O35" s="18">
+        <f t="shared" si="1"/>
+        <v>50742</v>
+      </c>
+      <c r="P35" s="18">
+        <f t="shared" si="1"/>
+        <v>113100</v>
+      </c>
+      <c r="Q35" s="18">
+        <f t="shared" si="1"/>
+        <v>91500</v>
+      </c>
+      <c r="R35" s="18"/>
+      <c r="T35" s="30"/>
+      <c r="U35" s="24"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
+      <c r="AB35" s="24"/>
+      <c r="AC35" s="25"/>
+    </row>
+    <row r="36" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="16">
+        <v>2043</v>
+      </c>
+      <c r="D36" s="10">
+        <v>19.359000000000002</v>
+      </c>
+      <c r="E36" s="19">
+        <v>19.808</v>
+      </c>
+      <c r="F36" s="10">
+        <v>33.182000000000002</v>
+      </c>
+      <c r="G36" s="11">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="H36" s="11">
+        <v>59.8</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="J36" s="13">
+        <v>41919</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36" s="5"/>
+      <c r="M36" s="18">
+        <f t="shared" si="0"/>
+        <v>19359</v>
+      </c>
+      <c r="N36" s="18">
+        <f t="shared" si="0"/>
+        <v>19808</v>
+      </c>
+      <c r="O36" s="18">
+        <f t="shared" si="0"/>
+        <v>33182</v>
+      </c>
+      <c r="P36" s="18">
+        <f t="shared" si="0"/>
+        <v>78600</v>
+      </c>
+      <c r="Q36" s="18">
+        <f t="shared" si="0"/>
+        <v>59800</v>
+      </c>
+      <c r="R36" s="18"/>
+      <c r="T36" s="30"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
+      <c r="W36" s="24"/>
+      <c r="X36" s="24"/>
+      <c r="Y36" s="24"/>
+      <c r="Z36" s="24"/>
+      <c r="AA36" s="24"/>
+      <c r="AB36" s="24"/>
+      <c r="AC36" s="25"/>
+    </row>
+    <row r="37" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37">
+        <v>2832</v>
+      </c>
+      <c r="D37" s="10">
+        <v>33.670999999999999</v>
+      </c>
+      <c r="E37" s="19">
+        <v>23.584</v>
+      </c>
+      <c r="F37" s="10">
+        <v>36.384</v>
+      </c>
+      <c r="G37" s="11">
+        <v>110.1</v>
+      </c>
+      <c r="H37" s="11">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="J37" s="13">
+        <v>42443</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L37" s="5"/>
+      <c r="M37" s="18">
+        <f t="shared" si="0"/>
+        <v>33671</v>
+      </c>
+      <c r="N37" s="18">
+        <f t="shared" si="0"/>
+        <v>23584</v>
+      </c>
+      <c r="O37" s="18">
+        <f t="shared" si="0"/>
+        <v>36384</v>
+      </c>
+      <c r="P37" s="18">
+        <f t="shared" si="0"/>
+        <v>110100</v>
+      </c>
+      <c r="Q37" s="18">
+        <f t="shared" si="0"/>
+        <v>65600</v>
+      </c>
+      <c r="R37" s="18"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="24"/>
+      <c r="V37" s="24"/>
+      <c r="W37" s="24"/>
+      <c r="X37" s="24"/>
+      <c r="Y37" s="24"/>
+      <c r="Z37" s="24"/>
+      <c r="AA37" s="24"/>
+      <c r="AB37" s="24"/>
+      <c r="AC37" s="25"/>
+    </row>
+    <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38">
+        <v>3066</v>
+      </c>
+      <c r="D38" s="10">
+        <v>28.776</v>
+      </c>
+      <c r="E38" s="19">
+        <v>23.881</v>
+      </c>
+      <c r="F38" s="10">
+        <v>47.396000000000001</v>
+      </c>
+      <c r="G38" s="11">
+        <v>103.658</v>
+      </c>
+      <c r="H38" s="11">
+        <v>85.453000000000003</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="J38" s="13">
+        <v>44691</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L38" s="5"/>
+      <c r="M38" s="18">
+        <f t="shared" si="0"/>
+        <v>28776</v>
+      </c>
+      <c r="N38" s="18">
+        <f t="shared" si="0"/>
+        <v>23881</v>
+      </c>
+      <c r="O38" s="18">
+        <f t="shared" si="0"/>
+        <v>47396</v>
+      </c>
+      <c r="P38" s="18">
+        <f t="shared" si="0"/>
+        <v>103658</v>
+      </c>
+      <c r="Q38" s="18">
+        <f t="shared" si="0"/>
+        <v>85453</v>
+      </c>
+      <c r="R38" s="18"/>
+      <c r="T38" s="30"/>
+      <c r="U38" s="24"/>
+      <c r="V38" s="24"/>
+      <c r="W38" s="24"/>
+      <c r="X38" s="24"/>
+      <c r="Y38" s="24"/>
+      <c r="Z38" s="24"/>
+      <c r="AA38" s="24"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="25"/>
+    </row>
+    <row r="39" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39">
+        <v>3200</v>
+      </c>
+      <c r="D39" s="10">
+        <v>37.845999999999997</v>
+      </c>
+      <c r="E39" s="19">
+        <v>23.882000000000001</v>
+      </c>
+      <c r="F39" s="10">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="G39" s="11">
+        <v>116.6</v>
+      </c>
+      <c r="H39" s="11">
+        <v>85.5</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="13">
+        <v>41537</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L39" s="5"/>
+      <c r="M39" s="18">
+        <f t="shared" si="0"/>
+        <v>37846</v>
+      </c>
+      <c r="N39" s="18">
+        <f t="shared" si="0"/>
+        <v>23882</v>
+      </c>
+      <c r="O39" s="18">
+        <f t="shared" si="0"/>
+        <v>47437</v>
+      </c>
+      <c r="P39" s="18">
+        <f t="shared" si="0"/>
+        <v>116600</v>
+      </c>
+      <c r="Q39" s="18">
+        <f t="shared" si="0"/>
+        <v>85500</v>
+      </c>
+      <c r="R39" s="18"/>
+      <c r="T39" s="30"/>
+      <c r="U39" s="24"/>
+      <c r="V39" s="24"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="25"/>
+    </row>
+    <row r="40" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40">
+        <v>2667</v>
+      </c>
+      <c r="D40" s="10">
+        <v>24.206</v>
+      </c>
+      <c r="E40" s="19">
+        <v>24.602</v>
+      </c>
+      <c r="F40" s="10">
+        <v>41.085000000000001</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="J40" s="13">
+        <v>40683</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L40" s="5"/>
+      <c r="M40" s="18">
+        <f t="shared" si="0"/>
+        <v>24206</v>
+      </c>
+      <c r="N40" s="18">
+        <f t="shared" si="0"/>
+        <v>24602</v>
+      </c>
+      <c r="O40" s="18">
+        <f t="shared" si="0"/>
+        <v>41085</v>
+      </c>
+      <c r="P40" s="18"/>
+      <c r="Q40" s="18"/>
+      <c r="R40" s="18"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
+      <c r="Y40" s="24"/>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="25"/>
+    </row>
+    <row r="41" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41">
+        <v>2829</v>
+      </c>
+      <c r="D41" s="10">
+        <v>21.475999999999999</v>
+      </c>
+      <c r="E41" s="19">
+        <v>25.608000000000001</v>
+      </c>
+      <c r="F41" s="10">
+        <v>30.663</v>
+      </c>
+      <c r="G41" s="11">
+        <v>95.2</v>
+      </c>
+      <c r="H41" s="11">
+        <v>55.3</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="J41" s="13">
+        <v>39896</v>
+      </c>
+      <c r="K41" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L41" s="5"/>
+      <c r="M41" s="18">
+        <f t="shared" si="0"/>
+        <v>21476</v>
+      </c>
+      <c r="N41" s="18">
+        <f t="shared" si="0"/>
+        <v>25608</v>
+      </c>
+      <c r="O41" s="18">
+        <f t="shared" si="0"/>
+        <v>30663</v>
+      </c>
+      <c r="P41" s="18">
+        <f t="shared" si="0"/>
+        <v>95200</v>
+      </c>
+      <c r="Q41" s="18">
+        <f t="shared" si="0"/>
+        <v>55300</v>
+      </c>
+      <c r="R41" s="18"/>
+      <c r="T41" s="30"/>
+      <c r="U41" s="24"/>
+      <c r="V41" s="24"/>
+      <c r="W41" s="24"/>
+      <c r="X41" s="24"/>
+      <c r="Y41" s="24"/>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="25"/>
+    </row>
+    <row r="42" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42">
+        <v>2667</v>
+      </c>
+      <c r="D42" s="10">
+        <v>27.460999999999999</v>
+      </c>
+      <c r="E42" s="19">
+        <v>26.341999999999999</v>
+      </c>
+      <c r="F42" s="10">
+        <v>27.893999999999998</v>
+      </c>
+      <c r="G42" s="11">
+        <v>107.5</v>
+      </c>
+      <c r="H42" s="11">
+        <v>86.4</v>
+      </c>
+      <c r="I42" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42" s="13">
+        <v>43956</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L42" s="5"/>
+      <c r="M42" s="18">
+        <f t="shared" si="0"/>
+        <v>27461</v>
+      </c>
+      <c r="N42" s="18">
+        <f t="shared" si="0"/>
+        <v>26342</v>
+      </c>
+      <c r="O42" s="18">
+        <f t="shared" si="0"/>
+        <v>27894</v>
+      </c>
+      <c r="P42" s="18">
+        <f t="shared" si="0"/>
+        <v>107500</v>
+      </c>
+      <c r="Q42" s="18">
+        <f t="shared" si="0"/>
+        <v>86400</v>
+      </c>
+      <c r="R42" s="18"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="24"/>
+      <c r="V42" s="24"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="24"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="25"/>
+    </row>
+    <row r="43" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43">
+        <v>3352</v>
+      </c>
+      <c r="D43" s="10">
+        <v>28.021999999999998</v>
+      </c>
+      <c r="E43" s="19">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="F43" s="10">
+        <v>44.103999999999999</v>
+      </c>
+      <c r="G43" s="11">
+        <v>122.4</v>
+      </c>
+      <c r="H43" s="11">
+        <v>79.2</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="J43" s="13">
+        <v>42315</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L43" s="5"/>
+      <c r="M43" s="18">
+        <f t="shared" si="0"/>
+        <v>28022</v>
+      </c>
+      <c r="N43" s="18">
+        <f t="shared" si="0"/>
+        <v>32586</v>
+      </c>
+      <c r="O43" s="18">
+        <f t="shared" si="0"/>
+        <v>44104</v>
+      </c>
+      <c r="P43" s="18">
+        <f t="shared" si="0"/>
+        <v>122400</v>
+      </c>
+      <c r="Q43" s="18">
+        <f t="shared" si="0"/>
+        <v>79200</v>
+      </c>
+      <c r="R43" s="18"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="24"/>
+      <c r="V43" s="24"/>
+      <c r="W43" s="24"/>
+      <c r="X43" s="24"/>
+      <c r="Y43" s="24"/>
+      <c r="Z43" s="24"/>
+      <c r="AA43" s="24"/>
+      <c r="AB43" s="24"/>
+      <c r="AC43" s="25"/>
+    </row>
+    <row r="44" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44" s="16">
+        <v>2300</v>
+      </c>
+      <c r="D44" s="10">
+        <v>39.049999999999997</v>
+      </c>
+      <c r="E44" s="19">
+        <v>33.215000000000003</v>
+      </c>
+      <c r="F44" s="10">
+        <v>54.26</v>
+      </c>
+      <c r="G44" s="11">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="H44" s="11">
+        <v>97.8</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="13">
+        <v>42397</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L44" s="5"/>
+      <c r="M44" s="18">
+        <f t="shared" si="0"/>
+        <v>39050</v>
+      </c>
+      <c r="N44" s="18">
+        <f t="shared" si="0"/>
+        <v>33215</v>
+      </c>
+      <c r="O44" s="18">
+        <f t="shared" si="0"/>
+        <v>54260</v>
+      </c>
+      <c r="P44" s="18">
+        <f t="shared" si="0"/>
+        <v>142700</v>
+      </c>
+      <c r="Q44" s="18">
+        <f t="shared" si="0"/>
+        <v>97800</v>
+      </c>
+      <c r="R44" s="18"/>
+      <c r="T44" s="30"/>
+      <c r="U44" s="24"/>
+      <c r="V44" s="24"/>
+      <c r="W44" s="24"/>
+      <c r="X44" s="24"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="25"/>
+    </row>
+    <row r="45" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D45" s="10">
+        <v>40.698999999999998</v>
+      </c>
+      <c r="E45" s="19">
+        <v>37.018000000000001</v>
+      </c>
+      <c r="F45" s="10">
+        <v>52.634999999999998</v>
+      </c>
+      <c r="G45" s="11">
+        <v>154.5</v>
+      </c>
+      <c r="H45" s="11">
+        <v>94.9</v>
+      </c>
+      <c r="I45" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="J45" s="13">
+        <v>42397</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L45" s="5"/>
+      <c r="M45" s="18">
+        <f t="shared" si="0"/>
+        <v>40699</v>
+      </c>
+      <c r="N45" s="18">
+        <f t="shared" si="0"/>
+        <v>37018</v>
+      </c>
+      <c r="O45" s="18">
+        <f t="shared" si="0"/>
+        <v>52635</v>
+      </c>
+      <c r="P45" s="18">
+        <f t="shared" si="0"/>
+        <v>154500</v>
+      </c>
+      <c r="Q45" s="18">
+        <f t="shared" si="0"/>
+        <v>94900</v>
+      </c>
+      <c r="R45" s="18"/>
+      <c r="T45" s="30"/>
+      <c r="U45" s="24"/>
+      <c r="V45" s="24"/>
+      <c r="W45" s="24"/>
+      <c r="X45" s="24"/>
+      <c r="Y45" s="24"/>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="24"/>
+      <c r="AB45" s="24"/>
+      <c r="AC45" s="25"/>
+    </row>
+    <row r="46" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46" s="16">
+        <v>2600</v>
+      </c>
+      <c r="D46" s="10">
+        <v>45.381999999999998</v>
+      </c>
+      <c r="E46" s="19">
+        <v>40.313000000000002</v>
+      </c>
+      <c r="F46" s="10">
+        <v>61.804000000000002</v>
+      </c>
+      <c r="G46" s="11">
+        <v>169.9</v>
+      </c>
+      <c r="H46" s="11">
+        <v>111.4</v>
+      </c>
+      <c r="I46" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="J46" s="13">
+        <v>42817</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="18">
+        <f t="shared" si="0"/>
+        <v>45382</v>
+      </c>
+      <c r="N46" s="18">
+        <f t="shared" si="0"/>
+        <v>40313</v>
+      </c>
+      <c r="O46" s="18">
+        <f t="shared" si="0"/>
+        <v>61804</v>
+      </c>
+      <c r="P46" s="18">
+        <f t="shared" si="0"/>
+        <v>169900</v>
+      </c>
+      <c r="Q46" s="18">
+        <f t="shared" si="0"/>
+        <v>111400</v>
+      </c>
+      <c r="R46" s="18"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="24"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="24"/>
+      <c r="X46" s="24"/>
+      <c r="Y46" s="24"/>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="24"/>
+      <c r="AB46" s="24"/>
+      <c r="AC46" s="25"/>
+    </row>
+    <row r="47" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47" s="16">
+        <v>2700</v>
+      </c>
+      <c r="D47" s="10">
+        <v>57.2</v>
+      </c>
+      <c r="E47" s="19">
+        <v>43.731999999999999</v>
+      </c>
+      <c r="F47" s="10">
+        <v>107.95399999999999</v>
+      </c>
+      <c r="G47" s="11">
+        <v>196.6</v>
+      </c>
+      <c r="H47" s="11">
+        <v>194.6</v>
+      </c>
+      <c r="I47" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="J47" s="13">
+        <v>44155</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="18">
+        <f t="shared" si="0"/>
+        <v>57200</v>
+      </c>
+      <c r="N47" s="18">
+        <f t="shared" si="0"/>
+        <v>43732</v>
+      </c>
+      <c r="O47" s="18">
+        <f t="shared" si="0"/>
+        <v>107954</v>
+      </c>
+      <c r="P47" s="18">
+        <f t="shared" si="0"/>
+        <v>196600</v>
+      </c>
+      <c r="Q47" s="18">
+        <f t="shared" si="0"/>
+        <v>194600</v>
+      </c>
+      <c r="R47" s="18"/>
+      <c r="T47" s="30"/>
+      <c r="U47" s="24"/>
+      <c r="V47" s="24"/>
+      <c r="W47" s="24"/>
+      <c r="X47" s="24"/>
+      <c r="Y47" s="24"/>
+      <c r="Z47" s="24"/>
+      <c r="AA47" s="24"/>
+      <c r="AB47" s="24"/>
+      <c r="AC47" s="25"/>
+    </row>
+    <row r="48" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48" s="16">
+        <v>2600</v>
+      </c>
+      <c r="D48" s="10">
+        <v>55.045999999999999</v>
+      </c>
+      <c r="E48" s="19">
+        <v>44.618000000000002</v>
+      </c>
+      <c r="F48" s="10">
+        <v>73.569999999999993</v>
+      </c>
+      <c r="G48" s="11">
+        <v>195.6</v>
+      </c>
+      <c r="H48" s="11">
+        <v>132.6</v>
+      </c>
+      <c r="I48" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="J48" s="13">
+        <v>43355</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L48" s="5"/>
+      <c r="M48" s="18">
+        <f t="shared" si="0"/>
+        <v>55046</v>
+      </c>
+      <c r="N48" s="18">
+        <f t="shared" si="0"/>
+        <v>44618</v>
+      </c>
+      <c r="O48" s="18">
+        <f t="shared" si="0"/>
+        <v>73570</v>
+      </c>
+      <c r="P48" s="18">
+        <f t="shared" si="0"/>
+        <v>195600</v>
+      </c>
+      <c r="Q48" s="18">
+        <f t="shared" si="0"/>
+        <v>132600</v>
+      </c>
+      <c r="R48" s="18"/>
+      <c r="T48" s="30"/>
+      <c r="U48" s="24"/>
+      <c r="V48" s="24"/>
+      <c r="W48" s="24"/>
+      <c r="X48" s="24"/>
+      <c r="Y48" s="24"/>
+      <c r="Z48" s="24"/>
+      <c r="AA48" s="24"/>
+      <c r="AB48" s="24"/>
+      <c r="AC48" s="25"/>
+    </row>
+    <row r="49" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49" s="16">
+        <v>2600</v>
+      </c>
+      <c r="D49" s="10">
+        <v>63.682000000000002</v>
+      </c>
+      <c r="E49" s="19">
+        <v>45.731999999999999</v>
+      </c>
+      <c r="F49" s="10">
+        <v>68.159000000000006</v>
+      </c>
+      <c r="G49" s="11">
+        <v>211.2</v>
+      </c>
+      <c r="H49" s="11">
+        <v>122.9</v>
+      </c>
+      <c r="I49" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" s="13">
+        <v>43146</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="18">
+        <f t="shared" si="0"/>
+        <v>63682</v>
+      </c>
+      <c r="N49" s="18">
+        <f t="shared" si="0"/>
+        <v>45732</v>
+      </c>
+      <c r="O49" s="18">
+        <f t="shared" si="0"/>
+        <v>68159</v>
+      </c>
+      <c r="P49" s="18">
+        <f t="shared" si="0"/>
+        <v>211200</v>
+      </c>
+      <c r="Q49" s="18">
+        <f t="shared" si="0"/>
+        <v>122900</v>
+      </c>
+      <c r="R49" s="18"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="24"/>
+      <c r="V49" s="24"/>
+      <c r="W49" s="24"/>
+      <c r="X49" s="24"/>
+      <c r="Y49" s="24"/>
+      <c r="Z49" s="24"/>
+      <c r="AA49" s="24"/>
+      <c r="AB49" s="24"/>
+      <c r="AC49" s="25"/>
+    </row>
+    <row r="50" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50" s="16">
+        <v>2500</v>
+      </c>
+      <c r="D50" s="10">
+        <v>50.423000000000002</v>
+      </c>
+      <c r="E50" s="19">
+        <v>46.116999999999997</v>
+      </c>
+      <c r="F50" s="10">
+        <v>70.039000000000001</v>
+      </c>
+      <c r="G50" s="11">
+        <v>192</v>
+      </c>
+      <c r="H50" s="11">
+        <v>126.3</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" s="13">
+        <v>43146</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L50" s="5"/>
+      <c r="M50" s="18">
+        <f t="shared" si="0"/>
+        <v>50423</v>
+      </c>
+      <c r="N50" s="18">
+        <f t="shared" si="0"/>
+        <v>46117</v>
+      </c>
+      <c r="O50" s="18">
+        <f t="shared" si="0"/>
+        <v>70039</v>
+      </c>
+      <c r="P50" s="18">
+        <f t="shared" si="0"/>
+        <v>192000</v>
+      </c>
+      <c r="Q50" s="18">
+        <f t="shared" si="0"/>
+        <v>126300</v>
+      </c>
+      <c r="R50" s="18"/>
+      <c r="T50" s="30"/>
+      <c r="U50" s="24"/>
+      <c r="V50" s="24"/>
+      <c r="W50" s="24"/>
+      <c r="X50" s="24"/>
+      <c r="Y50" s="24"/>
+      <c r="Z50" s="24"/>
+      <c r="AA50" s="24"/>
+      <c r="AB50" s="24"/>
+      <c r="AC50" s="25"/>
+    </row>
+    <row r="51" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51">
+        <v>2112</v>
+      </c>
+      <c r="D51" s="10">
+        <v>61.249000000000002</v>
+      </c>
+      <c r="E51" s="19">
+        <v>46.226999999999997</v>
+      </c>
+      <c r="F51" s="10">
+        <v>113.619</v>
+      </c>
+      <c r="G51" s="11">
+        <v>209</v>
+      </c>
+      <c r="H51" s="11">
+        <v>204.9</v>
+      </c>
+      <c r="I51" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="J51" s="14">
+        <v>45298</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L51" s="5"/>
+      <c r="M51" s="18">
+        <f t="shared" si="0"/>
+        <v>61249</v>
+      </c>
+      <c r="N51" s="18">
+        <f t="shared" si="0"/>
+        <v>46227</v>
+      </c>
+      <c r="O51" s="18">
+        <f t="shared" si="0"/>
+        <v>113619</v>
+      </c>
+      <c r="P51" s="18">
+        <f t="shared" si="0"/>
+        <v>209000</v>
+      </c>
+      <c r="Q51" s="18">
+        <f t="shared" si="0"/>
+        <v>204900</v>
+      </c>
+      <c r="R51" s="18"/>
+      <c r="T51" s="30"/>
+      <c r="U51" s="24"/>
+      <c r="V51" s="24"/>
+      <c r="W51" s="24"/>
+      <c r="X51" s="24"/>
+      <c r="Y51" s="24"/>
+      <c r="Z51" s="24"/>
+      <c r="AA51" s="24"/>
+      <c r="AB51" s="24"/>
+      <c r="AC51" s="25"/>
+    </row>
+    <row r="52" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52" s="20">
+        <v>3700</v>
+      </c>
+      <c r="D52" s="10">
+        <v>68.150000000000006</v>
+      </c>
+      <c r="E52" s="19">
+        <v>48.103000000000002</v>
+      </c>
+      <c r="F52" s="10">
+        <v>118.447</v>
+      </c>
+      <c r="G52" s="11">
+        <v>223.80500000000001</v>
+      </c>
+      <c r="H52" s="11">
+        <v>216.554</v>
+      </c>
+      <c r="I52" s="8"/>
+      <c r="J52" s="14">
+        <v>45773</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L52" s="5"/>
+      <c r="M52" s="18">
+        <f t="shared" si="0"/>
+        <v>68150</v>
+      </c>
+      <c r="N52" s="18">
+        <f t="shared" si="0"/>
+        <v>48103</v>
+      </c>
+      <c r="O52" s="18">
+        <f t="shared" si="0"/>
+        <v>118447</v>
+      </c>
+      <c r="P52" s="18">
+        <f t="shared" si="0"/>
+        <v>223805</v>
+      </c>
+      <c r="Q52" s="18">
+        <f t="shared" si="0"/>
+        <v>216554</v>
+      </c>
+      <c r="R52" s="18"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="24"/>
+      <c r="W52" s="24"/>
+      <c r="X52" s="24"/>
+      <c r="Y52" s="24"/>
+      <c r="Z52" s="24"/>
+      <c r="AA52" s="24"/>
+      <c r="AB52" s="24"/>
+      <c r="AC52" s="25"/>
+    </row>
+    <row r="53" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53">
+        <v>2295</v>
+      </c>
+      <c r="D53" s="10">
+        <v>59.665999999999997</v>
+      </c>
+      <c r="E53" s="19">
+        <v>49.441000000000003</v>
+      </c>
+      <c r="F53" s="10">
+        <v>116.922</v>
+      </c>
+      <c r="G53" s="11">
+        <v>214.8</v>
+      </c>
+      <c r="H53" s="11">
+        <v>210.8</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="J53" s="14">
+        <v>45298</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L53" s="5"/>
+      <c r="M53" s="18">
+        <f t="shared" si="0"/>
+        <v>59666</v>
+      </c>
+      <c r="N53" s="18">
+        <f t="shared" si="0"/>
+        <v>49441</v>
+      </c>
+      <c r="O53" s="18">
+        <f t="shared" si="0"/>
+        <v>116922</v>
+      </c>
+      <c r="P53" s="18">
+        <f t="shared" si="0"/>
+        <v>214800</v>
+      </c>
+      <c r="Q53" s="18">
+        <f t="shared" si="0"/>
+        <v>210800</v>
+      </c>
+      <c r="R53" s="18"/>
+      <c r="T53" s="30"/>
+      <c r="U53" s="24"/>
+      <c r="V53" s="24"/>
+      <c r="W53" s="24"/>
+      <c r="X53" s="24"/>
+      <c r="Y53" s="24"/>
+      <c r="Z53" s="24"/>
+      <c r="AA53" s="24"/>
+      <c r="AB53" s="24"/>
+      <c r="AC53" s="25"/>
+    </row>
+    <row r="54" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54">
+        <v>3700</v>
+      </c>
+      <c r="D54" s="10">
+        <v>62.206000000000003</v>
+      </c>
+      <c r="E54" s="19">
+        <v>49.951000000000001</v>
+      </c>
+      <c r="F54" s="10">
+        <v>112.593</v>
+      </c>
+      <c r="G54" s="11">
+        <v>219.9</v>
+      </c>
+      <c r="H54" s="11">
+        <v>203</v>
+      </c>
+      <c r="I54" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="J54" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L54" s="5"/>
+      <c r="M54" s="18">
+        <f t="shared" si="0"/>
+        <v>62206</v>
+      </c>
+      <c r="N54" s="18">
+        <f t="shared" si="0"/>
+        <v>49951</v>
+      </c>
+      <c r="O54" s="18">
+        <f t="shared" si="0"/>
+        <v>112593</v>
+      </c>
+      <c r="P54" s="18">
+        <f t="shared" si="0"/>
+        <v>219900</v>
+      </c>
+      <c r="Q54" s="18">
+        <f t="shared" si="0"/>
+        <v>203000</v>
+      </c>
+      <c r="R54" s="18"/>
+      <c r="T54" s="30"/>
+      <c r="U54" s="24"/>
+      <c r="V54" s="24"/>
+      <c r="W54" s="24"/>
+      <c r="X54" s="24"/>
+      <c r="Y54" s="24"/>
+      <c r="Z54" s="24"/>
+      <c r="AA54" s="24"/>
+      <c r="AB54" s="24"/>
+      <c r="AC54" s="25"/>
+    </row>
+    <row r="55" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55">
+        <v>4160</v>
+      </c>
+      <c r="D55" s="10">
+        <v>77.174000000000007</v>
+      </c>
+      <c r="E55" s="19">
+        <v>56.761000000000003</v>
+      </c>
+      <c r="F55" s="10">
+        <v>138.00299999999999</v>
+      </c>
+      <c r="G55" s="11">
+        <v>259.47000000000003</v>
+      </c>
+      <c r="H55" s="11">
+        <v>248.81200000000001</v>
+      </c>
+      <c r="I55" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="J55" s="14">
+        <v>45211</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L55" s="5"/>
+      <c r="M55" s="18">
+        <f t="shared" si="0"/>
+        <v>77174</v>
+      </c>
+      <c r="N55" s="18">
+        <f t="shared" si="0"/>
+        <v>56761</v>
+      </c>
+      <c r="O55" s="18">
+        <f t="shared" ref="M55:Q58" si="2">F55*1000</f>
+        <v>138003</v>
+      </c>
+      <c r="P55" s="18">
+        <f t="shared" si="2"/>
+        <v>259470.00000000003</v>
+      </c>
+      <c r="Q55" s="18">
+        <f t="shared" si="2"/>
+        <v>248812</v>
+      </c>
+      <c r="R55" s="18"/>
+      <c r="S55" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="T55" s="32"/>
+      <c r="U55" s="24"/>
+      <c r="V55" s="24"/>
+      <c r="W55" s="24"/>
+      <c r="X55" s="24"/>
+      <c r="Y55" s="24"/>
+      <c r="Z55" s="24"/>
+      <c r="AA55" s="24"/>
+      <c r="AB55" s="24"/>
+      <c r="AC55" s="25"/>
+    </row>
+    <row r="56" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="15">
+        <v>3090</v>
+      </c>
+      <c r="D56" s="10">
+        <v>63.435000000000002</v>
+      </c>
+      <c r="E56" s="19">
+        <v>66.734999999999999</v>
+      </c>
+      <c r="F56" s="10">
+        <v>143.465</v>
+      </c>
+      <c r="G56" s="11">
+        <v>261.7</v>
+      </c>
+      <c r="H56" s="11">
+        <v>258.7</v>
+      </c>
+      <c r="I56" s="8"/>
+      <c r="J56" s="14">
+        <v>46116</v>
+      </c>
+      <c r="K56" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="L56" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="M56" s="18">
+        <f t="shared" ref="M56:N56" si="3">D56*1000</f>
+        <v>63435</v>
+      </c>
+      <c r="N56" s="18">
+        <f t="shared" si="3"/>
+        <v>66735</v>
+      </c>
+      <c r="O56" s="18">
+        <f t="shared" ref="O56" si="4">F56*1000</f>
+        <v>143465</v>
+      </c>
+      <c r="P56" s="18">
+        <f t="shared" ref="P56" si="5">G56*1000</f>
+        <v>261700</v>
+      </c>
+      <c r="Q56" s="18">
+        <f t="shared" ref="Q56" si="6">H56*1000</f>
+        <v>258700</v>
+      </c>
+      <c r="R56" s="18"/>
+      <c r="S56" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="T56" s="31"/>
+      <c r="U56" s="24"/>
+      <c r="V56" s="24"/>
+      <c r="W56" s="24"/>
+      <c r="X56" s="24"/>
+      <c r="Y56" s="24"/>
+      <c r="Z56" s="24"/>
+      <c r="AA56" s="24"/>
+      <c r="AB56" s="24"/>
+      <c r="AC56" s="25"/>
+    </row>
+    <row r="57" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C57" s="16">
+        <v>3200</v>
+      </c>
+      <c r="D57" s="10">
+        <v>66.938999999999993</v>
+      </c>
+      <c r="E57" s="19">
+        <v>79.733000000000004</v>
+      </c>
+      <c r="F57" s="10">
+        <v>216.304</v>
+      </c>
+      <c r="G57" s="11">
+        <v>296.39999999999998</v>
+      </c>
+      <c r="H57" s="11">
+        <v>389.9</v>
+      </c>
+      <c r="I57" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="14">
+        <v>45561</v>
+      </c>
+      <c r="K57" s="33" t="s">
+        <v>230</v>
+      </c>
+      <c r="L57" s="5"/>
+      <c r="M57" s="18">
+        <f t="shared" si="2"/>
+        <v>66939</v>
+      </c>
+      <c r="N57" s="18">
+        <f t="shared" si="2"/>
+        <v>79733</v>
+      </c>
+      <c r="O57" s="18">
+        <f t="shared" si="2"/>
+        <v>216304</v>
+      </c>
+      <c r="P57" s="18">
+        <f t="shared" si="2"/>
+        <v>296400</v>
+      </c>
+      <c r="Q57" s="18">
+        <f t="shared" si="2"/>
+        <v>389900</v>
+      </c>
+      <c r="R57" s="18"/>
+      <c r="S57" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="T57" s="31"/>
+      <c r="U57" s="23"/>
+      <c r="V57" s="24"/>
+      <c r="W57" s="24"/>
+      <c r="X57" s="23"/>
+      <c r="Y57" s="24"/>
+      <c r="Z57" s="24"/>
+      <c r="AA57" s="24"/>
+      <c r="AB57" s="24"/>
+      <c r="AC57" s="23"/>
+    </row>
+    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58">
+        <v>4700</v>
+      </c>
+      <c r="D58" s="10">
+        <v>104.52500000000001</v>
+      </c>
+      <c r="E58" s="19">
+        <v>85.01</v>
+      </c>
+      <c r="F58" s="10">
+        <v>264.86900000000003</v>
+      </c>
+      <c r="G58" s="11">
+        <v>372.2</v>
+      </c>
+      <c r="H58" s="11">
+        <v>377.5</v>
+      </c>
+      <c r="I58" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J58" s="14">
+        <v>45561</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L58" s="5"/>
+      <c r="M58" s="18">
+        <f t="shared" si="2"/>
+        <v>104525</v>
+      </c>
+      <c r="N58" s="18">
+        <f t="shared" si="2"/>
+        <v>85010</v>
+      </c>
+      <c r="O58" s="18">
+        <f t="shared" si="2"/>
+        <v>264869</v>
+      </c>
+      <c r="P58" s="18">
+        <f t="shared" si="2"/>
+        <v>372200</v>
+      </c>
+      <c r="Q58" s="18">
+        <f t="shared" si="2"/>
+        <v>377500</v>
+      </c>
+      <c r="R58" s="18"/>
+      <c r="S58" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="T58" s="31"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="C59" s="15">
+        <v>3210</v>
+      </c>
+      <c r="D59" s="10">
+        <v>83.274000000000001</v>
+      </c>
+      <c r="E59" s="19">
+        <v>86</v>
+      </c>
+      <c r="F59" s="10">
+        <v>163.31299999999999</v>
+      </c>
+      <c r="G59" s="11">
+        <v>339.9</v>
+      </c>
+      <c r="H59" s="11">
+        <v>296.2</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="13">
+        <v>46116</v>
+      </c>
+      <c r="K59" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="L59" t="s">
+        <v>252</v>
+      </c>
+      <c r="M59" s="18">
+        <f t="shared" ref="M59" si="7">D59*1000</f>
+        <v>83274</v>
+      </c>
+      <c r="N59" s="18">
+        <f t="shared" ref="N59" si="8">E59*1000</f>
+        <v>86000</v>
+      </c>
+      <c r="O59" s="18">
+        <f t="shared" ref="O59" si="9">F59*1000</f>
+        <v>163313</v>
+      </c>
+      <c r="P59" s="18">
+        <f t="shared" ref="P59" si="10">G59*1000</f>
+        <v>339900</v>
+      </c>
+      <c r="Q59" s="18">
+        <f t="shared" ref="Q59" si="11">H59*1000</f>
+        <v>296200</v>
+      </c>
+      <c r="S59" s="38" t="s">
+        <v>257</v>
+      </c>
+      <c r="T59" s="31"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="F60" s="10"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+    </row>
+    <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="J61" s="7"/>
+      <c r="K61" s="7"/>
+    </row>
+    <row r="62" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="J62" s="7"/>
+      <c r="K62" s="7"/>
+    </row>
+    <row r="63" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="J63" s="7"/>
+      <c r="K63" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67877F8F-8163-43CC-9F81-802504486149}">
   <dimension ref="A1:R61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -4047,13 +8234,13 @@
       <c r="R50" s="18"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="24" t="s">
+      <c r="A51" s="20" t="s">
         <v>236</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="C51" s="24">
+      <c r="C51" s="20">
         <v>3700</v>
       </c>
       <c r="D51" s="10">
@@ -4419,10 +8606,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5A198D7-6D1E-4BFD-BCE5-F3668492731D}">
   <dimension ref="A1:Q58"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -7268,10 +11455,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{142FA056-705A-034A-8892-EB09DFE76F3E}">
   <dimension ref="A1:K53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -8835,10 +13022,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -10364,10 +14551,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K51"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.85546875" bestFit="1" customWidth="1"/>
@@ -11855,10 +16042,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G49"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.140625" customWidth="1"/>
     <col min="2" max="2" width="11.42578125" customWidth="1"/>
@@ -11870,7 +16057,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -11882,10 +16069,10 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="27" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -11893,7 +16080,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
+      <c r="A2" s="26"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -11903,8 +16090,8 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
@@ -12051,22 +16238,22 @@
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="22">
+      <c r="B9" s="28">
         <v>2.7480000000000002</v>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="28">
         <v>3.282</v>
       </c>
-      <c r="D9" s="22">
+      <c r="D9" s="28">
         <v>3.7109999999999999</v>
       </c>
-      <c r="E9" s="23">
+      <c r="E9" s="29">
         <v>12.8</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="29">
         <v>6.69</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="28" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12074,33 +16261,33 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="22"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="22">
+      <c r="B11" s="28">
         <v>3.665</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="28">
         <v>5.46</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="28">
         <v>4.6849999999999996</v>
       </c>
-      <c r="E11" s="23">
+      <c r="E11" s="29">
         <v>18.399999999999999</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="29">
         <v>8.4499999999999993</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="28" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12108,12 +16295,12 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="22"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -12257,22 +16444,22 @@
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="22">
+      <c r="B19" s="28">
         <v>4.5910000000000002</v>
       </c>
-      <c r="C19" s="22">
+      <c r="C19" s="28">
         <v>9.8949999999999996</v>
       </c>
-      <c r="D19" s="22">
+      <c r="D19" s="28">
         <v>9.0860000000000003</v>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="29">
         <v>28.5</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="29">
         <v>16.399999999999999</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="28" t="s">
         <v>10</v>
       </c>
     </row>
@@ -12280,12 +16467,12 @@
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
-      <c r="D20" s="22"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="22"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="28"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -12909,7 +17096,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="20" t="s">
+      <c r="A48" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -12921,10 +17108,10 @@
       <c r="D48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="E48" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="27" t="s">
         <v>6</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -12932,7 +17119,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="20"/>
+      <c r="A49" s="26"/>
       <c r="B49" s="1" t="s">
         <v>2</v>
       </c>
@@ -12942,8 +17129,8 @@
       <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="21"/>
-      <c r="F49" s="21"/>
+      <c r="E49" s="27"/>
+      <c r="F49" s="27"/>
       <c r="G49" s="1" t="s">
         <v>8</v>
       </c>
@@ -12983,4 +17170,2997 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{515FCFF6-B255-4D72-A70A-82EF1E52ACB5}">
+  <dimension ref="A1:S59"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="5" max="5" width="7.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="7" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="27.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>83</v>
+      </c>
+      <c r="J1" t="s">
+        <v>181</v>
+      </c>
+      <c r="K1" t="s">
+        <v>238</v>
+      </c>
+      <c r="L1" t="s">
+        <v>240</v>
+      </c>
+      <c r="M1" t="s">
+        <v>241</v>
+      </c>
+      <c r="N1" t="s">
+        <v>242</v>
+      </c>
+      <c r="O1" t="s">
+        <v>243</v>
+      </c>
+      <c r="P1" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2">
+        <v>667</v>
+      </c>
+      <c r="D2">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="E2">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="F2">
+        <v>0.126</v>
+      </c>
+      <c r="G2">
+        <v>3</v>
+      </c>
+      <c r="H2">
+        <v>0.2</v>
+      </c>
+      <c r="I2" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="13">
+        <v>40892</v>
+      </c>
+      <c r="K2" t="s">
+        <v>228</v>
+      </c>
+      <c r="L2">
+        <v>541</v>
+      </c>
+      <c r="M2">
+        <v>959</v>
+      </c>
+      <c r="N2">
+        <v>126</v>
+      </c>
+      <c r="O2">
+        <v>3000</v>
+      </c>
+      <c r="P2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3">
+        <v>233</v>
+      </c>
+      <c r="D3">
+        <v>1.238</v>
+      </c>
+      <c r="E3">
+        <v>1.33</v>
+      </c>
+      <c r="F3">
+        <v>2.4089999999999998</v>
+      </c>
+      <c r="G3">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="H3">
+        <v>4.3</v>
+      </c>
+      <c r="I3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="13">
+        <v>41122</v>
+      </c>
+      <c r="K3" t="s">
+        <v>225</v>
+      </c>
+      <c r="L3">
+        <v>1238</v>
+      </c>
+      <c r="M3">
+        <v>1330</v>
+      </c>
+      <c r="N3">
+        <v>2409</v>
+      </c>
+      <c r="O3">
+        <v>5100</v>
+      </c>
+      <c r="P3">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4">
+        <v>600</v>
+      </c>
+      <c r="D4">
+        <v>1.04</v>
+      </c>
+      <c r="E4">
+        <v>1.6850000000000001</v>
+      </c>
+      <c r="F4">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G4">
+        <v>5.5</v>
+      </c>
+      <c r="H4">
+        <v>0.4</v>
+      </c>
+      <c r="I4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J4" s="13">
+        <v>41487</v>
+      </c>
+      <c r="K4" t="s">
+        <v>228</v>
+      </c>
+      <c r="L4">
+        <v>1040</v>
+      </c>
+      <c r="M4">
+        <v>1685</v>
+      </c>
+      <c r="N4">
+        <v>228</v>
+      </c>
+      <c r="O4">
+        <v>5500</v>
+      </c>
+      <c r="P4">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5">
+        <v>400</v>
+      </c>
+      <c r="D5">
+        <v>1.379</v>
+      </c>
+      <c r="E5">
+        <v>1.712</v>
+      </c>
+      <c r="F5">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G5">
+        <v>6.3</v>
+      </c>
+      <c r="H5">
+        <v>0.1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" s="13">
+        <v>41489</v>
+      </c>
+      <c r="K5" t="s">
+        <v>229</v>
+      </c>
+      <c r="L5">
+        <v>1379</v>
+      </c>
+      <c r="M5">
+        <v>1712</v>
+      </c>
+      <c r="N5">
+        <v>35</v>
+      </c>
+      <c r="O5">
+        <v>6300</v>
+      </c>
+      <c r="P5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6">
+        <v>667</v>
+      </c>
+      <c r="D6">
+        <v>1.024</v>
+      </c>
+      <c r="E6">
+        <v>1.821</v>
+      </c>
+      <c r="F6">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="G6">
+        <v>5.7</v>
+      </c>
+      <c r="H6">
+        <v>0.4</v>
+      </c>
+      <c r="I6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J6" s="13">
+        <v>41122</v>
+      </c>
+      <c r="K6" t="s">
+        <v>228</v>
+      </c>
+      <c r="L6">
+        <v>1024</v>
+      </c>
+      <c r="M6">
+        <v>1821</v>
+      </c>
+      <c r="N6">
+        <v>238</v>
+      </c>
+      <c r="O6">
+        <v>5700</v>
+      </c>
+      <c r="P6">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7">
+        <v>700</v>
+      </c>
+      <c r="D7">
+        <v>2.456</v>
+      </c>
+      <c r="E7">
+        <v>3.1059999999999999</v>
+      </c>
+      <c r="F7">
+        <v>2.0289999999999999</v>
+      </c>
+      <c r="G7">
+        <v>11.3</v>
+      </c>
+      <c r="H7">
+        <v>3.7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K7" t="s">
+        <v>226</v>
+      </c>
+      <c r="L7">
+        <v>2456</v>
+      </c>
+      <c r="M7">
+        <v>3106</v>
+      </c>
+      <c r="N7">
+        <v>2029</v>
+      </c>
+      <c r="O7">
+        <v>11300</v>
+      </c>
+      <c r="P7">
+        <v>3660</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8">
+        <v>800</v>
+      </c>
+      <c r="D8">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="E8">
+        <v>3.282</v>
+      </c>
+      <c r="F8">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="G8">
+        <v>12.8</v>
+      </c>
+      <c r="H8">
+        <v>6.7</v>
+      </c>
+      <c r="I8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J8" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K8" t="s">
+        <v>227</v>
+      </c>
+      <c r="L8">
+        <v>2748</v>
+      </c>
+      <c r="M8">
+        <v>3282</v>
+      </c>
+      <c r="N8">
+        <v>3711</v>
+      </c>
+      <c r="O8">
+        <v>12800</v>
+      </c>
+      <c r="P8">
+        <v>6690</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C9">
+        <v>933</v>
+      </c>
+      <c r="D9">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="E9">
+        <v>5.1639999999999997</v>
+      </c>
+      <c r="F9">
+        <v>8.9160000000000004</v>
+      </c>
+      <c r="G9">
+        <v>19.899999999999999</v>
+      </c>
+      <c r="H9">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K9" t="s">
+        <v>225</v>
+      </c>
+      <c r="L9">
+        <v>4709</v>
+      </c>
+      <c r="M9">
+        <v>5164</v>
+      </c>
+      <c r="N9">
+        <v>8916</v>
+      </c>
+      <c r="O9">
+        <v>19900</v>
+      </c>
+      <c r="P9">
+        <v>16100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>94</v>
+      </c>
+      <c r="B10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C10">
+        <v>1008</v>
+      </c>
+      <c r="D10">
+        <v>3.665</v>
+      </c>
+      <c r="E10">
+        <v>5.46</v>
+      </c>
+      <c r="F10">
+        <v>4.6849999999999996</v>
+      </c>
+      <c r="G10">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="H10">
+        <v>8.5</v>
+      </c>
+      <c r="I10" t="s">
+        <v>10</v>
+      </c>
+      <c r="J10" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K10" t="s">
+        <v>227</v>
+      </c>
+      <c r="L10">
+        <v>3665</v>
+      </c>
+      <c r="M10">
+        <v>5460</v>
+      </c>
+      <c r="N10">
+        <v>4685</v>
+      </c>
+      <c r="O10">
+        <v>18400</v>
+      </c>
+      <c r="P10">
+        <v>8450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11">
+        <v>1000</v>
+      </c>
+      <c r="D11">
+        <v>4.665</v>
+      </c>
+      <c r="E11">
+        <v>6.4809999999999999</v>
+      </c>
+      <c r="F11">
+        <v>5.0590000000000002</v>
+      </c>
+      <c r="G11">
+        <v>22.6</v>
+      </c>
+      <c r="H11">
+        <v>9.1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J11" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K11" t="s">
+        <v>227</v>
+      </c>
+      <c r="L11">
+        <v>4665</v>
+      </c>
+      <c r="M11">
+        <v>6481</v>
+      </c>
+      <c r="N11">
+        <v>5059</v>
+      </c>
+      <c r="O11">
+        <v>22600</v>
+      </c>
+      <c r="P11">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C12">
+        <v>988</v>
+      </c>
+      <c r="D12">
+        <v>5.7990000000000004</v>
+      </c>
+      <c r="E12">
+        <v>6.7169999999999996</v>
+      </c>
+      <c r="F12">
+        <v>8.0549999999999997</v>
+      </c>
+      <c r="G12">
+        <v>25.3</v>
+      </c>
+      <c r="H12">
+        <v>14.5</v>
+      </c>
+      <c r="I12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" s="13">
+        <v>42217</v>
+      </c>
+      <c r="K12" t="s">
+        <v>224</v>
+      </c>
+      <c r="L12">
+        <v>5799</v>
+      </c>
+      <c r="M12">
+        <v>6717</v>
+      </c>
+      <c r="N12">
+        <v>8055</v>
+      </c>
+      <c r="O12">
+        <v>25300</v>
+      </c>
+      <c r="P12">
+        <v>14500</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C13">
+        <v>1200</v>
+      </c>
+      <c r="D13">
+        <v>6.21</v>
+      </c>
+      <c r="E13">
+        <v>7.0469999999999997</v>
+      </c>
+      <c r="F13">
+        <v>12.384</v>
+      </c>
+      <c r="G13">
+        <v>26.4</v>
+      </c>
+      <c r="H13">
+        <v>22</v>
+      </c>
+      <c r="I13" t="s">
+        <v>26</v>
+      </c>
+      <c r="J13" s="13">
+        <v>41797</v>
+      </c>
+      <c r="K13" t="s">
+        <v>225</v>
+      </c>
+      <c r="L13">
+        <v>6210</v>
+      </c>
+      <c r="M13">
+        <v>7047</v>
+      </c>
+      <c r="N13">
+        <v>12384</v>
+      </c>
+      <c r="O13">
+        <v>26400</v>
+      </c>
+      <c r="P13">
+        <v>22000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>153</v>
+      </c>
+      <c r="B14" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14">
+        <v>1666</v>
+      </c>
+      <c r="D14">
+        <v>7.2430000000000003</v>
+      </c>
+      <c r="E14">
+        <v>7.109</v>
+      </c>
+      <c r="F14">
+        <v>7.351</v>
+      </c>
+      <c r="G14">
+        <v>28.6</v>
+      </c>
+      <c r="H14">
+        <v>12.8</v>
+      </c>
+      <c r="I14" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="13">
+        <v>40269</v>
+      </c>
+      <c r="K14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14">
+        <v>7243</v>
+      </c>
+      <c r="M14">
+        <v>7109</v>
+      </c>
+      <c r="N14">
+        <v>7351</v>
+      </c>
+      <c r="O14">
+        <v>28600</v>
+      </c>
+      <c r="P14">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B15" t="s">
+        <v>102</v>
+      </c>
+      <c r="C15">
+        <v>2000</v>
+      </c>
+      <c r="D15">
+        <v>9.3940000000000001</v>
+      </c>
+      <c r="E15">
+        <v>7.5289999999999999</v>
+      </c>
+      <c r="F15">
+        <v>13.164</v>
+      </c>
+      <c r="G15">
+        <v>33.200000000000003</v>
+      </c>
+      <c r="H15">
+        <v>23.7</v>
+      </c>
+      <c r="I15" t="s">
+        <v>35</v>
+      </c>
+      <c r="J15" s="13">
+        <v>40017</v>
+      </c>
+      <c r="K15" t="s">
+        <v>225</v>
+      </c>
+      <c r="L15">
+        <v>9394</v>
+      </c>
+      <c r="M15">
+        <v>7529</v>
+      </c>
+      <c r="N15">
+        <v>13164</v>
+      </c>
+      <c r="O15">
+        <v>33200</v>
+      </c>
+      <c r="P15">
+        <v>23700</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>149</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16">
+        <v>1600</v>
+      </c>
+      <c r="D16">
+        <v>7.7519999999999998</v>
+      </c>
+      <c r="E16">
+        <v>7.5789999999999997</v>
+      </c>
+      <c r="F16">
+        <v>7.0679999999999996</v>
+      </c>
+      <c r="G16">
+        <v>30.6</v>
+      </c>
+      <c r="H16">
+        <v>12.8</v>
+      </c>
+      <c r="I16" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="13">
+        <v>40026</v>
+      </c>
+      <c r="K16" t="s">
+        <v>225</v>
+      </c>
+      <c r="L16">
+        <v>7752</v>
+      </c>
+      <c r="M16">
+        <v>7579</v>
+      </c>
+      <c r="N16">
+        <v>7068</v>
+      </c>
+      <c r="O16">
+        <v>30600</v>
+      </c>
+      <c r="P16">
+        <v>12800</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>155</v>
+      </c>
+      <c r="B17" t="s">
+        <v>101</v>
+      </c>
+      <c r="C17">
+        <v>1666</v>
+      </c>
+      <c r="D17">
+        <v>9.3859999999999992</v>
+      </c>
+      <c r="E17">
+        <v>8.39</v>
+      </c>
+      <c r="F17">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="G17">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="H17">
+        <v>13.2</v>
+      </c>
+      <c r="I17" t="s">
+        <v>33</v>
+      </c>
+      <c r="J17" s="13">
+        <v>41496</v>
+      </c>
+      <c r="K17" t="s">
+        <v>223</v>
+      </c>
+      <c r="L17">
+        <v>9386</v>
+      </c>
+      <c r="M17">
+        <v>8390</v>
+      </c>
+      <c r="N17">
+        <v>7313</v>
+      </c>
+      <c r="O17">
+        <v>35300</v>
+      </c>
+      <c r="P17">
+        <v>13200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18">
+        <v>1200</v>
+      </c>
+      <c r="D18">
+        <v>6.78</v>
+      </c>
+      <c r="E18">
+        <v>9.5239999999999991</v>
+      </c>
+      <c r="F18">
+        <v>9.1739999999999995</v>
+      </c>
+      <c r="G18">
+        <v>33</v>
+      </c>
+      <c r="H18">
+        <v>16.5</v>
+      </c>
+      <c r="I18" t="s">
+        <v>10</v>
+      </c>
+      <c r="J18" s="13">
+        <v>45298</v>
+      </c>
+      <c r="K18" t="s">
+        <v>224</v>
+      </c>
+      <c r="L18">
+        <v>6780</v>
+      </c>
+      <c r="M18">
+        <v>9524</v>
+      </c>
+      <c r="N18">
+        <v>9174</v>
+      </c>
+      <c r="O18">
+        <v>33000</v>
+      </c>
+      <c r="P18">
+        <v>16500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19">
+        <v>1512</v>
+      </c>
+      <c r="D19">
+        <v>4.5910000000000002</v>
+      </c>
+      <c r="E19">
+        <v>9.8949999999999996</v>
+      </c>
+      <c r="F19">
+        <v>9.0860000000000003</v>
+      </c>
+      <c r="G19">
+        <v>28.5</v>
+      </c>
+      <c r="H19">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="I19" t="s">
+        <v>10</v>
+      </c>
+      <c r="J19" s="13">
+        <v>42031</v>
+      </c>
+      <c r="K19" t="s">
+        <v>227</v>
+      </c>
+      <c r="L19">
+        <v>4591</v>
+      </c>
+      <c r="M19">
+        <v>9895</v>
+      </c>
+      <c r="N19">
+        <v>9086</v>
+      </c>
+      <c r="O19">
+        <v>28500</v>
+      </c>
+      <c r="P19">
+        <v>16400</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>182</v>
+      </c>
+      <c r="B20" t="s">
+        <v>183</v>
+      </c>
+      <c r="C20">
+        <v>1200</v>
+      </c>
+      <c r="D20">
+        <v>8.68</v>
+      </c>
+      <c r="E20">
+        <v>10.948</v>
+      </c>
+      <c r="F20">
+        <v>10.154999999999999</v>
+      </c>
+      <c r="G20">
+        <v>39.700000000000003</v>
+      </c>
+      <c r="H20">
+        <v>18.3</v>
+      </c>
+      <c r="I20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="13">
+        <v>45319</v>
+      </c>
+      <c r="K20" t="s">
+        <v>224</v>
+      </c>
+      <c r="L20">
+        <v>8680</v>
+      </c>
+      <c r="M20">
+        <v>10948</v>
+      </c>
+      <c r="N20">
+        <v>10155</v>
+      </c>
+      <c r="O20">
+        <v>39718</v>
+      </c>
+      <c r="P20">
+        <v>18310</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+      <c r="B21" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21">
+        <v>1800</v>
+      </c>
+      <c r="D21">
+        <v>11.269</v>
+      </c>
+      <c r="E21">
+        <v>11.927</v>
+      </c>
+      <c r="F21">
+        <v>20.516999999999999</v>
+      </c>
+      <c r="G21">
+        <v>46.6</v>
+      </c>
+      <c r="H21">
+        <v>37</v>
+      </c>
+      <c r="I21" t="s">
+        <v>187</v>
+      </c>
+      <c r="J21" s="13">
+        <v>40672</v>
+      </c>
+      <c r="K21" t="s">
+        <v>223</v>
+      </c>
+      <c r="L21">
+        <v>11269</v>
+      </c>
+      <c r="M21">
+        <v>11927</v>
+      </c>
+      <c r="N21">
+        <v>20517</v>
+      </c>
+      <c r="O21">
+        <v>46600</v>
+      </c>
+      <c r="P21">
+        <v>37000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>104</v>
+      </c>
+      <c r="C22">
+        <v>2000</v>
+      </c>
+      <c r="D22">
+        <v>12.138</v>
+      </c>
+      <c r="E22">
+        <v>12.568</v>
+      </c>
+      <c r="F22">
+        <v>21.143999999999998</v>
+      </c>
+      <c r="G22">
+        <v>49.6</v>
+      </c>
+      <c r="H22">
+        <v>38.1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>188</v>
+      </c>
+      <c r="J22" s="13">
+        <v>39919</v>
+      </c>
+      <c r="K22" t="s">
+        <v>225</v>
+      </c>
+      <c r="L22">
+        <v>12138</v>
+      </c>
+      <c r="M22">
+        <v>12568</v>
+      </c>
+      <c r="N22">
+        <v>21144</v>
+      </c>
+      <c r="O22">
+        <v>49600</v>
+      </c>
+      <c r="P22">
+        <v>38100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>158</v>
+      </c>
+      <c r="B23" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23">
+        <v>1860</v>
+      </c>
+      <c r="D23">
+        <v>18.433</v>
+      </c>
+      <c r="E23">
+        <v>15.15</v>
+      </c>
+      <c r="F23">
+        <v>16.635999999999999</v>
+      </c>
+      <c r="G23">
+        <v>66</v>
+      </c>
+      <c r="H23">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>189</v>
+      </c>
+      <c r="J23" s="13">
+        <v>41788</v>
+      </c>
+      <c r="K23" t="s">
+        <v>223</v>
+      </c>
+      <c r="L23">
+        <v>18433</v>
+      </c>
+      <c r="M23">
+        <v>15150</v>
+      </c>
+      <c r="N23">
+        <v>16636</v>
+      </c>
+      <c r="O23">
+        <v>66000</v>
+      </c>
+      <c r="P23">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>231</v>
+      </c>
+      <c r="B24" t="s">
+        <v>232</v>
+      </c>
+      <c r="C24">
+        <v>1400</v>
+      </c>
+      <c r="D24">
+        <v>14.398999999999999</v>
+      </c>
+      <c r="E24">
+        <v>15.946999999999999</v>
+      </c>
+      <c r="F24">
+        <v>17.788</v>
+      </c>
+      <c r="G24">
+        <v>61.2</v>
+      </c>
+      <c r="H24">
+        <v>32.1</v>
+      </c>
+      <c r="J24" s="13">
+        <v>45772</v>
+      </c>
+      <c r="K24" t="s">
+        <v>224</v>
+      </c>
+      <c r="L24">
+        <v>14399</v>
+      </c>
+      <c r="M24">
+        <v>15947</v>
+      </c>
+      <c r="N24">
+        <v>17788</v>
+      </c>
+      <c r="O24">
+        <v>61171</v>
+      </c>
+      <c r="P24">
+        <v>32072</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>160</v>
+      </c>
+      <c r="C25">
+        <v>1800</v>
+      </c>
+      <c r="D25">
+        <v>13.595000000000001</v>
+      </c>
+      <c r="E25">
+        <v>16.120999999999999</v>
+      </c>
+      <c r="F25">
+        <v>19.565999999999999</v>
+      </c>
+      <c r="G25">
+        <v>59.9</v>
+      </c>
+      <c r="H25">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="I25" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" s="13">
+        <v>40672</v>
+      </c>
+      <c r="K25" t="s">
+        <v>223</v>
+      </c>
+      <c r="L25">
+        <v>13595</v>
+      </c>
+      <c r="M25">
+        <v>16121</v>
+      </c>
+      <c r="N25">
+        <v>19566</v>
+      </c>
+      <c r="O25">
+        <v>59900</v>
+      </c>
+      <c r="P25">
+        <v>35300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26">
+        <v>1580</v>
+      </c>
+      <c r="D26">
+        <v>19.981000000000002</v>
+      </c>
+      <c r="E26">
+        <v>16.207000000000001</v>
+      </c>
+      <c r="F26">
+        <v>18.001000000000001</v>
+      </c>
+      <c r="G26">
+        <v>71</v>
+      </c>
+      <c r="H26">
+        <v>32.5</v>
+      </c>
+      <c r="I26" t="s">
+        <v>191</v>
+      </c>
+      <c r="J26" s="13">
+        <v>41851</v>
+      </c>
+      <c r="K26" t="s">
+        <v>223</v>
+      </c>
+      <c r="L26">
+        <v>19981</v>
+      </c>
+      <c r="M26">
+        <v>16207</v>
+      </c>
+      <c r="N26">
+        <v>18001</v>
+      </c>
+      <c r="O26">
+        <v>71000</v>
+      </c>
+      <c r="P26">
+        <v>32500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" t="s">
+        <v>122</v>
+      </c>
+      <c r="C27">
+        <v>1299</v>
+      </c>
+      <c r="D27">
+        <v>19.050999999999998</v>
+      </c>
+      <c r="E27">
+        <v>17.286000000000001</v>
+      </c>
+      <c r="F27">
+        <v>25.289000000000001</v>
+      </c>
+      <c r="G27">
+        <v>72.2</v>
+      </c>
+      <c r="H27">
+        <v>45.6</v>
+      </c>
+      <c r="I27" t="s">
+        <v>10</v>
+      </c>
+      <c r="J27" s="13">
+        <v>41861</v>
+      </c>
+      <c r="K27" t="s">
+        <v>223</v>
+      </c>
+      <c r="L27">
+        <v>19051</v>
+      </c>
+      <c r="M27">
+        <v>17286</v>
+      </c>
+      <c r="N27">
+        <v>25289</v>
+      </c>
+      <c r="O27">
+        <v>72200</v>
+      </c>
+      <c r="P27">
+        <v>45600</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>110</v>
+      </c>
+      <c r="C28">
+        <v>2527</v>
+      </c>
+      <c r="D28">
+        <v>28.488</v>
+      </c>
+      <c r="E28">
+        <v>17.780999999999999</v>
+      </c>
+      <c r="F28">
+        <v>36.673000000000002</v>
+      </c>
+      <c r="G28">
+        <v>87.2</v>
+      </c>
+      <c r="H28">
+        <v>66.099999999999994</v>
+      </c>
+      <c r="I28" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" s="13">
+        <v>41457</v>
+      </c>
+      <c r="K28" t="s">
+        <v>223</v>
+      </c>
+      <c r="L28">
+        <v>28488</v>
+      </c>
+      <c r="M28">
+        <v>17781</v>
+      </c>
+      <c r="N28">
+        <v>36673</v>
+      </c>
+      <c r="O28">
+        <v>87200</v>
+      </c>
+      <c r="P28">
+        <v>66100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>113</v>
+      </c>
+      <c r="B29" t="s">
+        <v>123</v>
+      </c>
+      <c r="C29">
+        <v>1600</v>
+      </c>
+      <c r="D29">
+        <v>23.695</v>
+      </c>
+      <c r="E29">
+        <v>17.817</v>
+      </c>
+      <c r="F29">
+        <v>25.515999999999998</v>
+      </c>
+      <c r="G29">
+        <v>80.7</v>
+      </c>
+      <c r="H29">
+        <v>46</v>
+      </c>
+      <c r="I29" t="s">
+        <v>210</v>
+      </c>
+      <c r="J29" s="13">
+        <v>44089</v>
+      </c>
+      <c r="K29" t="s">
+        <v>223</v>
+      </c>
+      <c r="L29">
+        <v>23695</v>
+      </c>
+      <c r="M29">
+        <v>17817</v>
+      </c>
+      <c r="N29">
+        <v>25516</v>
+      </c>
+      <c r="O29">
+        <v>80700</v>
+      </c>
+      <c r="P29">
+        <v>46000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>108</v>
+      </c>
+      <c r="B30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30">
+        <v>1400</v>
+      </c>
+      <c r="D30">
+        <v>18.776</v>
+      </c>
+      <c r="E30">
+        <v>17.878</v>
+      </c>
+      <c r="F30">
+        <v>29.106000000000002</v>
+      </c>
+      <c r="G30">
+        <v>73.2</v>
+      </c>
+      <c r="H30">
+        <v>52.5</v>
+      </c>
+      <c r="I30" t="s">
+        <v>10</v>
+      </c>
+      <c r="J30" s="13">
+        <v>43641</v>
+      </c>
+      <c r="K30" t="s">
+        <v>223</v>
+      </c>
+      <c r="L30">
+        <v>18776</v>
+      </c>
+      <c r="M30">
+        <v>17878</v>
+      </c>
+      <c r="N30">
+        <v>29106</v>
+      </c>
+      <c r="O30">
+        <v>73200</v>
+      </c>
+      <c r="P30">
+        <v>52500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>212</v>
+      </c>
+      <c r="B31" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31">
+        <v>1500</v>
+      </c>
+      <c r="D31">
+        <v>15.319000000000001</v>
+      </c>
+      <c r="E31">
+        <v>18.061</v>
+      </c>
+      <c r="F31">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="G31">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="H31">
+        <v>62.4</v>
+      </c>
+      <c r="I31" t="s">
+        <v>10</v>
+      </c>
+      <c r="J31" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K31" t="s">
+        <v>224</v>
+      </c>
+      <c r="L31">
+        <v>15319</v>
+      </c>
+      <c r="M31">
+        <v>18061</v>
+      </c>
+      <c r="N31">
+        <v>34620</v>
+      </c>
+      <c r="O31">
+        <v>67400</v>
+      </c>
+      <c r="P31">
+        <v>62400</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" t="s">
+        <v>109</v>
+      </c>
+      <c r="C32">
+        <v>2607</v>
+      </c>
+      <c r="D32">
+        <v>18.265000000000001</v>
+      </c>
+      <c r="E32">
+        <v>18.957999999999998</v>
+      </c>
+      <c r="F32">
+        <v>31.843</v>
+      </c>
+      <c r="G32">
+        <v>74.8</v>
+      </c>
+      <c r="H32">
+        <v>57.4</v>
+      </c>
+      <c r="I32" t="s">
+        <v>193</v>
+      </c>
+      <c r="J32" s="13">
+        <v>41151</v>
+      </c>
+      <c r="K32" t="s">
+        <v>223</v>
+      </c>
+      <c r="L32">
+        <v>18265</v>
+      </c>
+      <c r="M32">
+        <v>18958</v>
+      </c>
+      <c r="N32">
+        <v>31843</v>
+      </c>
+      <c r="O32">
+        <v>74800</v>
+      </c>
+      <c r="P32">
+        <v>57400</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" t="s">
+        <v>105</v>
+      </c>
+      <c r="C33">
+        <v>2100</v>
+      </c>
+      <c r="D33">
+        <v>14.395</v>
+      </c>
+      <c r="E33">
+        <v>19.298999999999999</v>
+      </c>
+      <c r="F33">
+        <v>23.132000000000001</v>
+      </c>
+      <c r="G33">
+        <v>68.2</v>
+      </c>
+      <c r="H33">
+        <v>41.7</v>
+      </c>
+      <c r="I33" t="s">
+        <v>43</v>
+      </c>
+      <c r="J33" s="13">
+        <v>40060</v>
+      </c>
+      <c r="K33" t="s">
+        <v>223</v>
+      </c>
+      <c r="L33">
+        <v>14395</v>
+      </c>
+      <c r="M33">
+        <v>19299</v>
+      </c>
+      <c r="N33">
+        <v>23132</v>
+      </c>
+      <c r="O33">
+        <v>68200</v>
+      </c>
+      <c r="P33">
+        <v>41700</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" t="s">
+        <v>134</v>
+      </c>
+      <c r="C34">
+        <v>2266</v>
+      </c>
+      <c r="D34">
+        <v>28.631</v>
+      </c>
+      <c r="E34">
+        <v>19.780999999999999</v>
+      </c>
+      <c r="F34">
+        <v>31.140999999999998</v>
+      </c>
+      <c r="G34">
+        <v>92.9</v>
+      </c>
+      <c r="H34">
+        <v>56.1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>206</v>
+      </c>
+      <c r="J34" s="13">
+        <v>42713</v>
+      </c>
+      <c r="K34" t="s">
+        <v>223</v>
+      </c>
+      <c r="L34">
+        <v>28631</v>
+      </c>
+      <c r="M34">
+        <v>19781</v>
+      </c>
+      <c r="N34">
+        <v>31141</v>
+      </c>
+      <c r="O34">
+        <v>92900</v>
+      </c>
+      <c r="P34">
+        <v>56100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>245</v>
+      </c>
+      <c r="B35" t="s">
+        <v>247</v>
+      </c>
+      <c r="C35">
+        <v>2400</v>
+      </c>
+      <c r="D35">
+        <v>23.448</v>
+      </c>
+      <c r="E35">
+        <v>32.408000000000001</v>
+      </c>
+      <c r="F35">
+        <v>50.741999999999997</v>
+      </c>
+      <c r="G35">
+        <v>113.1</v>
+      </c>
+      <c r="H35">
+        <v>91.5</v>
+      </c>
+      <c r="I35" t="s">
+        <v>10</v>
+      </c>
+      <c r="J35" s="13">
+        <v>46116</v>
+      </c>
+      <c r="K35" t="s">
+        <v>224</v>
+      </c>
+      <c r="L35">
+        <v>23448</v>
+      </c>
+      <c r="M35">
+        <v>32408</v>
+      </c>
+      <c r="N35">
+        <v>50742</v>
+      </c>
+      <c r="O35">
+        <v>113052</v>
+      </c>
+      <c r="P35">
+        <v>91486</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B36" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36">
+        <v>2043</v>
+      </c>
+      <c r="D36">
+        <v>19.359000000000002</v>
+      </c>
+      <c r="E36">
+        <v>19.808</v>
+      </c>
+      <c r="F36">
+        <v>33.182000000000002</v>
+      </c>
+      <c r="G36">
+        <v>78.599999999999994</v>
+      </c>
+      <c r="H36">
+        <v>59.8</v>
+      </c>
+      <c r="I36" t="s">
+        <v>205</v>
+      </c>
+      <c r="J36" s="13">
+        <v>41919</v>
+      </c>
+      <c r="K36" t="s">
+        <v>223</v>
+      </c>
+      <c r="L36">
+        <v>19359</v>
+      </c>
+      <c r="M36">
+        <v>19808</v>
+      </c>
+      <c r="N36">
+        <v>33182</v>
+      </c>
+      <c r="O36">
+        <v>78600</v>
+      </c>
+      <c r="P36">
+        <v>59800</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>135</v>
+      </c>
+      <c r="B37" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37">
+        <v>2832</v>
+      </c>
+      <c r="D37">
+        <v>33.670999999999999</v>
+      </c>
+      <c r="E37">
+        <v>23.584</v>
+      </c>
+      <c r="F37">
+        <v>36.384</v>
+      </c>
+      <c r="G37">
+        <v>110.1</v>
+      </c>
+      <c r="H37">
+        <v>65.599999999999994</v>
+      </c>
+      <c r="I37" t="s">
+        <v>204</v>
+      </c>
+      <c r="J37" s="13">
+        <v>42443</v>
+      </c>
+      <c r="K37" t="s">
+        <v>223</v>
+      </c>
+      <c r="L37">
+        <v>33671</v>
+      </c>
+      <c r="M37">
+        <v>23584</v>
+      </c>
+      <c r="N37">
+        <v>36384</v>
+      </c>
+      <c r="O37">
+        <v>110100</v>
+      </c>
+      <c r="P37">
+        <v>65600</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38">
+        <v>3066</v>
+      </c>
+      <c r="D38">
+        <v>28.776</v>
+      </c>
+      <c r="E38">
+        <v>23.881</v>
+      </c>
+      <c r="F38">
+        <v>47.396000000000001</v>
+      </c>
+      <c r="G38">
+        <v>103.7</v>
+      </c>
+      <c r="H38">
+        <v>85.5</v>
+      </c>
+      <c r="I38" t="s">
+        <v>203</v>
+      </c>
+      <c r="J38" s="13">
+        <v>44691</v>
+      </c>
+      <c r="K38" t="s">
+        <v>223</v>
+      </c>
+      <c r="L38">
+        <v>28776</v>
+      </c>
+      <c r="M38">
+        <v>23881</v>
+      </c>
+      <c r="N38">
+        <v>47396</v>
+      </c>
+      <c r="O38">
+        <v>103658</v>
+      </c>
+      <c r="P38">
+        <v>85453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>150</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39">
+        <v>3200</v>
+      </c>
+      <c r="D39">
+        <v>37.845999999999997</v>
+      </c>
+      <c r="E39">
+        <v>23.882000000000001</v>
+      </c>
+      <c r="F39">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="G39">
+        <v>116.6</v>
+      </c>
+      <c r="H39">
+        <v>85.5</v>
+      </c>
+      <c r="I39" t="s">
+        <v>10</v>
+      </c>
+      <c r="J39" s="13">
+        <v>41537</v>
+      </c>
+      <c r="K39" t="s">
+        <v>223</v>
+      </c>
+      <c r="L39">
+        <v>37846</v>
+      </c>
+      <c r="M39">
+        <v>23882</v>
+      </c>
+      <c r="N39">
+        <v>47437</v>
+      </c>
+      <c r="O39">
+        <v>116600</v>
+      </c>
+      <c r="P39">
+        <v>85500</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>151</v>
+      </c>
+      <c r="B40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C40">
+        <v>2667</v>
+      </c>
+      <c r="D40">
+        <v>24.206</v>
+      </c>
+      <c r="E40">
+        <v>24.602</v>
+      </c>
+      <c r="F40">
+        <v>41.085000000000001</v>
+      </c>
+      <c r="G40" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" t="s">
+        <v>10</v>
+      </c>
+      <c r="I40" t="s">
+        <v>202</v>
+      </c>
+      <c r="J40" s="13">
+        <v>40683</v>
+      </c>
+      <c r="K40" t="s">
+        <v>223</v>
+      </c>
+      <c r="L40">
+        <v>24206</v>
+      </c>
+      <c r="M40">
+        <v>24602</v>
+      </c>
+      <c r="N40">
+        <v>41085</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>186</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+      <c r="C41">
+        <v>2829</v>
+      </c>
+      <c r="D41">
+        <v>21.475999999999999</v>
+      </c>
+      <c r="E41">
+        <v>25.608000000000001</v>
+      </c>
+      <c r="F41">
+        <v>30.663</v>
+      </c>
+      <c r="G41">
+        <v>95.2</v>
+      </c>
+      <c r="H41">
+        <v>55.3</v>
+      </c>
+      <c r="I41" t="s">
+        <v>201</v>
+      </c>
+      <c r="J41" s="13">
+        <v>39896</v>
+      </c>
+      <c r="K41" t="s">
+        <v>223</v>
+      </c>
+      <c r="L41">
+        <v>21476</v>
+      </c>
+      <c r="M41">
+        <v>25608</v>
+      </c>
+      <c r="N41">
+        <v>30663</v>
+      </c>
+      <c r="O41">
+        <v>95200</v>
+      </c>
+      <c r="P41">
+        <v>55300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>167</v>
+      </c>
+      <c r="B42" t="s">
+        <v>168</v>
+      </c>
+      <c r="C42">
+        <v>2667</v>
+      </c>
+      <c r="D42">
+        <v>27.460999999999999</v>
+      </c>
+      <c r="E42">
+        <v>26.341999999999999</v>
+      </c>
+      <c r="F42">
+        <v>27.893999999999998</v>
+      </c>
+      <c r="G42">
+        <v>107.5</v>
+      </c>
+      <c r="H42">
+        <v>86.4</v>
+      </c>
+      <c r="I42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J42" s="13">
+        <v>43956</v>
+      </c>
+      <c r="K42" t="s">
+        <v>223</v>
+      </c>
+      <c r="L42">
+        <v>27461</v>
+      </c>
+      <c r="M42">
+        <v>26342</v>
+      </c>
+      <c r="N42">
+        <v>27894</v>
+      </c>
+      <c r="O42">
+        <v>107500</v>
+      </c>
+      <c r="P42">
+        <v>86400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>138</v>
+      </c>
+      <c r="B43" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43">
+        <v>3352</v>
+      </c>
+      <c r="D43">
+        <v>28.021999999999998</v>
+      </c>
+      <c r="E43">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="F43">
+        <v>44.103999999999999</v>
+      </c>
+      <c r="G43">
+        <v>122.4</v>
+      </c>
+      <c r="H43">
+        <v>79.2</v>
+      </c>
+      <c r="I43" t="s">
+        <v>200</v>
+      </c>
+      <c r="J43" s="13">
+        <v>42315</v>
+      </c>
+      <c r="K43" t="s">
+        <v>223</v>
+      </c>
+      <c r="L43">
+        <v>28022</v>
+      </c>
+      <c r="M43">
+        <v>32586</v>
+      </c>
+      <c r="N43">
+        <v>44104</v>
+      </c>
+      <c r="O43">
+        <v>122400</v>
+      </c>
+      <c r="P43">
+        <v>79200</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>120</v>
+      </c>
+      <c r="B44" t="s">
+        <v>171</v>
+      </c>
+      <c r="C44">
+        <v>2300</v>
+      </c>
+      <c r="D44">
+        <v>39.049999999999997</v>
+      </c>
+      <c r="E44">
+        <v>33.215000000000003</v>
+      </c>
+      <c r="F44">
+        <v>54.26</v>
+      </c>
+      <c r="G44">
+        <v>142.69999999999999</v>
+      </c>
+      <c r="H44">
+        <v>97.8</v>
+      </c>
+      <c r="I44" t="s">
+        <v>10</v>
+      </c>
+      <c r="J44" s="13">
+        <v>42397</v>
+      </c>
+      <c r="K44" t="s">
+        <v>223</v>
+      </c>
+      <c r="L44">
+        <v>39050</v>
+      </c>
+      <c r="M44">
+        <v>33215</v>
+      </c>
+      <c r="N44">
+        <v>54260</v>
+      </c>
+      <c r="O44">
+        <v>142700</v>
+      </c>
+      <c r="P44">
+        <v>97800</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45">
+        <v>2500</v>
+      </c>
+      <c r="D45">
+        <v>40.698999999999998</v>
+      </c>
+      <c r="E45">
+        <v>37.018000000000001</v>
+      </c>
+      <c r="F45">
+        <v>52.634999999999998</v>
+      </c>
+      <c r="G45">
+        <v>154.5</v>
+      </c>
+      <c r="H45">
+        <v>94.9</v>
+      </c>
+      <c r="I45" t="s">
+        <v>199</v>
+      </c>
+      <c r="J45" s="13">
+        <v>42397</v>
+      </c>
+      <c r="K45" t="s">
+        <v>223</v>
+      </c>
+      <c r="L45">
+        <v>40699</v>
+      </c>
+      <c r="M45">
+        <v>37018</v>
+      </c>
+      <c r="N45">
+        <v>52635</v>
+      </c>
+      <c r="O45">
+        <v>154500</v>
+      </c>
+      <c r="P45">
+        <v>94900</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>141</v>
+      </c>
+      <c r="B46" t="s">
+        <v>142</v>
+      </c>
+      <c r="C46">
+        <v>2600</v>
+      </c>
+      <c r="D46">
+        <v>45.381999999999998</v>
+      </c>
+      <c r="E46">
+        <v>40.313000000000002</v>
+      </c>
+      <c r="F46">
+        <v>61.804000000000002</v>
+      </c>
+      <c r="G46">
+        <v>169.9</v>
+      </c>
+      <c r="H46">
+        <v>111.4</v>
+      </c>
+      <c r="I46" t="s">
+        <v>198</v>
+      </c>
+      <c r="J46" s="13">
+        <v>42817</v>
+      </c>
+      <c r="K46" t="s">
+        <v>223</v>
+      </c>
+      <c r="L46">
+        <v>45382</v>
+      </c>
+      <c r="M46">
+        <v>40313</v>
+      </c>
+      <c r="N46">
+        <v>61804</v>
+      </c>
+      <c r="O46">
+        <v>169900</v>
+      </c>
+      <c r="P46">
+        <v>111400</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>173</v>
+      </c>
+      <c r="B47" t="s">
+        <v>166</v>
+      </c>
+      <c r="C47">
+        <v>2700</v>
+      </c>
+      <c r="D47">
+        <v>57.2</v>
+      </c>
+      <c r="E47">
+        <v>43.731999999999999</v>
+      </c>
+      <c r="F47">
+        <v>107.95399999999999</v>
+      </c>
+      <c r="G47">
+        <v>196.6</v>
+      </c>
+      <c r="H47">
+        <v>194.6</v>
+      </c>
+      <c r="I47" t="s">
+        <v>197</v>
+      </c>
+      <c r="J47" s="13">
+        <v>44155</v>
+      </c>
+      <c r="K47" t="s">
+        <v>223</v>
+      </c>
+      <c r="L47">
+        <v>57200</v>
+      </c>
+      <c r="M47">
+        <v>43732</v>
+      </c>
+      <c r="N47">
+        <v>107954</v>
+      </c>
+      <c r="O47">
+        <v>196600</v>
+      </c>
+      <c r="P47">
+        <v>194600</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>172</v>
+      </c>
+      <c r="C48">
+        <v>2600</v>
+      </c>
+      <c r="D48">
+        <v>55.045999999999999</v>
+      </c>
+      <c r="E48">
+        <v>44.618000000000002</v>
+      </c>
+      <c r="F48">
+        <v>73.569999999999993</v>
+      </c>
+      <c r="G48">
+        <v>195.6</v>
+      </c>
+      <c r="H48">
+        <v>132.6</v>
+      </c>
+      <c r="I48" t="s">
+        <v>196</v>
+      </c>
+      <c r="J48" s="13">
+        <v>43355</v>
+      </c>
+      <c r="K48" t="s">
+        <v>223</v>
+      </c>
+      <c r="L48">
+        <v>55046</v>
+      </c>
+      <c r="M48">
+        <v>44618</v>
+      </c>
+      <c r="N48">
+        <v>73570</v>
+      </c>
+      <c r="O48">
+        <v>195600</v>
+      </c>
+      <c r="P48">
+        <v>132600</v>
+      </c>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>126</v>
+      </c>
+      <c r="B49" t="s">
+        <v>124</v>
+      </c>
+      <c r="C49">
+        <v>2600</v>
+      </c>
+      <c r="D49">
+        <v>63.682000000000002</v>
+      </c>
+      <c r="E49">
+        <v>45.731999999999999</v>
+      </c>
+      <c r="F49">
+        <v>68.159000000000006</v>
+      </c>
+      <c r="G49">
+        <v>211.2</v>
+      </c>
+      <c r="H49">
+        <v>122.9</v>
+      </c>
+      <c r="I49" t="s">
+        <v>10</v>
+      </c>
+      <c r="J49" s="13">
+        <v>43146</v>
+      </c>
+      <c r="K49" t="s">
+        <v>223</v>
+      </c>
+      <c r="L49">
+        <v>63682</v>
+      </c>
+      <c r="M49">
+        <v>45732</v>
+      </c>
+      <c r="N49">
+        <v>68159</v>
+      </c>
+      <c r="O49">
+        <v>211200</v>
+      </c>
+      <c r="P49">
+        <v>122900</v>
+      </c>
+    </row>
+    <row r="50" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" t="s">
+        <v>125</v>
+      </c>
+      <c r="C50">
+        <v>2500</v>
+      </c>
+      <c r="D50">
+        <v>50.423000000000002</v>
+      </c>
+      <c r="E50">
+        <v>46.116999999999997</v>
+      </c>
+      <c r="F50">
+        <v>70.039000000000001</v>
+      </c>
+      <c r="G50">
+        <v>192</v>
+      </c>
+      <c r="H50">
+        <v>126.3</v>
+      </c>
+      <c r="I50" t="s">
+        <v>10</v>
+      </c>
+      <c r="J50" s="13">
+        <v>43146</v>
+      </c>
+      <c r="K50" t="s">
+        <v>223</v>
+      </c>
+      <c r="L50">
+        <v>50423</v>
+      </c>
+      <c r="M50">
+        <v>46117</v>
+      </c>
+      <c r="N50">
+        <v>70039</v>
+      </c>
+      <c r="O50">
+        <v>192000</v>
+      </c>
+      <c r="P50">
+        <v>126300</v>
+      </c>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>216</v>
+      </c>
+      <c r="B51" t="s">
+        <v>217</v>
+      </c>
+      <c r="C51">
+        <v>2112</v>
+      </c>
+      <c r="D51">
+        <v>61.249000000000002</v>
+      </c>
+      <c r="E51">
+        <v>46.226999999999997</v>
+      </c>
+      <c r="F51">
+        <v>113.619</v>
+      </c>
+      <c r="G51">
+        <v>209</v>
+      </c>
+      <c r="H51">
+        <v>204.9</v>
+      </c>
+      <c r="I51" t="s">
+        <v>218</v>
+      </c>
+      <c r="J51" s="13">
+        <v>45298</v>
+      </c>
+      <c r="K51" t="s">
+        <v>223</v>
+      </c>
+      <c r="L51">
+        <v>61249</v>
+      </c>
+      <c r="M51">
+        <v>46227</v>
+      </c>
+      <c r="N51">
+        <v>113619</v>
+      </c>
+      <c r="O51">
+        <v>209000</v>
+      </c>
+      <c r="P51">
+        <v>204900</v>
+      </c>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>236</v>
+      </c>
+      <c r="B52" t="s">
+        <v>237</v>
+      </c>
+      <c r="C52">
+        <v>3700</v>
+      </c>
+      <c r="D52">
+        <v>68.150000000000006</v>
+      </c>
+      <c r="E52">
+        <v>48.103000000000002</v>
+      </c>
+      <c r="F52">
+        <v>118.447</v>
+      </c>
+      <c r="G52">
+        <v>223.8</v>
+      </c>
+      <c r="H52">
+        <v>216.6</v>
+      </c>
+      <c r="J52" s="13">
+        <v>45773</v>
+      </c>
+      <c r="K52" t="s">
+        <v>223</v>
+      </c>
+      <c r="L52">
+        <v>68150</v>
+      </c>
+      <c r="M52">
+        <v>48103</v>
+      </c>
+      <c r="N52">
+        <v>118447</v>
+      </c>
+      <c r="O52">
+        <v>223805</v>
+      </c>
+      <c r="P52">
+        <v>216554</v>
+      </c>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53">
+        <v>2295</v>
+      </c>
+      <c r="D53">
+        <v>59.665999999999997</v>
+      </c>
+      <c r="E53">
+        <v>49.441000000000003</v>
+      </c>
+      <c r="F53">
+        <v>116.922</v>
+      </c>
+      <c r="G53">
+        <v>214.8</v>
+      </c>
+      <c r="H53">
+        <v>210.8</v>
+      </c>
+      <c r="I53" t="s">
+        <v>235</v>
+      </c>
+      <c r="J53" s="13">
+        <v>45298</v>
+      </c>
+      <c r="K53" t="s">
+        <v>223</v>
+      </c>
+      <c r="L53">
+        <v>59666</v>
+      </c>
+      <c r="M53">
+        <v>49441</v>
+      </c>
+      <c r="N53">
+        <v>116922</v>
+      </c>
+      <c r="O53">
+        <v>214800</v>
+      </c>
+      <c r="P53">
+        <v>210800</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>208</v>
+      </c>
+      <c r="B54" t="s">
+        <v>209</v>
+      </c>
+      <c r="C54">
+        <v>3700</v>
+      </c>
+      <c r="D54">
+        <v>62.206000000000003</v>
+      </c>
+      <c r="E54">
+        <v>49.951000000000001</v>
+      </c>
+      <c r="F54">
+        <v>112.593</v>
+      </c>
+      <c r="G54">
+        <v>219.9</v>
+      </c>
+      <c r="H54">
+        <v>203</v>
+      </c>
+      <c r="I54" t="s">
+        <v>207</v>
+      </c>
+      <c r="J54" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K54" t="s">
+        <v>223</v>
+      </c>
+      <c r="L54">
+        <v>62206</v>
+      </c>
+      <c r="M54">
+        <v>49951</v>
+      </c>
+      <c r="N54">
+        <v>112593</v>
+      </c>
+      <c r="O54">
+        <v>219900</v>
+      </c>
+      <c r="P54">
+        <v>203000</v>
+      </c>
+      <c r="S54" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>177</v>
+      </c>
+      <c r="B55" t="s">
+        <v>178</v>
+      </c>
+      <c r="C55">
+        <v>4160</v>
+      </c>
+      <c r="D55">
+        <v>77.174000000000007</v>
+      </c>
+      <c r="E55">
+        <v>56.761000000000003</v>
+      </c>
+      <c r="F55">
+        <v>138.00299999999999</v>
+      </c>
+      <c r="G55">
+        <v>259.5</v>
+      </c>
+      <c r="H55">
+        <v>248.8</v>
+      </c>
+      <c r="I55" t="s">
+        <v>195</v>
+      </c>
+      <c r="J55" s="13">
+        <v>45211</v>
+      </c>
+      <c r="K55" t="s">
+        <v>223</v>
+      </c>
+      <c r="L55">
+        <v>77174</v>
+      </c>
+      <c r="M55">
+        <v>56761</v>
+      </c>
+      <c r="N55">
+        <v>138003</v>
+      </c>
+      <c r="O55">
+        <v>259470</v>
+      </c>
+      <c r="P55">
+        <v>248812</v>
+      </c>
+      <c r="S55" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>246</v>
+      </c>
+      <c r="B56" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56">
+        <v>3090</v>
+      </c>
+      <c r="D56">
+        <v>63.435000000000002</v>
+      </c>
+      <c r="E56">
+        <v>66.734999999999999</v>
+      </c>
+      <c r="F56">
+        <v>143.465</v>
+      </c>
+      <c r="G56">
+        <v>261.7</v>
+      </c>
+      <c r="H56">
+        <v>258.7</v>
+      </c>
+      <c r="J56" s="13">
+        <v>46116</v>
+      </c>
+      <c r="K56" t="s">
+        <v>250</v>
+      </c>
+      <c r="L56">
+        <v>63435</v>
+      </c>
+      <c r="M56">
+        <v>66735</v>
+      </c>
+      <c r="N56">
+        <v>143465</v>
+      </c>
+      <c r="O56">
+        <v>261682</v>
+      </c>
+      <c r="P56">
+        <v>258660</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>251</v>
+      </c>
+      <c r="S56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>220</v>
+      </c>
+      <c r="B57" t="s">
+        <v>219</v>
+      </c>
+      <c r="C57">
+        <v>3200</v>
+      </c>
+      <c r="D57">
+        <v>66.938999999999993</v>
+      </c>
+      <c r="E57">
+        <v>79.733000000000004</v>
+      </c>
+      <c r="F57">
+        <v>216.304</v>
+      </c>
+      <c r="G57">
+        <v>296.39999999999998</v>
+      </c>
+      <c r="H57">
+        <v>389.9</v>
+      </c>
+      <c r="I57" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K57" t="s">
+        <v>230</v>
+      </c>
+      <c r="L57">
+        <v>66939</v>
+      </c>
+      <c r="M57">
+        <v>79733</v>
+      </c>
+      <c r="N57">
+        <v>216304</v>
+      </c>
+      <c r="O57">
+        <v>296400</v>
+      </c>
+      <c r="P57">
+        <v>389900</v>
+      </c>
+      <c r="S57" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>184</v>
+      </c>
+      <c r="B58" t="s">
+        <v>185</v>
+      </c>
+      <c r="C58">
+        <v>4700</v>
+      </c>
+      <c r="D58">
+        <v>104.52500000000001</v>
+      </c>
+      <c r="E58">
+        <v>85.01</v>
+      </c>
+      <c r="F58">
+        <v>264.86900000000003</v>
+      </c>
+      <c r="G58">
+        <v>372.2</v>
+      </c>
+      <c r="H58">
+        <v>377.5</v>
+      </c>
+      <c r="I58" t="s">
+        <v>194</v>
+      </c>
+      <c r="J58" s="13">
+        <v>45561</v>
+      </c>
+      <c r="K58" t="s">
+        <v>223</v>
+      </c>
+      <c r="L58">
+        <v>104525</v>
+      </c>
+      <c r="M58">
+        <v>85010</v>
+      </c>
+      <c r="N58">
+        <v>264869</v>
+      </c>
+      <c r="O58">
+        <v>372200</v>
+      </c>
+      <c r="P58">
+        <v>377500</v>
+      </c>
+      <c r="S58" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>253</v>
+      </c>
+      <c r="B59" t="s">
+        <v>254</v>
+      </c>
+      <c r="C59">
+        <v>3210</v>
+      </c>
+      <c r="D59">
+        <v>83.274000000000001</v>
+      </c>
+      <c r="E59">
+        <v>86</v>
+      </c>
+      <c r="F59">
+        <v>163.31299999999999</v>
+      </c>
+      <c r="G59">
+        <v>339.9</v>
+      </c>
+      <c r="H59">
+        <v>296.2</v>
+      </c>
+      <c r="I59" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="13">
+        <v>46116</v>
+      </c>
+      <c r="K59" t="s">
+        <v>255</v>
+      </c>
+      <c r="L59">
+        <v>83274</v>
+      </c>
+      <c r="M59">
+        <v>86000</v>
+      </c>
+      <c r="N59">
+        <v>163313</v>
+      </c>
+      <c r="O59">
+        <v>339907</v>
+      </c>
+      <c r="P59">
+        <v>296248</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/nbench/list2026.xlsx
+++ b/nbench/list2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\archive\github\benchmark\nbench\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D97879D0-3740-4811-9015-BD9A29C21C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9BA65-6DF8-4DC5-AC07-62E853870D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28905" yWindow="180" windowWidth="26505" windowHeight="15705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6990" yWindow="30" windowWidth="26505" windowHeight="15705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="7" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="2020" sheetId="2" r:id="rId6"/>
     <sheet name="2019" sheetId="1" r:id="rId7"/>
     <sheet name="csv" sheetId="8" r:id="rId8"/>
+    <sheet name="export_markdown" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1474" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="268">
   <si>
     <t>CPU</t>
   </si>
@@ -836,6 +837,18 @@
   </si>
   <si>
     <t>regular PC</t>
+  </si>
+  <si>
+    <t>MIPS 74Kc</t>
+  </si>
+  <si>
+    <t>TP-Link Archer C7</t>
+  </si>
+  <si>
+    <t>Qualc. Atheros QCA9563</t>
+  </si>
+  <si>
+    <t>6.12.74, gcc 14.3.0</t>
   </si>
 </sst>
 </file>
@@ -848,7 +861,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -904,8 +917,27 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1F2328"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -978,6 +1010,36 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF5050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1022,7 +1084,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1077,18 +1139,6 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1104,6 +1154,45 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1111,6 +1200,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF5050"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1433,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82BCFD32-DD89-45D1-9DAB-60CCE8B3399A}">
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC64"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.42578125" bestFit="1" customWidth="1"/>
@@ -1558,7 +1652,7 @@
       <c r="J2" s="13">
         <v>40892</v>
       </c>
-      <c r="K2" t="s">
+      <c r="K2" s="41" t="s">
         <v>228</v>
       </c>
       <c r="M2" s="18">
@@ -1581,7 +1675,7 @@
         <f>H2*1000</f>
         <v>200</v>
       </c>
-      <c r="T2" s="30"/>
+      <c r="T2" s="26"/>
       <c r="U2" s="24"/>
       <c r="V2" s="24"/>
       <c r="W2" s="24"/>
@@ -1623,11 +1717,11 @@
       <c r="J3" s="13">
         <v>41122</v>
       </c>
-      <c r="K3" t="s">
+      <c r="K3" s="17" t="s">
         <v>225</v>
       </c>
       <c r="M3" s="18">
-        <f t="shared" ref="M3:Q55" si="0">D3*1000</f>
+        <f t="shared" ref="M3:Q56" si="0">D3*1000</f>
         <v>1238</v>
       </c>
       <c r="N3" s="18">
@@ -1647,7 +1741,7 @@
         <v>4300</v>
       </c>
       <c r="R3" s="18"/>
-      <c r="T3" s="30"/>
+      <c r="T3" s="26"/>
       <c r="U3" s="24"/>
       <c r="V3" s="24"/>
       <c r="W3" s="24"/>
@@ -1689,7 +1783,7 @@
       <c r="J4" s="13">
         <v>41487</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="41" t="s">
         <v>228</v>
       </c>
       <c r="M4" s="18">
@@ -1713,7 +1807,7 @@
         <v>400</v>
       </c>
       <c r="R4" s="18"/>
-      <c r="T4" s="30"/>
+      <c r="T4" s="26"/>
       <c r="U4" s="24"/>
       <c r="V4" s="24"/>
       <c r="W4" s="24"/>
@@ -1755,7 +1849,7 @@
       <c r="J5" s="13">
         <v>41489</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="39" t="s">
         <v>229</v>
       </c>
       <c r="M5" s="18">
@@ -1779,7 +1873,7 @@
         <v>60</v>
       </c>
       <c r="R5" s="18"/>
-      <c r="T5" s="30"/>
+      <c r="T5" s="26"/>
       <c r="U5" s="24"/>
       <c r="V5" s="24"/>
       <c r="W5" s="24"/>
@@ -1821,7 +1915,7 @@
       <c r="J6" s="13">
         <v>41122</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="41" t="s">
         <v>228</v>
       </c>
       <c r="M6" s="18">
@@ -1845,7 +1939,7 @@
         <v>400</v>
       </c>
       <c r="R6" s="18"/>
-      <c r="T6" s="30"/>
+      <c r="T6" s="26"/>
       <c r="U6" s="24"/>
       <c r="V6" s="24"/>
       <c r="W6" s="24"/>
@@ -1857,13 +1951,13 @@
       <c r="AC6" s="25"/>
     </row>
     <row r="7" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="36" t="s">
+      <c r="B7" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="32">
         <v>700</v>
       </c>
       <c r="D7" s="10">
@@ -1885,7 +1979,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" t="s">
+      <c r="K7" s="41" t="s">
         <v>226</v>
       </c>
       <c r="M7" s="18">
@@ -1909,7 +2003,7 @@
         <v>3660</v>
       </c>
       <c r="R7" s="18"/>
-      <c r="T7" s="30"/>
+      <c r="T7" s="26"/>
       <c r="U7" s="24"/>
       <c r="V7" s="24"/>
       <c r="W7" s="24"/>
@@ -1951,7 +2045,7 @@
       <c r="J8" s="13">
         <v>41861</v>
       </c>
-      <c r="K8" t="s">
+      <c r="K8" s="40" t="s">
         <v>227</v>
       </c>
       <c r="M8" s="18">
@@ -1975,7 +2069,7 @@
         <v>6690</v>
       </c>
       <c r="R8" s="18"/>
-      <c r="T8" s="30"/>
+      <c r="T8" s="26"/>
       <c r="U8" s="24"/>
       <c r="V8" s="24"/>
       <c r="W8" s="24"/>
@@ -1987,61 +2081,64 @@
       <c r="AC8" s="25"/>
     </row>
     <row r="9" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="C9" s="16">
-        <v>933</v>
+      <c r="A9" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="17">
+        <v>750</v>
       </c>
       <c r="D9" s="10">
-        <v>4.7089999999999996</v>
+        <v>1.7330000000000001</v>
       </c>
       <c r="E9" s="19">
-        <v>5.1639999999999997</v>
+        <v>3.9889999999999999</v>
       </c>
       <c r="F9" s="10">
-        <v>8.9160000000000004</v>
+        <v>0.25</v>
       </c>
       <c r="G9" s="11">
-        <v>19.899999999999999</v>
+        <v>11.183</v>
       </c>
       <c r="H9" s="11">
-        <v>16.100000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="J9" s="13">
-        <v>41861</v>
-      </c>
-      <c r="K9" t="s">
-        <v>225</v>
+        <v>46117</v>
+      </c>
+      <c r="K9" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="L9" t="s">
+        <v>267</v>
       </c>
       <c r="M9" s="18">
-        <f t="shared" si="0"/>
-        <v>4709</v>
+        <f t="shared" ref="M9:Q9" si="1">D9*1000</f>
+        <v>1733</v>
       </c>
       <c r="N9" s="18">
-        <f t="shared" si="0"/>
-        <v>5164</v>
+        <f t="shared" si="1"/>
+        <v>3989</v>
       </c>
       <c r="O9" s="18">
-        <f t="shared" si="0"/>
-        <v>8916</v>
+        <f t="shared" si="1"/>
+        <v>250</v>
       </c>
       <c r="P9" s="18">
-        <f t="shared" si="0"/>
-        <v>19900</v>
+        <f t="shared" si="1"/>
+        <v>11183</v>
       </c>
       <c r="Q9" s="18">
-        <f t="shared" si="0"/>
-        <v>16100.000000000002</v>
+        <f t="shared" si="1"/>
+        <v>450</v>
       </c>
       <c r="R9" s="18"/>
-      <c r="T9" s="30"/>
+      <c r="T9" s="26"/>
       <c r="U9" s="24"/>
       <c r="V9" s="24"/>
       <c r="W9" s="24"/>
@@ -2053,61 +2150,61 @@
       <c r="AC9" s="25"/>
     </row>
     <row r="10" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C10">
-        <v>1008</v>
+      <c r="A10" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="16">
+        <v>933</v>
       </c>
       <c r="D10" s="10">
-        <v>3.665</v>
+        <v>4.7089999999999996</v>
       </c>
       <c r="E10" s="19">
-        <v>5.46</v>
+        <v>5.1639999999999997</v>
       </c>
       <c r="F10" s="10">
-        <v>4.6849999999999996</v>
+        <v>8.9160000000000004</v>
       </c>
       <c r="G10" s="11">
-        <v>18.399999999999999</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="H10" s="11">
-        <v>8.4499999999999993</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="J10" s="13">
         <v>41861</v>
       </c>
-      <c r="K10" t="s">
-        <v>227</v>
+      <c r="K10" s="17" t="s">
+        <v>225</v>
       </c>
       <c r="M10" s="18">
         <f t="shared" si="0"/>
-        <v>3665</v>
+        <v>4709</v>
       </c>
       <c r="N10" s="18">
         <f t="shared" si="0"/>
-        <v>5460</v>
+        <v>5164</v>
       </c>
       <c r="O10" s="18">
         <f t="shared" si="0"/>
-        <v>4685</v>
+        <v>8916</v>
       </c>
       <c r="P10" s="18">
         <f t="shared" si="0"/>
-        <v>18400</v>
+        <v>19900</v>
       </c>
       <c r="Q10" s="18">
         <f t="shared" si="0"/>
-        <v>8450</v>
+        <v>16100.000000000002</v>
       </c>
       <c r="R10" s="18"/>
-      <c r="T10" s="30"/>
+      <c r="T10" s="26"/>
       <c r="U10" s="24"/>
       <c r="V10" s="24"/>
       <c r="W10" s="24"/>
@@ -2119,29 +2216,29 @@
       <c r="AC10" s="25"/>
     </row>
     <row r="11" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="36" t="s">
-        <v>115</v>
-      </c>
-      <c r="C11" s="36">
-        <v>1000</v>
+      <c r="A11" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11">
+        <v>1008</v>
       </c>
       <c r="D11" s="10">
-        <v>4.665</v>
+        <v>3.665</v>
       </c>
       <c r="E11" s="19">
-        <v>6.4809999999999999</v>
+        <v>5.46</v>
       </c>
       <c r="F11" s="10">
-        <v>5.0590000000000002</v>
+        <v>4.6849999999999996</v>
       </c>
       <c r="G11" s="11">
-        <v>22.6</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="H11" s="11">
-        <v>9.1</v>
+        <v>8.4499999999999993</v>
       </c>
       <c r="I11" s="8" t="s">
         <v>10</v>
@@ -2149,31 +2246,31 @@
       <c r="J11" s="13">
         <v>41861</v>
       </c>
-      <c r="K11" t="s">
+      <c r="K11" s="40" t="s">
         <v>227</v>
       </c>
       <c r="M11" s="18">
         <f t="shared" si="0"/>
-        <v>4665</v>
+        <v>3665</v>
       </c>
       <c r="N11" s="18">
         <f t="shared" si="0"/>
-        <v>6481</v>
+        <v>5460</v>
       </c>
       <c r="O11" s="18">
         <f t="shared" si="0"/>
-        <v>5059</v>
+        <v>4685</v>
       </c>
       <c r="P11" s="18">
         <f t="shared" si="0"/>
-        <v>22600</v>
+        <v>18400</v>
       </c>
       <c r="Q11" s="18">
         <f t="shared" si="0"/>
-        <v>9100</v>
+        <v>8450</v>
       </c>
       <c r="R11" s="18"/>
-      <c r="T11" s="30"/>
+      <c r="T11" s="26"/>
       <c r="U11" s="24"/>
       <c r="V11" s="24"/>
       <c r="W11" s="24"/>
@@ -2185,61 +2282,61 @@
       <c r="AC11" s="25"/>
     </row>
     <row r="12" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C12">
-        <v>988</v>
+      <c r="A12" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="32">
+        <v>1000</v>
       </c>
       <c r="D12" s="10">
-        <v>5.7990000000000004</v>
+        <v>4.665</v>
       </c>
       <c r="E12" s="19">
-        <v>6.7169999999999996</v>
+        <v>6.4809999999999999</v>
       </c>
       <c r="F12" s="10">
-        <v>8.0549999999999997</v>
+        <v>5.0590000000000002</v>
       </c>
       <c r="G12" s="11">
-        <v>25.3</v>
+        <v>22.6</v>
       </c>
       <c r="H12" s="11">
-        <v>14.5</v>
+        <v>9.1</v>
       </c>
       <c r="I12" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J12" s="13">
-        <v>42217</v>
-      </c>
-      <c r="K12" s="34" t="s">
-        <v>224</v>
+        <v>41861</v>
+      </c>
+      <c r="K12" s="40" t="s">
+        <v>227</v>
       </c>
       <c r="M12" s="18">
         <f t="shared" si="0"/>
-        <v>5799</v>
+        <v>4665</v>
       </c>
       <c r="N12" s="18">
         <f t="shared" si="0"/>
-        <v>6717</v>
+        <v>6481</v>
       </c>
       <c r="O12" s="18">
         <f t="shared" si="0"/>
-        <v>8055</v>
+        <v>5059</v>
       </c>
       <c r="P12" s="18">
         <f t="shared" si="0"/>
-        <v>25300</v>
+        <v>22600</v>
       </c>
       <c r="Q12" s="18">
         <f t="shared" si="0"/>
-        <v>14500</v>
+        <v>9100</v>
       </c>
       <c r="R12" s="18"/>
-      <c r="T12" s="30"/>
+      <c r="T12" s="26"/>
       <c r="U12" s="24"/>
       <c r="V12" s="24"/>
       <c r="W12" s="24"/>
@@ -2251,61 +2348,61 @@
       <c r="AC12" s="25"/>
     </row>
     <row r="13" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="16">
-        <v>1200</v>
+      <c r="A13" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13">
+        <v>988</v>
       </c>
       <c r="D13" s="10">
-        <v>6.21</v>
+        <v>5.7990000000000004</v>
       </c>
       <c r="E13" s="19">
-        <v>7.0469999999999997</v>
+        <v>6.7169999999999996</v>
       </c>
       <c r="F13" s="10">
-        <v>12.384</v>
+        <v>8.0549999999999997</v>
       </c>
       <c r="G13" s="11">
-        <v>26.4</v>
+        <v>25.3</v>
       </c>
       <c r="H13" s="11">
-        <v>22</v>
+        <v>14.5</v>
       </c>
       <c r="I13" s="8" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J13" s="13">
-        <v>41797</v>
-      </c>
-      <c r="K13" t="s">
-        <v>225</v>
+        <v>42217</v>
+      </c>
+      <c r="K13" s="30" t="s">
+        <v>224</v>
       </c>
       <c r="M13" s="18">
         <f t="shared" si="0"/>
-        <v>6210</v>
+        <v>5799</v>
       </c>
       <c r="N13" s="18">
         <f t="shared" si="0"/>
-        <v>7047</v>
+        <v>6717</v>
       </c>
       <c r="O13" s="18">
         <f t="shared" si="0"/>
-        <v>12384</v>
+        <v>8055</v>
       </c>
       <c r="P13" s="18">
         <f t="shared" si="0"/>
-        <v>26400</v>
+        <v>25300</v>
       </c>
       <c r="Q13" s="18">
         <f t="shared" si="0"/>
-        <v>22000</v>
+        <v>14500</v>
       </c>
       <c r="R13" s="18"/>
-      <c r="T13" s="30"/>
+      <c r="T13" s="26"/>
       <c r="U13" s="24"/>
       <c r="V13" s="24"/>
       <c r="W13" s="24"/>
@@ -2318,61 +2415,60 @@
     </row>
     <row r="14" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
-        <v>153</v>
+        <v>98</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C14" s="16">
-        <v>1666</v>
+        <v>1200</v>
       </c>
       <c r="D14" s="10">
-        <v>7.2430000000000003</v>
+        <v>6.21</v>
       </c>
       <c r="E14" s="19">
-        <v>7.109</v>
+        <v>7.0469999999999997</v>
       </c>
       <c r="F14" s="10">
-        <v>7.351</v>
+        <v>12.384</v>
       </c>
       <c r="G14" s="11">
-        <v>28.6</v>
+        <v>26.4</v>
       </c>
       <c r="H14" s="11">
-        <v>12.8</v>
+        <v>22</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J14" s="13">
-        <v>40269</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L14" s="5"/>
+        <v>41797</v>
+      </c>
+      <c r="K14" s="17" t="s">
+        <v>225</v>
+      </c>
       <c r="M14" s="18">
         <f t="shared" si="0"/>
-        <v>7243</v>
+        <v>6210</v>
       </c>
       <c r="N14" s="18">
         <f t="shared" si="0"/>
-        <v>7109</v>
+        <v>7047</v>
       </c>
       <c r="O14" s="18">
         <f t="shared" si="0"/>
-        <v>7351</v>
+        <v>12384</v>
       </c>
       <c r="P14" s="18">
         <f t="shared" si="0"/>
-        <v>28600</v>
+        <v>26400</v>
       </c>
       <c r="Q14" s="18">
         <f t="shared" si="0"/>
-        <v>12800</v>
+        <v>22000</v>
       </c>
       <c r="R14" s="18"/>
-      <c r="T14" s="30"/>
+      <c r="T14" s="26"/>
       <c r="U14" s="24"/>
       <c r="V14" s="24"/>
       <c r="W14" s="24"/>
@@ -2384,61 +2480,62 @@
       <c r="AC14" s="25"/>
     </row>
     <row r="15" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>154</v>
-      </c>
-      <c r="B15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15">
-        <v>2000</v>
+      <c r="A15" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="16">
+        <v>1666</v>
       </c>
       <c r="D15" s="10">
-        <v>9.3940000000000001</v>
+        <v>7.2430000000000003</v>
       </c>
       <c r="E15" s="19">
-        <v>7.5289999999999999</v>
+        <v>7.109</v>
       </c>
       <c r="F15" s="10">
-        <v>13.164</v>
+        <v>7.351</v>
       </c>
       <c r="G15" s="11">
-        <v>33.200000000000003</v>
+        <v>28.6</v>
       </c>
       <c r="H15" s="11">
-        <v>23.7</v>
+        <v>12.8</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J15" s="13">
-        <v>40017</v>
-      </c>
-      <c r="K15" t="s">
-        <v>225</v>
-      </c>
+        <v>40269</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L15" s="5"/>
       <c r="M15" s="18">
         <f t="shared" si="0"/>
-        <v>9394</v>
+        <v>7243</v>
       </c>
       <c r="N15" s="18">
         <f t="shared" si="0"/>
-        <v>7529</v>
+        <v>7109</v>
       </c>
       <c r="O15" s="18">
         <f t="shared" si="0"/>
-        <v>13164</v>
+        <v>7351</v>
       </c>
       <c r="P15" s="18">
         <f t="shared" si="0"/>
-        <v>33200</v>
+        <v>28600</v>
       </c>
       <c r="Q15" s="18">
         <f t="shared" si="0"/>
-        <v>23700</v>
+        <v>12800</v>
       </c>
       <c r="R15" s="18"/>
-      <c r="T15" s="30"/>
+      <c r="T15" s="26"/>
       <c r="U15" s="24"/>
       <c r="V15" s="24"/>
       <c r="W15" s="24"/>
@@ -2450,61 +2547,61 @@
       <c r="AC15" s="25"/>
     </row>
     <row r="16" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>118</v>
-      </c>
-      <c r="C16" s="16">
-        <v>1600</v>
+      <c r="A16" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16">
+        <v>2000</v>
       </c>
       <c r="D16" s="10">
-        <v>7.7519999999999998</v>
+        <v>9.3940000000000001</v>
       </c>
       <c r="E16" s="19">
-        <v>7.5789999999999997</v>
+        <v>7.5289999999999999</v>
       </c>
       <c r="F16" s="10">
-        <v>7.0679999999999996</v>
+        <v>13.164</v>
       </c>
       <c r="G16" s="11">
-        <v>30.6</v>
+        <v>33.200000000000003</v>
       </c>
       <c r="H16" s="11">
-        <v>12.8</v>
+        <v>23.7</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="J16" s="13">
-        <v>40026</v>
-      </c>
-      <c r="K16" t="s">
+        <v>40017</v>
+      </c>
+      <c r="K16" s="17" t="s">
         <v>225</v>
       </c>
       <c r="M16" s="18">
         <f t="shared" si="0"/>
-        <v>7752</v>
+        <v>9394</v>
       </c>
       <c r="N16" s="18">
         <f t="shared" si="0"/>
-        <v>7579</v>
+        <v>7529</v>
       </c>
       <c r="O16" s="18">
         <f t="shared" si="0"/>
-        <v>7068</v>
+        <v>13164</v>
       </c>
       <c r="P16" s="18">
         <f t="shared" si="0"/>
-        <v>30600</v>
+        <v>33200</v>
       </c>
       <c r="Q16" s="18">
         <f t="shared" si="0"/>
-        <v>12800</v>
+        <v>23700</v>
       </c>
       <c r="R16" s="18"/>
-      <c r="T16" s="30"/>
+      <c r="T16" s="26"/>
       <c r="U16" s="24"/>
       <c r="V16" s="24"/>
       <c r="W16" s="24"/>
@@ -2517,61 +2614,60 @@
     </row>
     <row r="17" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="16" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C17" s="16">
-        <v>1666</v>
+        <v>1600</v>
       </c>
       <c r="D17" s="10">
-        <v>9.3859999999999992</v>
+        <v>7.7519999999999998</v>
       </c>
       <c r="E17" s="19">
-        <v>8.39</v>
+        <v>7.5789999999999997</v>
       </c>
       <c r="F17" s="10">
-        <v>7.3129999999999997</v>
+        <v>7.0679999999999996</v>
       </c>
       <c r="G17" s="11">
-        <v>35.299999999999997</v>
+        <v>30.6</v>
       </c>
       <c r="H17" s="11">
-        <v>13.2</v>
+        <v>12.8</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J17" s="13">
-        <v>41496</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L17" s="5"/>
+        <v>40026</v>
+      </c>
+      <c r="K17" s="17" t="s">
+        <v>225</v>
+      </c>
       <c r="M17" s="18">
         <f t="shared" si="0"/>
-        <v>9386</v>
+        <v>7752</v>
       </c>
       <c r="N17" s="18">
         <f t="shared" si="0"/>
-        <v>8390</v>
+        <v>7579</v>
       </c>
       <c r="O17" s="18">
         <f t="shared" si="0"/>
-        <v>7313</v>
+        <v>7068</v>
       </c>
       <c r="P17" s="18">
         <f t="shared" si="0"/>
-        <v>35300</v>
+        <v>30600</v>
       </c>
       <c r="Q17" s="18">
         <f t="shared" si="0"/>
-        <v>13200</v>
+        <v>12800</v>
       </c>
       <c r="R17" s="18"/>
-      <c r="T17" s="30"/>
+      <c r="T17" s="26"/>
       <c r="U17" s="24"/>
       <c r="V17" s="24"/>
       <c r="W17" s="24"/>
@@ -2583,61 +2679,62 @@
       <c r="AC17" s="25"/>
     </row>
     <row r="18" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="36" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="C18" s="36">
-        <v>1200</v>
+      <c r="A18" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="16">
+        <v>1666</v>
       </c>
       <c r="D18" s="10">
-        <v>6.78</v>
+        <v>9.3859999999999992</v>
       </c>
       <c r="E18" s="19">
-        <v>9.5239999999999991</v>
+        <v>8.39</v>
       </c>
       <c r="F18" s="10">
-        <v>9.1739999999999995</v>
+        <v>7.3129999999999997</v>
       </c>
       <c r="G18" s="11">
+        <v>35.299999999999997</v>
+      </c>
+      <c r="H18" s="11">
+        <v>13.2</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="11">
-        <v>16.5</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>10</v>
-      </c>
       <c r="J18" s="13">
-        <v>45298</v>
-      </c>
-      <c r="K18" s="34" t="s">
-        <v>224</v>
-      </c>
+        <v>41496</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L18" s="5"/>
       <c r="M18" s="18">
         <f t="shared" si="0"/>
-        <v>6780</v>
+        <v>9386</v>
       </c>
       <c r="N18" s="18">
         <f t="shared" si="0"/>
-        <v>9524</v>
+        <v>8390</v>
       </c>
       <c r="O18" s="18">
         <f t="shared" si="0"/>
-        <v>9174</v>
+        <v>7313</v>
       </c>
       <c r="P18" s="18">
         <f t="shared" si="0"/>
-        <v>33000</v>
+        <v>35300</v>
       </c>
       <c r="Q18" s="18">
         <f t="shared" si="0"/>
-        <v>16500</v>
+        <v>13200</v>
       </c>
       <c r="R18" s="18"/>
-      <c r="T18" s="30"/>
+      <c r="T18" s="26"/>
       <c r="U18" s="24"/>
       <c r="V18" s="24"/>
       <c r="W18" s="24"/>
@@ -2649,61 +2746,61 @@
       <c r="AC18" s="25"/>
     </row>
     <row r="19" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="B19" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="C19">
-        <v>1512</v>
+      <c r="A19" s="32" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="32">
+        <v>1200</v>
       </c>
       <c r="D19" s="10">
-        <v>4.5910000000000002</v>
+        <v>6.78</v>
       </c>
       <c r="E19" s="19">
-        <v>9.8949999999999996</v>
+        <v>9.5239999999999991</v>
       </c>
       <c r="F19" s="10">
-        <v>9.0860000000000003</v>
+        <v>9.1739999999999995</v>
       </c>
       <c r="G19" s="11">
-        <v>28.5</v>
+        <v>33</v>
       </c>
       <c r="H19" s="11">
-        <v>16.399999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="I19" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J19" s="13">
-        <v>42031</v>
-      </c>
-      <c r="K19" t="s">
-        <v>227</v>
+        <v>45298</v>
+      </c>
+      <c r="K19" s="30" t="s">
+        <v>224</v>
       </c>
       <c r="M19" s="18">
         <f t="shared" si="0"/>
-        <v>4591</v>
+        <v>6780</v>
       </c>
       <c r="N19" s="18">
         <f t="shared" si="0"/>
-        <v>9895</v>
+        <v>9524</v>
       </c>
       <c r="O19" s="18">
         <f t="shared" si="0"/>
-        <v>9086</v>
+        <v>9174</v>
       </c>
       <c r="P19" s="18">
         <f t="shared" si="0"/>
-        <v>28500</v>
+        <v>33000</v>
       </c>
       <c r="Q19" s="18">
         <f t="shared" si="0"/>
-        <v>16400</v>
+        <v>16500</v>
       </c>
       <c r="R19" s="18"/>
-      <c r="T19" s="30"/>
+      <c r="T19" s="26"/>
       <c r="U19" s="24"/>
       <c r="V19" s="24"/>
       <c r="W19" s="24"/>
@@ -2715,185 +2812,185 @@
       <c r="AC19" s="25"/>
     </row>
     <row r="20" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="36" t="s">
-        <v>182</v>
-      </c>
-      <c r="B20" s="36" t="s">
-        <v>183</v>
-      </c>
-      <c r="C20" s="36">
-        <v>1200</v>
+      <c r="A20" s="15" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20">
+        <v>1512</v>
       </c>
       <c r="D20" s="10">
-        <v>8.68</v>
+        <v>4.5910000000000002</v>
       </c>
       <c r="E20" s="19">
-        <v>10.948</v>
+        <v>9.8949999999999996</v>
       </c>
       <c r="F20" s="10">
-        <v>10.154999999999999</v>
+        <v>9.0860000000000003</v>
       </c>
       <c r="G20" s="11">
-        <v>39.718000000000004</v>
+        <v>28.5</v>
       </c>
       <c r="H20" s="11">
-        <v>18.309999999999999</v>
+        <v>16.399999999999999</v>
       </c>
       <c r="I20" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J20" s="13">
+        <v>42031</v>
+      </c>
+      <c r="K20" s="40" t="s">
+        <v>227</v>
+      </c>
+      <c r="M20" s="18">
+        <f t="shared" si="0"/>
+        <v>4591</v>
+      </c>
+      <c r="N20" s="18">
+        <f t="shared" si="0"/>
+        <v>9895</v>
+      </c>
+      <c r="O20" s="18">
+        <f t="shared" si="0"/>
+        <v>9086</v>
+      </c>
+      <c r="P20" s="18">
+        <f t="shared" si="0"/>
+        <v>28500</v>
+      </c>
+      <c r="Q20" s="18">
+        <f t="shared" si="0"/>
+        <v>16400</v>
+      </c>
+      <c r="R20" s="18"/>
+      <c r="T20" s="26"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="24"/>
+      <c r="AA20" s="24"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="25"/>
+    </row>
+    <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="32">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="10">
+        <v>8.68</v>
+      </c>
+      <c r="E21" s="19">
+        <v>10.948</v>
+      </c>
+      <c r="F21" s="10">
+        <v>10.154999999999999</v>
+      </c>
+      <c r="G21" s="11">
+        <v>39.718000000000004</v>
+      </c>
+      <c r="H21" s="11">
+        <v>18.309999999999999</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" s="13">
         <v>45319</v>
       </c>
-      <c r="K20" s="34" t="s">
+      <c r="K21" s="30" t="s">
         <v>224</v>
       </c>
-      <c r="M20" s="18">
+      <c r="M21" s="18">
         <f t="shared" si="0"/>
         <v>8680</v>
       </c>
-      <c r="N20" s="18">
+      <c r="N21" s="18">
         <f t="shared" si="0"/>
         <v>10948</v>
       </c>
-      <c r="O20" s="18">
+      <c r="O21" s="18">
         <f t="shared" si="0"/>
         <v>10155</v>
       </c>
-      <c r="P20" s="18">
+      <c r="P21" s="18">
         <f t="shared" si="0"/>
         <v>39718</v>
       </c>
-      <c r="Q20" s="18">
+      <c r="Q21" s="18">
         <f t="shared" si="0"/>
         <v>18310</v>
       </c>
-      <c r="R20" s="18"/>
-      <c r="T20" s="31"/>
-    </row>
-    <row r="21" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="R21" s="18"/>
+      <c r="T21" s="27"/>
+    </row>
+    <row r="22" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
         <v>111</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>103</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>1800</v>
       </c>
-      <c r="D21" s="10">
+      <c r="D22" s="10">
         <v>11.269</v>
       </c>
-      <c r="E21" s="19">
+      <c r="E22" s="19">
         <v>11.927</v>
       </c>
-      <c r="F21" s="10">
+      <c r="F22" s="10">
         <v>20.516999999999999</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G22" s="11">
         <v>46.6</v>
       </c>
-      <c r="H21" s="11">
+      <c r="H22" s="11">
         <v>37</v>
       </c>
-      <c r="I21" s="8" t="s">
+      <c r="I22" s="8" t="s">
         <v>187</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J22" s="13">
         <v>40672</v>
       </c>
-      <c r="K21" s="5" t="s">
+      <c r="K22" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="L21" s="5"/>
-      <c r="M21" s="18">
+      <c r="L22" s="5"/>
+      <c r="M22" s="18">
         <f t="shared" si="0"/>
         <v>11269</v>
       </c>
-      <c r="N21" s="18">
+      <c r="N22" s="18">
         <f t="shared" si="0"/>
         <v>11927</v>
       </c>
-      <c r="O21" s="18">
+      <c r="O22" s="18">
         <f t="shared" si="0"/>
         <v>20517</v>
       </c>
-      <c r="P21" s="18">
+      <c r="P22" s="18">
         <f t="shared" si="0"/>
         <v>46600</v>
       </c>
-      <c r="Q21" s="18">
+      <c r="Q22" s="18">
         <f t="shared" si="0"/>
         <v>37000</v>
       </c>
-      <c r="R21" s="18"/>
-      <c r="T21" s="30"/>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="24"/>
-      <c r="X21" s="24"/>
-      <c r="Y21" s="24"/>
-      <c r="Z21" s="24"/>
-      <c r="AA21" s="24"/>
-      <c r="AB21" s="24"/>
-      <c r="AC21" s="25"/>
-    </row>
-    <row r="22" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C22" s="16">
-        <v>2000</v>
-      </c>
-      <c r="D22" s="10">
-        <v>12.138</v>
-      </c>
-      <c r="E22" s="19">
-        <v>12.568</v>
-      </c>
-      <c r="F22" s="10">
-        <v>21.143999999999998</v>
-      </c>
-      <c r="G22" s="11">
-        <v>49.6</v>
-      </c>
-      <c r="H22" s="11">
-        <v>38.1</v>
-      </c>
-      <c r="I22" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="J22" s="13">
-        <v>39919</v>
-      </c>
-      <c r="K22" t="s">
-        <v>225</v>
-      </c>
-      <c r="M22" s="18">
-        <f t="shared" si="0"/>
-        <v>12138</v>
-      </c>
-      <c r="N22" s="18">
-        <f t="shared" si="0"/>
-        <v>12568</v>
-      </c>
-      <c r="O22" s="18">
-        <f t="shared" si="0"/>
-        <v>21144</v>
-      </c>
-      <c r="P22" s="18">
-        <f t="shared" si="0"/>
-        <v>49600</v>
-      </c>
-      <c r="Q22" s="18">
-        <f t="shared" si="0"/>
-        <v>38100</v>
-      </c>
       <c r="R22" s="18"/>
-      <c r="T22" s="30"/>
+      <c r="T22" s="26"/>
       <c r="U22" s="24"/>
       <c r="V22" s="24"/>
       <c r="W22" s="24"/>
@@ -2906,61 +3003,60 @@
     </row>
     <row r="23" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C23" s="16">
-        <v>1860</v>
+        <v>2000</v>
       </c>
       <c r="D23" s="10">
-        <v>18.433</v>
+        <v>12.138</v>
       </c>
       <c r="E23" s="19">
-        <v>15.15</v>
+        <v>12.568</v>
       </c>
       <c r="F23" s="10">
-        <v>16.635999999999999</v>
+        <v>21.143999999999998</v>
       </c>
       <c r="G23" s="11">
-        <v>66</v>
+        <v>49.6</v>
       </c>
       <c r="H23" s="11">
-        <v>30</v>
+        <v>38.1</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J23" s="13">
-        <v>41788</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L23" s="5"/>
+        <v>39919</v>
+      </c>
+      <c r="K23" s="17" t="s">
+        <v>225</v>
+      </c>
       <c r="M23" s="18">
         <f t="shared" si="0"/>
-        <v>18433</v>
+        <v>12138</v>
       </c>
       <c r="N23" s="18">
         <f t="shared" si="0"/>
-        <v>15150</v>
+        <v>12568</v>
       </c>
       <c r="O23" s="18">
         <f t="shared" si="0"/>
-        <v>16636</v>
+        <v>21144</v>
       </c>
       <c r="P23" s="18">
         <f t="shared" si="0"/>
-        <v>66000</v>
+        <v>49600</v>
       </c>
       <c r="Q23" s="18">
         <f t="shared" si="0"/>
-        <v>30000</v>
+        <v>38100</v>
       </c>
       <c r="R23" s="18"/>
-      <c r="T23" s="30"/>
+      <c r="T23" s="26"/>
       <c r="U23" s="24"/>
       <c r="V23" s="24"/>
       <c r="W23" s="24"/>
@@ -2972,158 +3068,158 @@
       <c r="AC23" s="25"/>
     </row>
     <row r="24" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36" t="s">
-        <v>231</v>
-      </c>
-      <c r="B24" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="C24" s="36">
-        <v>1400</v>
+      <c r="A24" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="16">
+        <v>1860</v>
       </c>
       <c r="D24" s="10">
-        <v>14.398999999999999</v>
+        <v>18.433</v>
       </c>
       <c r="E24" s="19">
-        <v>15.946999999999999</v>
+        <v>15.15</v>
       </c>
       <c r="F24" s="10">
-        <v>17.788</v>
+        <v>16.635999999999999</v>
       </c>
       <c r="G24" s="11">
-        <v>61.170999999999999</v>
+        <v>66</v>
       </c>
       <c r="H24" s="11">
-        <v>32.072000000000003</v>
-      </c>
-      <c r="I24" s="8"/>
+        <v>30</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>189</v>
+      </c>
       <c r="J24" s="13">
-        <v>45772</v>
-      </c>
-      <c r="K24" s="33" t="s">
-        <v>224</v>
+        <v>41788</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>223</v>
       </c>
       <c r="L24" s="5"/>
       <c r="M24" s="18">
         <f t="shared" si="0"/>
-        <v>14399</v>
+        <v>18433</v>
       </c>
       <c r="N24" s="18">
         <f t="shared" si="0"/>
-        <v>15947</v>
+        <v>15150</v>
       </c>
       <c r="O24" s="18">
         <f t="shared" si="0"/>
-        <v>17788</v>
+        <v>16636</v>
       </c>
       <c r="P24" s="18">
         <f t="shared" si="0"/>
-        <v>61171</v>
+        <v>66000</v>
       </c>
       <c r="Q24" s="18">
         <f t="shared" si="0"/>
-        <v>32072.000000000004</v>
+        <v>30000</v>
       </c>
       <c r="R24" s="18"/>
-      <c r="T24" s="31"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="24"/>
+      <c r="V24" s="24"/>
+      <c r="W24" s="24"/>
+      <c r="X24" s="24"/>
+      <c r="Y24" s="24"/>
+      <c r="Z24" s="24"/>
+      <c r="AA24" s="24"/>
+      <c r="AB24" s="24"/>
+      <c r="AC24" s="25"/>
     </row>
     <row r="25" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>111</v>
-      </c>
-      <c r="B25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C25">
-        <v>1800</v>
+      <c r="A25" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="32">
+        <v>1400</v>
       </c>
       <c r="D25" s="10">
-        <v>13.595000000000001</v>
+        <v>14.398999999999999</v>
       </c>
       <c r="E25" s="19">
-        <v>16.120999999999999</v>
+        <v>15.946999999999999</v>
       </c>
       <c r="F25" s="10">
-        <v>19.565999999999999</v>
+        <v>17.788</v>
       </c>
       <c r="G25" s="11">
-        <v>59.9</v>
+        <v>61.170999999999999</v>
       </c>
       <c r="H25" s="11">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>190</v>
-      </c>
+        <v>32.072000000000003</v>
+      </c>
+      <c r="I25" s="8"/>
       <c r="J25" s="13">
-        <v>40672</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>223</v>
+        <v>45772</v>
+      </c>
+      <c r="K25" s="29" t="s">
+        <v>224</v>
       </c>
       <c r="L25" s="5"/>
       <c r="M25" s="18">
         <f t="shared" si="0"/>
-        <v>13595</v>
+        <v>14399</v>
       </c>
       <c r="N25" s="18">
         <f t="shared" si="0"/>
-        <v>16120.999999999998</v>
+        <v>15947</v>
       </c>
       <c r="O25" s="18">
         <f t="shared" si="0"/>
-        <v>19566</v>
+        <v>17788</v>
       </c>
       <c r="P25" s="18">
         <f t="shared" si="0"/>
-        <v>59900</v>
+        <v>61171</v>
       </c>
       <c r="Q25" s="18">
         <f t="shared" si="0"/>
-        <v>35300</v>
+        <v>32072.000000000004</v>
       </c>
       <c r="R25" s="18"/>
-      <c r="T25" s="30"/>
-      <c r="U25" s="24"/>
-      <c r="V25" s="24"/>
-      <c r="W25" s="24"/>
-      <c r="X25" s="24"/>
-      <c r="Y25" s="24"/>
-      <c r="Z25" s="24"/>
-      <c r="AA25" s="24"/>
-      <c r="AB25" s="24"/>
-      <c r="AC25" s="25"/>
+      <c r="T25" s="27"/>
     </row>
     <row r="26" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="16" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C26" s="16">
-        <v>1580</v>
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26">
+        <v>1800</v>
       </c>
       <c r="D26" s="10">
-        <v>19.981000000000002</v>
+        <v>13.595000000000001</v>
       </c>
       <c r="E26" s="19">
-        <v>16.207000000000001</v>
+        <v>16.120999999999999</v>
       </c>
       <c r="F26" s="10">
-        <v>18.001000000000001</v>
+        <v>19.565999999999999</v>
       </c>
       <c r="G26" s="11">
-        <v>71</v>
+        <v>59.9</v>
       </c>
       <c r="H26" s="11">
-        <v>32.5</v>
+        <v>35.299999999999997</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J26" s="13">
-        <v>41851</v>
+        <v>40672</v>
       </c>
       <c r="K26" s="5" t="s">
         <v>223</v>
@@ -3131,26 +3227,26 @@
       <c r="L26" s="5"/>
       <c r="M26" s="18">
         <f t="shared" si="0"/>
-        <v>19981</v>
+        <v>13595</v>
       </c>
       <c r="N26" s="18">
         <f t="shared" si="0"/>
-        <v>16207</v>
+        <v>16120.999999999998</v>
       </c>
       <c r="O26" s="18">
         <f t="shared" si="0"/>
-        <v>18001</v>
+        <v>19566</v>
       </c>
       <c r="P26" s="18">
         <f t="shared" si="0"/>
-        <v>71000</v>
+        <v>59900</v>
       </c>
       <c r="Q26" s="18">
         <f t="shared" si="0"/>
-        <v>32500</v>
+        <v>35300</v>
       </c>
       <c r="R26" s="18"/>
-      <c r="T26" s="30"/>
+      <c r="T26" s="26"/>
       <c r="U26" s="24"/>
       <c r="V26" s="24"/>
       <c r="W26" s="24"/>
@@ -3163,34 +3259,34 @@
     </row>
     <row r="27" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="16" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
       <c r="B27" s="16" t="s">
-        <v>122</v>
+        <v>107</v>
       </c>
       <c r="C27" s="16">
-        <v>1299</v>
+        <v>1580</v>
       </c>
       <c r="D27" s="10">
-        <v>19.050999999999998</v>
+        <v>19.981000000000002</v>
       </c>
       <c r="E27" s="19">
-        <v>17.286000000000001</v>
+        <v>16.207000000000001</v>
       </c>
       <c r="F27" s="10">
-        <v>25.289000000000001</v>
+        <v>18.001000000000001</v>
       </c>
       <c r="G27" s="11">
-        <v>72.2</v>
+        <v>71</v>
       </c>
       <c r="H27" s="11">
-        <v>45.6</v>
+        <v>32.5</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>10</v>
+        <v>191</v>
       </c>
       <c r="J27" s="13">
-        <v>41861</v>
+        <v>41851</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>223</v>
@@ -3198,26 +3294,26 @@
       <c r="L27" s="5"/>
       <c r="M27" s="18">
         <f t="shared" si="0"/>
-        <v>19051</v>
+        <v>19981</v>
       </c>
       <c r="N27" s="18">
         <f t="shared" si="0"/>
-        <v>17286</v>
+        <v>16207</v>
       </c>
       <c r="O27" s="18">
         <f t="shared" si="0"/>
-        <v>25289</v>
+        <v>18001</v>
       </c>
       <c r="P27" s="18">
         <f t="shared" si="0"/>
-        <v>72200</v>
+        <v>71000</v>
       </c>
       <c r="Q27" s="18">
         <f t="shared" si="0"/>
-        <v>45600</v>
+        <v>32500</v>
       </c>
       <c r="R27" s="18"/>
-      <c r="T27" s="30"/>
+      <c r="T27" s="26"/>
       <c r="U27" s="24"/>
       <c r="V27" s="24"/>
       <c r="W27" s="24"/>
@@ -3229,35 +3325,35 @@
       <c r="AC27" s="25"/>
     </row>
     <row r="28" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
-        <v>137</v>
-      </c>
-      <c r="B28" t="s">
-        <v>110</v>
-      </c>
-      <c r="C28">
-        <v>2527</v>
+      <c r="A28" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="16">
+        <v>1299</v>
       </c>
       <c r="D28" s="10">
-        <v>28.488</v>
+        <v>19.050999999999998</v>
       </c>
       <c r="E28" s="19">
-        <v>17.780999999999999</v>
+        <v>17.286000000000001</v>
       </c>
       <c r="F28" s="10">
-        <v>36.673000000000002</v>
+        <v>25.289000000000001</v>
       </c>
       <c r="G28" s="11">
-        <v>87.2</v>
+        <v>72.2</v>
       </c>
       <c r="H28" s="11">
-        <v>66.099999999999994</v>
+        <v>45.6</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>192</v>
+        <v>10</v>
       </c>
       <c r="J28" s="13">
-        <v>41457</v>
+        <v>41861</v>
       </c>
       <c r="K28" s="5" t="s">
         <v>223</v>
@@ -3265,26 +3361,26 @@
       <c r="L28" s="5"/>
       <c r="M28" s="18">
         <f t="shared" si="0"/>
-        <v>28488</v>
+        <v>19051</v>
       </c>
       <c r="N28" s="18">
         <f t="shared" si="0"/>
-        <v>17781</v>
+        <v>17286</v>
       </c>
       <c r="O28" s="18">
         <f t="shared" si="0"/>
-        <v>36673</v>
+        <v>25289</v>
       </c>
       <c r="P28" s="18">
         <f t="shared" si="0"/>
-        <v>87200</v>
+        <v>72200</v>
       </c>
       <c r="Q28" s="18">
         <f t="shared" si="0"/>
-        <v>66100</v>
+        <v>45600</v>
       </c>
       <c r="R28" s="18"/>
-      <c r="T28" s="30"/>
+      <c r="T28" s="26"/>
       <c r="U28" s="24"/>
       <c r="V28" s="24"/>
       <c r="W28" s="24"/>
@@ -3296,35 +3392,35 @@
       <c r="AC28" s="25"/>
     </row>
     <row r="29" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="17">
-        <v>1600</v>
+      <c r="A29" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29">
+        <v>2527</v>
       </c>
       <c r="D29" s="10">
-        <v>23.695</v>
+        <v>28.488</v>
       </c>
       <c r="E29" s="19">
-        <v>17.817</v>
+        <v>17.780999999999999</v>
       </c>
       <c r="F29" s="10">
-        <v>25.515999999999998</v>
+        <v>36.673000000000002</v>
       </c>
       <c r="G29" s="11">
-        <v>80.7</v>
+        <v>87.2</v>
       </c>
       <c r="H29" s="11">
-        <v>46</v>
+        <v>66.099999999999994</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>210</v>
+        <v>192</v>
       </c>
       <c r="J29" s="13">
-        <v>44089</v>
+        <v>41457</v>
       </c>
       <c r="K29" s="5" t="s">
         <v>223</v>
@@ -3332,26 +3428,26 @@
       <c r="L29" s="5"/>
       <c r="M29" s="18">
         <f t="shared" si="0"/>
-        <v>23695</v>
+        <v>28488</v>
       </c>
       <c r="N29" s="18">
         <f t="shared" si="0"/>
-        <v>17817</v>
+        <v>17781</v>
       </c>
       <c r="O29" s="18">
         <f t="shared" si="0"/>
-        <v>25516</v>
+        <v>36673</v>
       </c>
       <c r="P29" s="18">
         <f t="shared" si="0"/>
-        <v>80700</v>
+        <v>87200</v>
       </c>
       <c r="Q29" s="18">
         <f t="shared" si="0"/>
-        <v>46000</v>
+        <v>66100</v>
       </c>
       <c r="R29" s="18"/>
-      <c r="T29" s="30"/>
+      <c r="T29" s="26"/>
       <c r="U29" s="24"/>
       <c r="V29" s="24"/>
       <c r="W29" s="24"/>
@@ -3363,35 +3459,35 @@
       <c r="AC29" s="25"/>
     </row>
     <row r="30" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C30" s="16">
-        <v>1400</v>
+      <c r="A30" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="17">
+        <v>1600</v>
       </c>
       <c r="D30" s="10">
-        <v>18.776</v>
+        <v>23.695</v>
       </c>
       <c r="E30" s="19">
-        <v>17.878</v>
+        <v>17.817</v>
       </c>
       <c r="F30" s="10">
-        <v>29.106000000000002</v>
+        <v>25.515999999999998</v>
       </c>
       <c r="G30" s="11">
-        <v>73.2</v>
+        <v>80.7</v>
       </c>
       <c r="H30" s="11">
-        <v>52.5</v>
+        <v>46</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>10</v>
+        <v>210</v>
       </c>
       <c r="J30" s="13">
-        <v>43641</v>
+        <v>44089</v>
       </c>
       <c r="K30" s="5" t="s">
         <v>223</v>
@@ -3399,26 +3495,26 @@
       <c r="L30" s="5"/>
       <c r="M30" s="18">
         <f t="shared" si="0"/>
-        <v>18776</v>
+        <v>23695</v>
       </c>
       <c r="N30" s="18">
         <f t="shared" si="0"/>
-        <v>17878</v>
+        <v>17817</v>
       </c>
       <c r="O30" s="18">
         <f t="shared" si="0"/>
-        <v>29106</v>
+        <v>25516</v>
       </c>
       <c r="P30" s="18">
         <f t="shared" si="0"/>
-        <v>73200</v>
+        <v>80700</v>
       </c>
       <c r="Q30" s="18">
         <f t="shared" si="0"/>
-        <v>52500</v>
+        <v>46000</v>
       </c>
       <c r="R30" s="18"/>
-      <c r="T30" s="30"/>
+      <c r="T30" s="26"/>
       <c r="U30" s="24"/>
       <c r="V30" s="24"/>
       <c r="W30" s="24"/>
@@ -3430,64 +3526,62 @@
       <c r="AC30" s="25"/>
     </row>
     <row r="31" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
-        <v>212</v>
-      </c>
-      <c r="B31" s="36" t="s">
-        <v>213</v>
-      </c>
-      <c r="C31" s="36">
-        <v>1500</v>
+      <c r="A31" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="16">
+        <v>1400</v>
       </c>
       <c r="D31" s="10">
-        <v>15.319000000000001</v>
+        <v>18.776</v>
       </c>
       <c r="E31" s="19">
-        <v>18.061</v>
+        <v>17.878</v>
       </c>
       <c r="F31" s="10">
-        <v>34.619999999999997</v>
+        <v>29.106000000000002</v>
       </c>
       <c r="G31" s="11">
-        <v>67.400000000000006</v>
+        <v>73.2</v>
       </c>
       <c r="H31" s="11">
-        <v>62.4</v>
+        <v>52.5</v>
       </c>
       <c r="I31" s="8" t="s">
         <v>10</v>
       </c>
       <c r="J31" s="13">
-        <v>45561</v>
-      </c>
-      <c r="K31" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="L31" t="s">
-        <v>256</v>
-      </c>
+        <v>43641</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L31" s="5"/>
       <c r="M31" s="18">
         <f t="shared" si="0"/>
-        <v>15319</v>
+        <v>18776</v>
       </c>
       <c r="N31" s="18">
         <f t="shared" si="0"/>
-        <v>18061</v>
+        <v>17878</v>
       </c>
       <c r="O31" s="18">
         <f t="shared" si="0"/>
-        <v>34620</v>
+        <v>29106</v>
       </c>
       <c r="P31" s="18">
         <f t="shared" si="0"/>
-        <v>67400</v>
+        <v>73200</v>
       </c>
       <c r="Q31" s="18">
         <f t="shared" si="0"/>
-        <v>62400</v>
+        <v>52500</v>
       </c>
       <c r="R31" s="18"/>
-      <c r="T31" s="30"/>
+      <c r="T31" s="26"/>
       <c r="U31" s="24"/>
       <c r="V31" s="24"/>
       <c r="W31" s="24"/>
@@ -3499,62 +3593,64 @@
       <c r="AC31" s="25"/>
     </row>
     <row r="32" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32">
-        <v>2607</v>
+      <c r="A32" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="32">
+        <v>1500</v>
       </c>
       <c r="D32" s="10">
-        <v>18.265000000000001</v>
+        <v>15.319000000000001</v>
       </c>
       <c r="E32" s="19">
-        <v>18.957999999999998</v>
+        <v>18.061</v>
       </c>
       <c r="F32" s="10">
-        <v>31.843</v>
+        <v>34.619999999999997</v>
       </c>
       <c r="G32" s="11">
-        <v>74.8</v>
+        <v>67.400000000000006</v>
       </c>
       <c r="H32" s="11">
-        <v>57.4</v>
+        <v>62.4</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>193</v>
+        <v>10</v>
       </c>
       <c r="J32" s="13">
-        <v>41151</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L32" s="5"/>
+        <v>45561</v>
+      </c>
+      <c r="K32" s="30" t="s">
+        <v>224</v>
+      </c>
+      <c r="L32" t="s">
+        <v>256</v>
+      </c>
       <c r="M32" s="18">
         <f t="shared" si="0"/>
-        <v>18265</v>
+        <v>15319</v>
       </c>
       <c r="N32" s="18">
         <f t="shared" si="0"/>
-        <v>18958</v>
+        <v>18061</v>
       </c>
       <c r="O32" s="18">
         <f t="shared" si="0"/>
-        <v>31843</v>
+        <v>34620</v>
       </c>
       <c r="P32" s="18">
         <f t="shared" si="0"/>
-        <v>74800</v>
+        <v>67400</v>
       </c>
       <c r="Q32" s="18">
         <f t="shared" si="0"/>
-        <v>57400</v>
+        <v>62400</v>
       </c>
       <c r="R32" s="18"/>
-      <c r="T32" s="30"/>
+      <c r="T32" s="26"/>
       <c r="U32" s="24"/>
       <c r="V32" s="24"/>
       <c r="W32" s="24"/>
@@ -3567,34 +3663,34 @@
     </row>
     <row r="33" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B33" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C33">
-        <v>2100</v>
+        <v>2607</v>
       </c>
       <c r="D33" s="10">
-        <v>14.395</v>
+        <v>18.265000000000001</v>
       </c>
       <c r="E33" s="19">
-        <v>19.298999999999999</v>
+        <v>18.957999999999998</v>
       </c>
       <c r="F33" s="10">
-        <v>23.132000000000001</v>
+        <v>31.843</v>
       </c>
       <c r="G33" s="11">
-        <v>68.2</v>
+        <v>74.8</v>
       </c>
       <c r="H33" s="11">
-        <v>41.7</v>
+        <v>57.4</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>43</v>
+        <v>193</v>
       </c>
       <c r="J33" s="13">
-        <v>40060</v>
+        <v>41151</v>
       </c>
       <c r="K33" s="5" t="s">
         <v>223</v>
@@ -3602,26 +3698,26 @@
       <c r="L33" s="5"/>
       <c r="M33" s="18">
         <f t="shared" si="0"/>
-        <v>14395</v>
+        <v>18265</v>
       </c>
       <c r="N33" s="18">
         <f t="shared" si="0"/>
-        <v>19299</v>
+        <v>18958</v>
       </c>
       <c r="O33" s="18">
         <f t="shared" si="0"/>
-        <v>23132</v>
+        <v>31843</v>
       </c>
       <c r="P33" s="18">
         <f t="shared" si="0"/>
-        <v>68200</v>
+        <v>74800</v>
       </c>
       <c r="Q33" s="18">
         <f t="shared" si="0"/>
-        <v>41700</v>
+        <v>57400</v>
       </c>
       <c r="R33" s="18"/>
-      <c r="T33" s="30"/>
+      <c r="T33" s="26"/>
       <c r="U33" s="24"/>
       <c r="V33" s="24"/>
       <c r="W33" s="24"/>
@@ -3633,35 +3729,35 @@
       <c r="AC33" s="25"/>
     </row>
     <row r="34" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C34" s="16">
-        <v>2266</v>
+      <c r="A34" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34">
+        <v>2100</v>
       </c>
       <c r="D34" s="10">
-        <v>28.631</v>
+        <v>14.395</v>
       </c>
       <c r="E34" s="19">
-        <v>19.780999999999999</v>
+        <v>19.298999999999999</v>
       </c>
       <c r="F34" s="10">
-        <v>31.140999999999998</v>
+        <v>23.132000000000001</v>
       </c>
       <c r="G34" s="11">
-        <v>92.9</v>
+        <v>68.2</v>
       </c>
       <c r="H34" s="11">
-        <v>56.1</v>
+        <v>41.7</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>206</v>
+        <v>43</v>
       </c>
       <c r="J34" s="13">
-        <v>42713</v>
+        <v>40060</v>
       </c>
       <c r="K34" s="5" t="s">
         <v>223</v>
@@ -3669,26 +3765,26 @@
       <c r="L34" s="5"/>
       <c r="M34" s="18">
         <f t="shared" si="0"/>
-        <v>28631</v>
+        <v>14395</v>
       </c>
       <c r="N34" s="18">
         <f t="shared" si="0"/>
-        <v>19781</v>
+        <v>19299</v>
       </c>
       <c r="O34" s="18">
         <f t="shared" si="0"/>
-        <v>31141</v>
+        <v>23132</v>
       </c>
       <c r="P34" s="18">
         <f t="shared" si="0"/>
-        <v>92900</v>
+        <v>68200</v>
       </c>
       <c r="Q34" s="18">
         <f t="shared" si="0"/>
-        <v>56100</v>
+        <v>41700</v>
       </c>
       <c r="R34" s="18"/>
-      <c r="T34" s="30"/>
+      <c r="T34" s="26"/>
       <c r="U34" s="24"/>
       <c r="V34" s="24"/>
       <c r="W34" s="24"/>
@@ -3700,64 +3796,62 @@
       <c r="AC34" s="25"/>
     </row>
     <row r="35" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="C35" s="15">
-        <v>2400</v>
+      <c r="A35" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="16">
+        <v>2266</v>
       </c>
       <c r="D35" s="10">
-        <v>23.448</v>
+        <v>28.631</v>
       </c>
       <c r="E35" s="19">
-        <v>32.408000000000001</v>
+        <v>19.780999999999999</v>
       </c>
       <c r="F35" s="10">
-        <v>50.741999999999997</v>
+        <v>31.140999999999998</v>
       </c>
       <c r="G35" s="11">
-        <v>113.1</v>
+        <v>92.9</v>
       </c>
       <c r="H35" s="11">
-        <v>91.5</v>
+        <v>56.1</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>10</v>
+        <v>206</v>
       </c>
       <c r="J35" s="13">
-        <v>46116</v>
-      </c>
-      <c r="K35" s="33" t="s">
-        <v>224</v>
-      </c>
-      <c r="L35" s="5" t="s">
-        <v>248</v>
-      </c>
+        <v>42713</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L35" s="5"/>
       <c r="M35" s="18">
-        <f t="shared" ref="M35:Q35" si="1">D35*1000</f>
-        <v>23448</v>
+        <f t="shared" si="0"/>
+        <v>28631</v>
       </c>
       <c r="N35" s="18">
-        <f t="shared" si="1"/>
-        <v>32408</v>
+        <f t="shared" si="0"/>
+        <v>19781</v>
       </c>
       <c r="O35" s="18">
-        <f t="shared" si="1"/>
-        <v>50742</v>
+        <f t="shared" si="0"/>
+        <v>31141</v>
       </c>
       <c r="P35" s="18">
-        <f t="shared" si="1"/>
-        <v>113100</v>
+        <f t="shared" si="0"/>
+        <v>92900</v>
       </c>
       <c r="Q35" s="18">
-        <f t="shared" si="1"/>
-        <v>91500</v>
+        <f t="shared" si="0"/>
+        <v>56100</v>
       </c>
       <c r="R35" s="18"/>
-      <c r="T35" s="30"/>
+      <c r="T35" s="26"/>
       <c r="U35" s="24"/>
       <c r="V35" s="24"/>
       <c r="W35" s="24"/>
@@ -3769,62 +3863,64 @@
       <c r="AC35" s="25"/>
     </row>
     <row r="36" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="16" t="s">
-        <v>163</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" s="16">
-        <v>2043</v>
+      <c r="A36" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="15">
+        <v>2400</v>
       </c>
       <c r="D36" s="10">
-        <v>19.359000000000002</v>
+        <v>23.448</v>
       </c>
       <c r="E36" s="19">
-        <v>19.808</v>
+        <v>32.408000000000001</v>
       </c>
       <c r="F36" s="10">
-        <v>33.182000000000002</v>
+        <v>50.741999999999997</v>
       </c>
       <c r="G36" s="11">
-        <v>78.599999999999994</v>
+        <v>113.1</v>
       </c>
       <c r="H36" s="11">
-        <v>59.8</v>
+        <v>91.5</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>205</v>
+        <v>10</v>
       </c>
       <c r="J36" s="13">
-        <v>41919</v>
-      </c>
-      <c r="K36" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="L36" s="5"/>
+        <v>46116</v>
+      </c>
+      <c r="K36" s="29" t="s">
+        <v>224</v>
+      </c>
+      <c r="L36" s="5" t="s">
+        <v>248</v>
+      </c>
       <c r="M36" s="18">
-        <f t="shared" si="0"/>
-        <v>19359</v>
+        <f t="shared" ref="M36:Q36" si="2">D36*1000</f>
+        <v>23448</v>
       </c>
       <c r="N36" s="18">
-        <f t="shared" si="0"/>
-        <v>19808</v>
+        <f t="shared" si="2"/>
+        <v>32408</v>
       </c>
       <c r="O36" s="18">
-        <f t="shared" si="0"/>
-        <v>33182</v>
+        <f t="shared" si="2"/>
+        <v>50742</v>
       </c>
       <c r="P36" s="18">
-        <f t="shared" si="0"/>
-        <v>78600</v>
+        <f t="shared" si="2"/>
+        <v>113100</v>
       </c>
       <c r="Q36" s="18">
-        <f t="shared" si="0"/>
-        <v>59800</v>
+        <f t="shared" si="2"/>
+        <v>91500</v>
       </c>
       <c r="R36" s="18"/>
-      <c r="T36" s="30"/>
+      <c r="T36" s="26"/>
       <c r="U36" s="24"/>
       <c r="V36" s="24"/>
       <c r="W36" s="24"/>
@@ -3836,35 +3932,35 @@
       <c r="AC36" s="25"/>
     </row>
     <row r="37" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>135</v>
-      </c>
-      <c r="B37" t="s">
-        <v>133</v>
-      </c>
-      <c r="C37">
-        <v>2832</v>
+      <c r="A37" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" s="16">
+        <v>2043</v>
       </c>
       <c r="D37" s="10">
-        <v>33.670999999999999</v>
+        <v>19.359000000000002</v>
       </c>
       <c r="E37" s="19">
-        <v>23.584</v>
+        <v>19.808</v>
       </c>
       <c r="F37" s="10">
-        <v>36.384</v>
+        <v>33.182000000000002</v>
       </c>
       <c r="G37" s="11">
-        <v>110.1</v>
+        <v>78.599999999999994</v>
       </c>
       <c r="H37" s="11">
-        <v>65.599999999999994</v>
+        <v>59.8</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J37" s="13">
-        <v>42443</v>
+        <v>41919</v>
       </c>
       <c r="K37" s="5" t="s">
         <v>223</v>
@@ -3872,26 +3968,26 @@
       <c r="L37" s="5"/>
       <c r="M37" s="18">
         <f t="shared" si="0"/>
-        <v>33671</v>
+        <v>19359</v>
       </c>
       <c r="N37" s="18">
         <f t="shared" si="0"/>
-        <v>23584</v>
+        <v>19808</v>
       </c>
       <c r="O37" s="18">
         <f t="shared" si="0"/>
-        <v>36384</v>
+        <v>33182</v>
       </c>
       <c r="P37" s="18">
         <f t="shared" si="0"/>
-        <v>110100</v>
+        <v>78600</v>
       </c>
       <c r="Q37" s="18">
         <f t="shared" si="0"/>
-        <v>65600</v>
+        <v>59800</v>
       </c>
       <c r="R37" s="18"/>
-      <c r="T37" s="30"/>
+      <c r="T37" s="26"/>
       <c r="U37" s="24"/>
       <c r="V37" s="24"/>
       <c r="W37" s="24"/>
@@ -3904,34 +4000,34 @@
     </row>
     <row r="38" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c r="B38" t="s">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="C38">
-        <v>3066</v>
+        <v>2832</v>
       </c>
       <c r="D38" s="10">
-        <v>28.776</v>
+        <v>33.670999999999999</v>
       </c>
       <c r="E38" s="19">
-        <v>23.881</v>
+        <v>23.584</v>
       </c>
       <c r="F38" s="10">
-        <v>47.396000000000001</v>
+        <v>36.384</v>
       </c>
       <c r="G38" s="11">
-        <v>103.658</v>
+        <v>110.1</v>
       </c>
       <c r="H38" s="11">
-        <v>85.453000000000003</v>
+        <v>65.599999999999994</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J38" s="13">
-        <v>44691</v>
+        <v>42443</v>
       </c>
       <c r="K38" s="5" t="s">
         <v>223</v>
@@ -3939,26 +4035,26 @@
       <c r="L38" s="5"/>
       <c r="M38" s="18">
         <f t="shared" si="0"/>
-        <v>28776</v>
+        <v>33671</v>
       </c>
       <c r="N38" s="18">
         <f t="shared" si="0"/>
-        <v>23881</v>
+        <v>23584</v>
       </c>
       <c r="O38" s="18">
         <f t="shared" si="0"/>
-        <v>47396</v>
+        <v>36384</v>
       </c>
       <c r="P38" s="18">
         <f t="shared" si="0"/>
-        <v>103658</v>
+        <v>110100</v>
       </c>
       <c r="Q38" s="18">
         <f t="shared" si="0"/>
-        <v>85453</v>
+        <v>65600</v>
       </c>
       <c r="R38" s="18"/>
-      <c r="T38" s="30"/>
+      <c r="T38" s="26"/>
       <c r="U38" s="24"/>
       <c r="V38" s="24"/>
       <c r="W38" s="24"/>
@@ -3971,34 +4067,34 @@
     </row>
     <row r="39" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>175</v>
       </c>
       <c r="C39">
-        <v>3200</v>
+        <v>3066</v>
       </c>
       <c r="D39" s="10">
-        <v>37.845999999999997</v>
+        <v>28.776</v>
       </c>
       <c r="E39" s="19">
-        <v>23.882000000000001</v>
+        <v>23.881</v>
       </c>
       <c r="F39" s="10">
-        <v>47.436999999999998</v>
+        <v>47.396000000000001</v>
       </c>
       <c r="G39" s="11">
-        <v>116.6</v>
+        <v>103.658</v>
       </c>
       <c r="H39" s="11">
-        <v>85.5</v>
+        <v>85.453000000000003</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>10</v>
+        <v>203</v>
       </c>
       <c r="J39" s="13">
-        <v>41537</v>
+        <v>44691</v>
       </c>
       <c r="K39" s="5" t="s">
         <v>223</v>
@@ -4006,26 +4102,26 @@
       <c r="L39" s="5"/>
       <c r="M39" s="18">
         <f t="shared" si="0"/>
-        <v>37846</v>
+        <v>28776</v>
       </c>
       <c r="N39" s="18">
         <f t="shared" si="0"/>
-        <v>23882</v>
+        <v>23881</v>
       </c>
       <c r="O39" s="18">
         <f t="shared" si="0"/>
-        <v>47437</v>
+        <v>47396</v>
       </c>
       <c r="P39" s="18">
         <f t="shared" si="0"/>
-        <v>116600</v>
+        <v>103658</v>
       </c>
       <c r="Q39" s="18">
         <f t="shared" si="0"/>
-        <v>85500</v>
+        <v>85453</v>
       </c>
       <c r="R39" s="18"/>
-      <c r="T39" s="30"/>
+      <c r="T39" s="26"/>
       <c r="U39" s="24"/>
       <c r="V39" s="24"/>
       <c r="W39" s="24"/>
@@ -4038,34 +4134,34 @@
     </row>
     <row r="40" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C40">
-        <v>2667</v>
+        <v>3200</v>
       </c>
       <c r="D40" s="10">
-        <v>24.206</v>
+        <v>37.845999999999997</v>
       </c>
       <c r="E40" s="19">
-        <v>24.602</v>
+        <v>23.882000000000001</v>
       </c>
       <c r="F40" s="10">
-        <v>41.085000000000001</v>
-      </c>
-      <c r="G40" s="11" t="s">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="G40" s="11">
+        <v>116.6</v>
+      </c>
+      <c r="H40" s="11">
+        <v>85.5</v>
+      </c>
+      <c r="I40" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H40" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I40" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="J40" s="13">
-        <v>40683</v>
+        <v>41537</v>
       </c>
       <c r="K40" s="5" t="s">
         <v>223</v>
@@ -4073,20 +4169,26 @@
       <c r="L40" s="5"/>
       <c r="M40" s="18">
         <f t="shared" si="0"/>
-        <v>24206</v>
+        <v>37846</v>
       </c>
       <c r="N40" s="18">
         <f t="shared" si="0"/>
-        <v>24602</v>
+        <v>23882</v>
       </c>
       <c r="O40" s="18">
         <f t="shared" si="0"/>
-        <v>41085</v>
-      </c>
-      <c r="P40" s="18"/>
-      <c r="Q40" s="18"/>
+        <v>47437</v>
+      </c>
+      <c r="P40" s="18">
+        <f t="shared" si="0"/>
+        <v>116600</v>
+      </c>
+      <c r="Q40" s="18">
+        <f t="shared" si="0"/>
+        <v>85500</v>
+      </c>
       <c r="R40" s="18"/>
-      <c r="T40" s="30"/>
+      <c r="T40" s="26"/>
       <c r="U40" s="24"/>
       <c r="V40" s="24"/>
       <c r="W40" s="24"/>
@@ -4099,34 +4201,34 @@
     </row>
     <row r="41" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>186</v>
+        <v>151</v>
       </c>
       <c r="B41" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C41">
-        <v>2829</v>
+        <v>2667</v>
       </c>
       <c r="D41" s="10">
-        <v>21.475999999999999</v>
+        <v>24.206</v>
       </c>
       <c r="E41" s="19">
-        <v>25.608000000000001</v>
+        <v>24.602</v>
       </c>
       <c r="F41" s="10">
-        <v>30.663</v>
-      </c>
-      <c r="G41" s="11">
-        <v>95.2</v>
-      </c>
-      <c r="H41" s="11">
-        <v>55.3</v>
+        <v>41.085000000000001</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H41" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J41" s="13">
-        <v>39896</v>
+        <v>40683</v>
       </c>
       <c r="K41" s="5" t="s">
         <v>223</v>
@@ -4134,26 +4236,20 @@
       <c r="L41" s="5"/>
       <c r="M41" s="18">
         <f t="shared" si="0"/>
-        <v>21476</v>
+        <v>24206</v>
       </c>
       <c r="N41" s="18">
         <f t="shared" si="0"/>
-        <v>25608</v>
+        <v>24602</v>
       </c>
       <c r="O41" s="18">
         <f t="shared" si="0"/>
-        <v>30663</v>
-      </c>
-      <c r="P41" s="18">
-        <f t="shared" si="0"/>
-        <v>95200</v>
-      </c>
-      <c r="Q41" s="18">
-        <f t="shared" si="0"/>
-        <v>55300</v>
-      </c>
+        <v>41085</v>
+      </c>
+      <c r="P41" s="18"/>
+      <c r="Q41" s="18"/>
       <c r="R41" s="18"/>
-      <c r="T41" s="30"/>
+      <c r="T41" s="26"/>
       <c r="U41" s="24"/>
       <c r="V41" s="24"/>
       <c r="W41" s="24"/>
@@ -4166,34 +4262,34 @@
     </row>
     <row r="42" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>167</v>
+        <v>186</v>
       </c>
       <c r="B42" t="s">
-        <v>168</v>
+        <v>114</v>
       </c>
       <c r="C42">
-        <v>2667</v>
+        <v>2829</v>
       </c>
       <c r="D42" s="10">
-        <v>27.460999999999999</v>
+        <v>21.475999999999999</v>
       </c>
       <c r="E42" s="19">
-        <v>26.341999999999999</v>
+        <v>25.608000000000001</v>
       </c>
       <c r="F42" s="10">
-        <v>27.893999999999998</v>
+        <v>30.663</v>
       </c>
       <c r="G42" s="11">
-        <v>107.5</v>
+        <v>95.2</v>
       </c>
       <c r="H42" s="11">
-        <v>86.4</v>
+        <v>55.3</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="J42" s="13">
-        <v>43956</v>
+        <v>39896</v>
       </c>
       <c r="K42" s="5" t="s">
         <v>223</v>
@@ -4201,26 +4297,26 @@
       <c r="L42" s="5"/>
       <c r="M42" s="18">
         <f t="shared" si="0"/>
-        <v>27461</v>
+        <v>21476</v>
       </c>
       <c r="N42" s="18">
         <f t="shared" si="0"/>
-        <v>26342</v>
+        <v>25608</v>
       </c>
       <c r="O42" s="18">
         <f t="shared" si="0"/>
-        <v>27894</v>
+        <v>30663</v>
       </c>
       <c r="P42" s="18">
         <f t="shared" si="0"/>
-        <v>107500</v>
+        <v>95200</v>
       </c>
       <c r="Q42" s="18">
         <f t="shared" si="0"/>
-        <v>86400</v>
+        <v>55300</v>
       </c>
       <c r="R42" s="18"/>
-      <c r="T42" s="30"/>
+      <c r="T42" s="26"/>
       <c r="U42" s="24"/>
       <c r="V42" s="24"/>
       <c r="W42" s="24"/>
@@ -4233,34 +4329,34 @@
     </row>
     <row r="43" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B43" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="C43">
-        <v>3352</v>
+        <v>2667</v>
       </c>
       <c r="D43" s="10">
-        <v>28.021999999999998</v>
+        <v>27.460999999999999</v>
       </c>
       <c r="E43" s="19">
-        <v>32.585999999999999</v>
+        <v>26.341999999999999</v>
       </c>
       <c r="F43" s="10">
-        <v>44.103999999999999</v>
+        <v>27.893999999999998</v>
       </c>
       <c r="G43" s="11">
-        <v>122.4</v>
+        <v>107.5</v>
       </c>
       <c r="H43" s="11">
-        <v>79.2</v>
+        <v>86.4</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="J43" s="13">
-        <v>42315</v>
+        <v>43956</v>
       </c>
       <c r="K43" s="5" t="s">
         <v>223</v>
@@ -4268,26 +4364,26 @@
       <c r="L43" s="5"/>
       <c r="M43" s="18">
         <f t="shared" si="0"/>
-        <v>28022</v>
+        <v>27461</v>
       </c>
       <c r="N43" s="18">
         <f t="shared" si="0"/>
-        <v>32586</v>
+        <v>26342</v>
       </c>
       <c r="O43" s="18">
         <f t="shared" si="0"/>
-        <v>44104</v>
+        <v>27894</v>
       </c>
       <c r="P43" s="18">
         <f t="shared" si="0"/>
-        <v>122400</v>
+        <v>107500</v>
       </c>
       <c r="Q43" s="18">
         <f t="shared" si="0"/>
-        <v>79200</v>
+        <v>86400</v>
       </c>
       <c r="R43" s="18"/>
-      <c r="T43" s="30"/>
+      <c r="T43" s="26"/>
       <c r="U43" s="24"/>
       <c r="V43" s="24"/>
       <c r="W43" s="24"/>
@@ -4299,35 +4395,35 @@
       <c r="AC43" s="25"/>
     </row>
     <row r="44" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="16" t="s">
-        <v>120</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="C44" s="16">
-        <v>2300</v>
+      <c r="A44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44">
+        <v>3352</v>
       </c>
       <c r="D44" s="10">
-        <v>39.049999999999997</v>
+        <v>28.021999999999998</v>
       </c>
       <c r="E44" s="19">
-        <v>33.215000000000003</v>
+        <v>32.585999999999999</v>
       </c>
       <c r="F44" s="10">
-        <v>54.26</v>
+        <v>44.103999999999999</v>
       </c>
       <c r="G44" s="11">
-        <v>142.69999999999999</v>
+        <v>122.4</v>
       </c>
       <c r="H44" s="11">
-        <v>97.8</v>
+        <v>79.2</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
       <c r="J44" s="13">
-        <v>42397</v>
+        <v>42315</v>
       </c>
       <c r="K44" s="5" t="s">
         <v>223</v>
@@ -4335,26 +4431,26 @@
       <c r="L44" s="5"/>
       <c r="M44" s="18">
         <f t="shared" si="0"/>
-        <v>39050</v>
+        <v>28022</v>
       </c>
       <c r="N44" s="18">
         <f t="shared" si="0"/>
-        <v>33215</v>
+        <v>32586</v>
       </c>
       <c r="O44" s="18">
         <f t="shared" si="0"/>
-        <v>54260</v>
+        <v>44104</v>
       </c>
       <c r="P44" s="18">
         <f t="shared" si="0"/>
-        <v>142700</v>
+        <v>122400</v>
       </c>
       <c r="Q44" s="18">
         <f t="shared" si="0"/>
-        <v>97800</v>
+        <v>79200</v>
       </c>
       <c r="R44" s="18"/>
-      <c r="T44" s="30"/>
+      <c r="T44" s="26"/>
       <c r="U44" s="24"/>
       <c r="V44" s="24"/>
       <c r="W44" s="24"/>
@@ -4367,31 +4463,31 @@
     </row>
     <row r="45" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="16" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>140</v>
+        <v>171</v>
       </c>
       <c r="C45" s="16">
-        <v>2500</v>
+        <v>2300</v>
       </c>
       <c r="D45" s="10">
-        <v>40.698999999999998</v>
+        <v>39.049999999999997</v>
       </c>
       <c r="E45" s="19">
-        <v>37.018000000000001</v>
+        <v>33.215000000000003</v>
       </c>
       <c r="F45" s="10">
-        <v>52.634999999999998</v>
+        <v>54.26</v>
       </c>
       <c r="G45" s="11">
-        <v>154.5</v>
+        <v>142.69999999999999</v>
       </c>
       <c r="H45" s="11">
-        <v>94.9</v>
+        <v>97.8</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>199</v>
+        <v>10</v>
       </c>
       <c r="J45" s="13">
         <v>42397</v>
@@ -4402,26 +4498,26 @@
       <c r="L45" s="5"/>
       <c r="M45" s="18">
         <f t="shared" si="0"/>
-        <v>40699</v>
+        <v>39050</v>
       </c>
       <c r="N45" s="18">
         <f t="shared" si="0"/>
-        <v>37018</v>
+        <v>33215</v>
       </c>
       <c r="O45" s="18">
         <f t="shared" si="0"/>
-        <v>52635</v>
+        <v>54260</v>
       </c>
       <c r="P45" s="18">
         <f t="shared" si="0"/>
-        <v>154500</v>
+        <v>142700</v>
       </c>
       <c r="Q45" s="18">
         <f t="shared" si="0"/>
-        <v>94900</v>
+        <v>97800</v>
       </c>
       <c r="R45" s="18"/>
-      <c r="T45" s="30"/>
+      <c r="T45" s="26"/>
       <c r="U45" s="24"/>
       <c r="V45" s="24"/>
       <c r="W45" s="24"/>
@@ -4434,34 +4530,34 @@
     </row>
     <row r="46" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="16" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C46" s="16">
-        <v>2600</v>
+        <v>2500</v>
       </c>
       <c r="D46" s="10">
-        <v>45.381999999999998</v>
+        <v>40.698999999999998</v>
       </c>
       <c r="E46" s="19">
-        <v>40.313000000000002</v>
+        <v>37.018000000000001</v>
       </c>
       <c r="F46" s="10">
-        <v>61.804000000000002</v>
+        <v>52.634999999999998</v>
       </c>
       <c r="G46" s="11">
-        <v>169.9</v>
+        <v>154.5</v>
       </c>
       <c r="H46" s="11">
-        <v>111.4</v>
+        <v>94.9</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J46" s="13">
-        <v>42817</v>
+        <v>42397</v>
       </c>
       <c r="K46" s="5" t="s">
         <v>223</v>
@@ -4469,26 +4565,26 @@
       <c r="L46" s="5"/>
       <c r="M46" s="18">
         <f t="shared" si="0"/>
-        <v>45382</v>
+        <v>40699</v>
       </c>
       <c r="N46" s="18">
         <f t="shared" si="0"/>
-        <v>40313</v>
+        <v>37018</v>
       </c>
       <c r="O46" s="18">
         <f t="shared" si="0"/>
-        <v>61804</v>
+        <v>52635</v>
       </c>
       <c r="P46" s="18">
         <f t="shared" si="0"/>
-        <v>169900</v>
+        <v>154500</v>
       </c>
       <c r="Q46" s="18">
         <f t="shared" si="0"/>
-        <v>111400</v>
+        <v>94900</v>
       </c>
       <c r="R46" s="18"/>
-      <c r="T46" s="30"/>
+      <c r="T46" s="26"/>
       <c r="U46" s="24"/>
       <c r="V46" s="24"/>
       <c r="W46" s="24"/>
@@ -4501,34 +4597,34 @@
     </row>
     <row r="47" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="16" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>166</v>
+        <v>142</v>
       </c>
       <c r="C47" s="16">
-        <v>2700</v>
+        <v>2600</v>
       </c>
       <c r="D47" s="10">
-        <v>57.2</v>
+        <v>45.381999999999998</v>
       </c>
       <c r="E47" s="19">
-        <v>43.731999999999999</v>
+        <v>40.313000000000002</v>
       </c>
       <c r="F47" s="10">
-        <v>107.95399999999999</v>
+        <v>61.804000000000002</v>
       </c>
       <c r="G47" s="11">
-        <v>196.6</v>
+        <v>169.9</v>
       </c>
       <c r="H47" s="11">
-        <v>194.6</v>
+        <v>111.4</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J47" s="13">
-        <v>44155</v>
+        <v>42817</v>
       </c>
       <c r="K47" s="5" t="s">
         <v>223</v>
@@ -4536,26 +4632,26 @@
       <c r="L47" s="5"/>
       <c r="M47" s="18">
         <f t="shared" si="0"/>
-        <v>57200</v>
+        <v>45382</v>
       </c>
       <c r="N47" s="18">
         <f t="shared" si="0"/>
-        <v>43732</v>
+        <v>40313</v>
       </c>
       <c r="O47" s="18">
         <f t="shared" si="0"/>
-        <v>107954</v>
+        <v>61804</v>
       </c>
       <c r="P47" s="18">
         <f t="shared" si="0"/>
-        <v>196600</v>
+        <v>169900</v>
       </c>
       <c r="Q47" s="18">
         <f t="shared" si="0"/>
-        <v>194600</v>
+        <v>111400</v>
       </c>
       <c r="R47" s="18"/>
-      <c r="T47" s="30"/>
+      <c r="T47" s="26"/>
       <c r="U47" s="24"/>
       <c r="V47" s="24"/>
       <c r="W47" s="24"/>
@@ -4568,34 +4664,34 @@
     </row>
     <row r="48" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="16" t="s">
-        <v>127</v>
+        <v>173</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C48" s="16">
-        <v>2600</v>
+        <v>2700</v>
       </c>
       <c r="D48" s="10">
-        <v>55.045999999999999</v>
+        <v>57.2</v>
       </c>
       <c r="E48" s="19">
-        <v>44.618000000000002</v>
+        <v>43.731999999999999</v>
       </c>
       <c r="F48" s="10">
-        <v>73.569999999999993</v>
+        <v>107.95399999999999</v>
       </c>
       <c r="G48" s="11">
-        <v>195.6</v>
+        <v>196.6</v>
       </c>
       <c r="H48" s="11">
-        <v>132.6</v>
+        <v>194.6</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J48" s="13">
-        <v>43355</v>
+        <v>44155</v>
       </c>
       <c r="K48" s="5" t="s">
         <v>223</v>
@@ -4603,26 +4699,26 @@
       <c r="L48" s="5"/>
       <c r="M48" s="18">
         <f t="shared" si="0"/>
-        <v>55046</v>
+        <v>57200</v>
       </c>
       <c r="N48" s="18">
         <f t="shared" si="0"/>
-        <v>44618</v>
+        <v>43732</v>
       </c>
       <c r="O48" s="18">
         <f t="shared" si="0"/>
-        <v>73570</v>
+        <v>107954</v>
       </c>
       <c r="P48" s="18">
         <f t="shared" si="0"/>
-        <v>195600</v>
+        <v>196600</v>
       </c>
       <c r="Q48" s="18">
         <f t="shared" si="0"/>
-        <v>132600</v>
+        <v>194600</v>
       </c>
       <c r="R48" s="18"/>
-      <c r="T48" s="30"/>
+      <c r="T48" s="26"/>
       <c r="U48" s="24"/>
       <c r="V48" s="24"/>
       <c r="W48" s="24"/>
@@ -4635,34 +4731,34 @@
     </row>
     <row r="49" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="16" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B49" s="16" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C49" s="16">
         <v>2600</v>
       </c>
       <c r="D49" s="10">
-        <v>63.682000000000002</v>
+        <v>55.045999999999999</v>
       </c>
       <c r="E49" s="19">
-        <v>45.731999999999999</v>
+        <v>44.618000000000002</v>
       </c>
       <c r="F49" s="10">
-        <v>68.159000000000006</v>
+        <v>73.569999999999993</v>
       </c>
       <c r="G49" s="11">
-        <v>211.2</v>
+        <v>195.6</v>
       </c>
       <c r="H49" s="11">
-        <v>122.9</v>
+        <v>132.6</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>10</v>
+        <v>196</v>
       </c>
       <c r="J49" s="13">
-        <v>43146</v>
+        <v>43355</v>
       </c>
       <c r="K49" s="5" t="s">
         <v>223</v>
@@ -4670,26 +4766,26 @@
       <c r="L49" s="5"/>
       <c r="M49" s="18">
         <f t="shared" si="0"/>
-        <v>63682</v>
+        <v>55046</v>
       </c>
       <c r="N49" s="18">
         <f t="shared" si="0"/>
-        <v>45732</v>
+        <v>44618</v>
       </c>
       <c r="O49" s="18">
         <f t="shared" si="0"/>
-        <v>68159</v>
+        <v>73570</v>
       </c>
       <c r="P49" s="18">
         <f t="shared" si="0"/>
-        <v>211200</v>
+        <v>195600</v>
       </c>
       <c r="Q49" s="18">
         <f t="shared" si="0"/>
-        <v>122900</v>
+        <v>132600</v>
       </c>
       <c r="R49" s="18"/>
-      <c r="T49" s="30"/>
+      <c r="T49" s="26"/>
       <c r="U49" s="24"/>
       <c r="V49" s="24"/>
       <c r="W49" s="24"/>
@@ -4702,28 +4798,28 @@
     </row>
     <row r="50" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="16" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B50" s="16" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C50" s="16">
-        <v>2500</v>
+        <v>2600</v>
       </c>
       <c r="D50" s="10">
-        <v>50.423000000000002</v>
+        <v>63.682000000000002</v>
       </c>
       <c r="E50" s="19">
-        <v>46.116999999999997</v>
+        <v>45.731999999999999</v>
       </c>
       <c r="F50" s="10">
-        <v>70.039000000000001</v>
+        <v>68.159000000000006</v>
       </c>
       <c r="G50" s="11">
-        <v>192</v>
+        <v>211.2</v>
       </c>
       <c r="H50" s="11">
-        <v>126.3</v>
+        <v>122.9</v>
       </c>
       <c r="I50" s="8" t="s">
         <v>10</v>
@@ -4737,26 +4833,26 @@
       <c r="L50" s="5"/>
       <c r="M50" s="18">
         <f t="shared" si="0"/>
-        <v>50423</v>
+        <v>63682</v>
       </c>
       <c r="N50" s="18">
         <f t="shared" si="0"/>
-        <v>46117</v>
+        <v>45732</v>
       </c>
       <c r="O50" s="18">
         <f t="shared" si="0"/>
-        <v>70039</v>
+        <v>68159</v>
       </c>
       <c r="P50" s="18">
         <f t="shared" si="0"/>
-        <v>192000</v>
+        <v>211200</v>
       </c>
       <c r="Q50" s="18">
         <f t="shared" si="0"/>
-        <v>126300</v>
+        <v>122900</v>
       </c>
       <c r="R50" s="18"/>
-      <c r="T50" s="30"/>
+      <c r="T50" s="26"/>
       <c r="U50" s="24"/>
       <c r="V50" s="24"/>
       <c r="W50" s="24"/>
@@ -4768,35 +4864,35 @@
       <c r="AC50" s="25"/>
     </row>
     <row r="51" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>216</v>
-      </c>
-      <c r="B51" t="s">
-        <v>217</v>
-      </c>
-      <c r="C51">
-        <v>2112</v>
+      <c r="A51" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="16">
+        <v>2500</v>
       </c>
       <c r="D51" s="10">
-        <v>61.249000000000002</v>
+        <v>50.423000000000002</v>
       </c>
       <c r="E51" s="19">
-        <v>46.226999999999997</v>
+        <v>46.116999999999997</v>
       </c>
       <c r="F51" s="10">
-        <v>113.619</v>
+        <v>70.039000000000001</v>
       </c>
       <c r="G51" s="11">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H51" s="11">
-        <v>204.9</v>
+        <v>126.3</v>
       </c>
       <c r="I51" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="J51" s="14">
-        <v>45298</v>
+        <v>10</v>
+      </c>
+      <c r="J51" s="13">
+        <v>43146</v>
       </c>
       <c r="K51" s="5" t="s">
         <v>223</v>
@@ -4804,26 +4900,26 @@
       <c r="L51" s="5"/>
       <c r="M51" s="18">
         <f t="shared" si="0"/>
-        <v>61249</v>
+        <v>50423</v>
       </c>
       <c r="N51" s="18">
         <f t="shared" si="0"/>
-        <v>46227</v>
+        <v>46117</v>
       </c>
       <c r="O51" s="18">
         <f t="shared" si="0"/>
-        <v>113619</v>
+        <v>70039</v>
       </c>
       <c r="P51" s="18">
         <f t="shared" si="0"/>
-        <v>209000</v>
+        <v>192000</v>
       </c>
       <c r="Q51" s="18">
         <f t="shared" si="0"/>
-        <v>204900</v>
+        <v>126300</v>
       </c>
       <c r="R51" s="18"/>
-      <c r="T51" s="30"/>
+      <c r="T51" s="26"/>
       <c r="U51" s="24"/>
       <c r="V51" s="24"/>
       <c r="W51" s="24"/>
@@ -4835,33 +4931,35 @@
       <c r="AC51" s="25"/>
     </row>
     <row r="52" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="20" t="s">
-        <v>236</v>
-      </c>
-      <c r="B52" s="20" t="s">
-        <v>237</v>
-      </c>
-      <c r="C52" s="20">
-        <v>3700</v>
+      <c r="A52" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52">
+        <v>2112</v>
       </c>
       <c r="D52" s="10">
-        <v>68.150000000000006</v>
+        <v>61.249000000000002</v>
       </c>
       <c r="E52" s="19">
-        <v>48.103000000000002</v>
+        <v>46.226999999999997</v>
       </c>
       <c r="F52" s="10">
-        <v>118.447</v>
+        <v>113.619</v>
       </c>
       <c r="G52" s="11">
-        <v>223.80500000000001</v>
+        <v>209</v>
       </c>
       <c r="H52" s="11">
-        <v>216.554</v>
-      </c>
-      <c r="I52" s="8"/>
+        <v>204.9</v>
+      </c>
+      <c r="I52" s="8" t="s">
+        <v>218</v>
+      </c>
       <c r="J52" s="14">
-        <v>45773</v>
+        <v>45298</v>
       </c>
       <c r="K52" s="5" t="s">
         <v>223</v>
@@ -4869,26 +4967,26 @@
       <c r="L52" s="5"/>
       <c r="M52" s="18">
         <f t="shared" si="0"/>
-        <v>68150</v>
+        <v>61249</v>
       </c>
       <c r="N52" s="18">
         <f t="shared" si="0"/>
-        <v>48103</v>
+        <v>46227</v>
       </c>
       <c r="O52" s="18">
         <f t="shared" si="0"/>
-        <v>118447</v>
+        <v>113619</v>
       </c>
       <c r="P52" s="18">
         <f t="shared" si="0"/>
-        <v>223805</v>
+        <v>209000</v>
       </c>
       <c r="Q52" s="18">
         <f t="shared" si="0"/>
-        <v>216554</v>
+        <v>204900</v>
       </c>
       <c r="R52" s="18"/>
-      <c r="T52" s="30"/>
+      <c r="T52" s="26"/>
       <c r="U52" s="24"/>
       <c r="V52" s="24"/>
       <c r="W52" s="24"/>
@@ -4900,35 +4998,33 @@
       <c r="AC52" s="25"/>
     </row>
     <row r="53" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" t="s">
-        <v>234</v>
-      </c>
-      <c r="B53" t="s">
-        <v>233</v>
-      </c>
-      <c r="C53">
-        <v>2295</v>
+      <c r="A53" s="20" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" s="20" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="20">
+        <v>3700</v>
       </c>
       <c r="D53" s="10">
-        <v>59.665999999999997</v>
+        <v>68.150000000000006</v>
       </c>
       <c r="E53" s="19">
-        <v>49.441000000000003</v>
+        <v>48.103000000000002</v>
       </c>
       <c r="F53" s="10">
-        <v>116.922</v>
+        <v>118.447</v>
       </c>
       <c r="G53" s="11">
-        <v>214.8</v>
+        <v>223.80500000000001</v>
       </c>
       <c r="H53" s="11">
-        <v>210.8</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>235</v>
-      </c>
+        <v>216.554</v>
+      </c>
+      <c r="I53" s="8"/>
       <c r="J53" s="14">
-        <v>45298</v>
+        <v>45773</v>
       </c>
       <c r="K53" s="5" t="s">
         <v>223</v>
@@ -4936,26 +5032,26 @@
       <c r="L53" s="5"/>
       <c r="M53" s="18">
         <f t="shared" si="0"/>
-        <v>59666</v>
+        <v>68150</v>
       </c>
       <c r="N53" s="18">
         <f t="shared" si="0"/>
-        <v>49441</v>
+        <v>48103</v>
       </c>
       <c r="O53" s="18">
         <f t="shared" si="0"/>
-        <v>116922</v>
+        <v>118447</v>
       </c>
       <c r="P53" s="18">
         <f t="shared" si="0"/>
-        <v>214800</v>
+        <v>223805</v>
       </c>
       <c r="Q53" s="18">
         <f t="shared" si="0"/>
-        <v>210800</v>
+        <v>216554</v>
       </c>
       <c r="R53" s="18"/>
-      <c r="T53" s="30"/>
+      <c r="T53" s="26"/>
       <c r="U53" s="24"/>
       <c r="V53" s="24"/>
       <c r="W53" s="24"/>
@@ -4968,34 +5064,34 @@
     </row>
     <row r="54" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>208</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s">
-        <v>209</v>
+        <v>233</v>
       </c>
       <c r="C54">
-        <v>3700</v>
+        <v>2295</v>
       </c>
       <c r="D54" s="10">
-        <v>62.206000000000003</v>
+        <v>59.665999999999997</v>
       </c>
       <c r="E54" s="19">
-        <v>49.951000000000001</v>
+        <v>49.441000000000003</v>
       </c>
       <c r="F54" s="10">
-        <v>112.593</v>
+        <v>116.922</v>
       </c>
       <c r="G54" s="11">
-        <v>219.9</v>
+        <v>214.8</v>
       </c>
       <c r="H54" s="11">
-        <v>203</v>
+        <v>210.8</v>
       </c>
       <c r="I54" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="J54" s="13">
-        <v>45561</v>
+        <v>235</v>
+      </c>
+      <c r="J54" s="14">
+        <v>45298</v>
       </c>
       <c r="K54" s="5" t="s">
         <v>223</v>
@@ -5003,26 +5099,26 @@
       <c r="L54" s="5"/>
       <c r="M54" s="18">
         <f t="shared" si="0"/>
-        <v>62206</v>
+        <v>59666</v>
       </c>
       <c r="N54" s="18">
         <f t="shared" si="0"/>
-        <v>49951</v>
+        <v>49441</v>
       </c>
       <c r="O54" s="18">
         <f t="shared" si="0"/>
-        <v>112593</v>
+        <v>116922</v>
       </c>
       <c r="P54" s="18">
         <f t="shared" si="0"/>
-        <v>219900</v>
+        <v>214800</v>
       </c>
       <c r="Q54" s="18">
         <f t="shared" si="0"/>
-        <v>203000</v>
+        <v>210800</v>
       </c>
       <c r="R54" s="18"/>
-      <c r="T54" s="30"/>
+      <c r="T54" s="26"/>
       <c r="U54" s="24"/>
       <c r="V54" s="24"/>
       <c r="W54" s="24"/>
@@ -5035,34 +5131,34 @@
     </row>
     <row r="55" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>208</v>
       </c>
       <c r="B55" t="s">
-        <v>178</v>
+        <v>209</v>
       </c>
       <c r="C55">
-        <v>4160</v>
+        <v>3700</v>
       </c>
       <c r="D55" s="10">
-        <v>77.174000000000007</v>
+        <v>62.206000000000003</v>
       </c>
       <c r="E55" s="19">
-        <v>56.761000000000003</v>
+        <v>49.951000000000001</v>
       </c>
       <c r="F55" s="10">
-        <v>138.00299999999999</v>
+        <v>112.593</v>
       </c>
       <c r="G55" s="11">
-        <v>259.47000000000003</v>
+        <v>219.9</v>
       </c>
       <c r="H55" s="11">
-        <v>248.81200000000001</v>
+        <v>203</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>195</v>
-      </c>
-      <c r="J55" s="14">
-        <v>45211</v>
+        <v>207</v>
+      </c>
+      <c r="J55" s="13">
+        <v>45561</v>
       </c>
       <c r="K55" s="5" t="s">
         <v>223</v>
@@ -5070,29 +5166,26 @@
       <c r="L55" s="5"/>
       <c r="M55" s="18">
         <f t="shared" si="0"/>
-        <v>77174</v>
+        <v>62206</v>
       </c>
       <c r="N55" s="18">
         <f t="shared" si="0"/>
-        <v>56761</v>
+        <v>49951</v>
       </c>
       <c r="O55" s="18">
-        <f t="shared" ref="M55:Q58" si="2">F55*1000</f>
-        <v>138003</v>
+        <f t="shared" si="0"/>
+        <v>112593</v>
       </c>
       <c r="P55" s="18">
-        <f t="shared" si="2"/>
-        <v>259470.00000000003</v>
+        <f t="shared" si="0"/>
+        <v>219900</v>
       </c>
       <c r="Q55" s="18">
-        <f t="shared" si="2"/>
-        <v>248812</v>
+        <f t="shared" si="0"/>
+        <v>203000</v>
       </c>
       <c r="R55" s="18"/>
-      <c r="S55" s="36" t="s">
-        <v>261</v>
-      </c>
-      <c r="T55" s="32"/>
+      <c r="T55" s="26"/>
       <c r="U55" s="24"/>
       <c r="V55" s="24"/>
       <c r="W55" s="24"/>
@@ -5104,65 +5197,65 @@
       <c r="AC55" s="25"/>
     </row>
     <row r="56" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="C56" s="15">
-        <v>3090</v>
+      <c r="A56" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56">
+        <v>4160</v>
       </c>
       <c r="D56" s="10">
-        <v>63.435000000000002</v>
+        <v>77.174000000000007</v>
       </c>
       <c r="E56" s="19">
-        <v>66.734999999999999</v>
+        <v>56.761000000000003</v>
       </c>
       <c r="F56" s="10">
-        <v>143.465</v>
+        <v>138.00299999999999</v>
       </c>
       <c r="G56" s="11">
-        <v>261.7</v>
+        <v>259.47000000000003</v>
       </c>
       <c r="H56" s="11">
-        <v>258.7</v>
-      </c>
-      <c r="I56" s="8"/>
+        <v>248.81200000000001</v>
+      </c>
+      <c r="I56" s="8" t="s">
+        <v>195</v>
+      </c>
       <c r="J56" s="14">
-        <v>46116</v>
-      </c>
-      <c r="K56" s="33" t="s">
-        <v>250</v>
-      </c>
-      <c r="L56" s="5" t="s">
-        <v>251</v>
-      </c>
+        <v>45211</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L56" s="5"/>
       <c r="M56" s="18">
-        <f t="shared" ref="M56:N56" si="3">D56*1000</f>
-        <v>63435</v>
+        <f t="shared" si="0"/>
+        <v>77174</v>
       </c>
       <c r="N56" s="18">
+        <f t="shared" si="0"/>
+        <v>56761</v>
+      </c>
+      <c r="O56" s="18">
+        <f t="shared" ref="M56:Q59" si="3">F56*1000</f>
+        <v>138003</v>
+      </c>
+      <c r="P56" s="18">
         <f t="shared" si="3"/>
-        <v>66735</v>
-      </c>
-      <c r="O56" s="18">
-        <f t="shared" ref="O56" si="4">F56*1000</f>
-        <v>143465</v>
-      </c>
-      <c r="P56" s="18">
-        <f t="shared" ref="P56" si="5">G56*1000</f>
-        <v>261700</v>
+        <v>259470.00000000003</v>
       </c>
       <c r="Q56" s="18">
-        <f t="shared" ref="Q56" si="6">H56*1000</f>
-        <v>258700</v>
+        <f t="shared" si="3"/>
+        <v>248812</v>
       </c>
       <c r="R56" s="18"/>
-      <c r="S56" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="T56" s="31"/>
+      <c r="S56" s="32" t="s">
+        <v>261</v>
+      </c>
+      <c r="T56" s="28"/>
       <c r="U56" s="24"/>
       <c r="V56" s="24"/>
       <c r="W56" s="24"/>
@@ -5174,204 +5267,270 @@
       <c r="AC56" s="25"/>
     </row>
     <row r="57" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C57" s="16">
-        <v>3200</v>
+      <c r="A57" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C57" s="15">
+        <v>3090</v>
       </c>
       <c r="D57" s="10">
-        <v>66.938999999999993</v>
+        <v>63.435000000000002</v>
       </c>
       <c r="E57" s="19">
-        <v>79.733000000000004</v>
+        <v>66.734999999999999</v>
       </c>
       <c r="F57" s="10">
-        <v>216.304</v>
+        <v>143.465</v>
       </c>
       <c r="G57" s="11">
-        <v>296.39999999999998</v>
+        <v>261.7</v>
       </c>
       <c r="H57" s="11">
-        <v>389.9</v>
-      </c>
-      <c r="I57" s="8" t="s">
-        <v>10</v>
-      </c>
+        <v>258.7</v>
+      </c>
+      <c r="I57" s="8"/>
       <c r="J57" s="14">
-        <v>45561</v>
-      </c>
-      <c r="K57" s="33" t="s">
-        <v>230</v>
-      </c>
-      <c r="L57" s="5"/>
+        <v>46116</v>
+      </c>
+      <c r="K57" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="L57" s="5" t="s">
+        <v>251</v>
+      </c>
       <c r="M57" s="18">
-        <f t="shared" si="2"/>
-        <v>66939</v>
+        <f t="shared" ref="M57:N57" si="4">D57*1000</f>
+        <v>63435</v>
       </c>
       <c r="N57" s="18">
-        <f t="shared" si="2"/>
-        <v>79733</v>
+        <f t="shared" si="4"/>
+        <v>66735</v>
       </c>
       <c r="O57" s="18">
-        <f t="shared" si="2"/>
-        <v>216304</v>
+        <f t="shared" ref="O57" si="5">F57*1000</f>
+        <v>143465</v>
       </c>
       <c r="P57" s="18">
-        <f t="shared" si="2"/>
-        <v>296400</v>
+        <f t="shared" ref="P57" si="6">G57*1000</f>
+        <v>261700</v>
       </c>
       <c r="Q57" s="18">
-        <f t="shared" si="2"/>
-        <v>389900</v>
+        <f t="shared" ref="Q57" si="7">H57*1000</f>
+        <v>258700</v>
       </c>
       <c r="R57" s="18"/>
-      <c r="S57" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="T57" s="31"/>
-      <c r="U57" s="23"/>
+      <c r="S57" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="T57" s="27"/>
+      <c r="U57" s="24"/>
       <c r="V57" s="24"/>
       <c r="W57" s="24"/>
-      <c r="X57" s="23"/>
+      <c r="X57" s="24"/>
       <c r="Y57" s="24"/>
       <c r="Z57" s="24"/>
       <c r="AA57" s="24"/>
       <c r="AB57" s="24"/>
-      <c r="AC57" s="23"/>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>184</v>
-      </c>
-      <c r="B58" t="s">
-        <v>185</v>
-      </c>
-      <c r="C58">
-        <v>4700</v>
+      <c r="AC57" s="25"/>
+    </row>
+    <row r="58" spans="1:29" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="16" t="s">
+        <v>220</v>
+      </c>
+      <c r="B58" s="16" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="16">
+        <v>3200</v>
       </c>
       <c r="D58" s="10">
-        <v>104.52500000000001</v>
+        <v>66.938999999999993</v>
       </c>
       <c r="E58" s="19">
-        <v>85.01</v>
+        <v>79.733000000000004</v>
       </c>
       <c r="F58" s="10">
-        <v>264.86900000000003</v>
+        <v>216.304</v>
       </c>
       <c r="G58" s="11">
-        <v>372.2</v>
+        <v>296.39999999999998</v>
       </c>
       <c r="H58" s="11">
-        <v>377.5</v>
+        <v>389.9</v>
       </c>
       <c r="I58" s="8" t="s">
-        <v>194</v>
+        <v>10</v>
       </c>
       <c r="J58" s="14">
         <v>45561</v>
       </c>
-      <c r="K58" s="5" t="s">
-        <v>223</v>
+      <c r="K58" s="29" t="s">
+        <v>230</v>
       </c>
       <c r="L58" s="5"/>
       <c r="M58" s="18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
+        <v>66939</v>
+      </c>
+      <c r="N58" s="18">
+        <f t="shared" si="3"/>
+        <v>79733</v>
+      </c>
+      <c r="O58" s="18">
+        <f t="shared" si="3"/>
+        <v>216304</v>
+      </c>
+      <c r="P58" s="18">
+        <f t="shared" si="3"/>
+        <v>296400</v>
+      </c>
+      <c r="Q58" s="18">
+        <f t="shared" si="3"/>
+        <v>389900</v>
+      </c>
+      <c r="R58" s="18"/>
+      <c r="S58" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="T58" s="27"/>
+      <c r="U58" s="23"/>
+      <c r="V58" s="24"/>
+      <c r="W58" s="24"/>
+      <c r="X58" s="23"/>
+      <c r="Y58" s="24"/>
+      <c r="Z58" s="24"/>
+      <c r="AA58" s="24"/>
+      <c r="AB58" s="24"/>
+      <c r="AC58" s="23"/>
+    </row>
+    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59">
+        <v>4700</v>
+      </c>
+      <c r="D59" s="10">
+        <v>104.52500000000001</v>
+      </c>
+      <c r="E59" s="19">
+        <v>85.01</v>
+      </c>
+      <c r="F59" s="10">
+        <v>264.86900000000003</v>
+      </c>
+      <c r="G59" s="11">
+        <v>372.2</v>
+      </c>
+      <c r="H59" s="11">
+        <v>377.5</v>
+      </c>
+      <c r="I59" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="J59" s="14">
+        <v>45561</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="L59" s="5"/>
+      <c r="M59" s="18">
+        <f t="shared" si="3"/>
         <v>104525</v>
       </c>
-      <c r="N58" s="18">
-        <f t="shared" si="2"/>
+      <c r="N59" s="18">
+        <f t="shared" si="3"/>
         <v>85010</v>
       </c>
-      <c r="O58" s="18">
-        <f t="shared" si="2"/>
+      <c r="O59" s="18">
+        <f t="shared" si="3"/>
         <v>264869</v>
       </c>
-      <c r="P58" s="18">
-        <f t="shared" si="2"/>
+      <c r="P59" s="18">
+        <f t="shared" si="3"/>
         <v>372200</v>
       </c>
-      <c r="Q58" s="18">
-        <f t="shared" si="2"/>
+      <c r="Q59" s="18">
+        <f t="shared" si="3"/>
         <v>377500</v>
       </c>
-      <c r="R58" s="18"/>
-      <c r="S58" s="16" t="s">
+      <c r="R59" s="18"/>
+      <c r="S59" s="16" t="s">
         <v>258</v>
       </c>
-      <c r="T58" s="31"/>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
+      <c r="T59" s="27"/>
+    </row>
+    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
         <v>253</v>
       </c>
-      <c r="B59" s="15" t="s">
+      <c r="B60" s="15" t="s">
         <v>254</v>
       </c>
-      <c r="C59" s="15">
+      <c r="C60" s="15">
         <v>3210</v>
       </c>
-      <c r="D59" s="10">
+      <c r="D60" s="10">
         <v>83.274000000000001</v>
       </c>
-      <c r="E59" s="19">
+      <c r="E60" s="19">
         <v>86</v>
       </c>
-      <c r="F59" s="10">
+      <c r="F60" s="10">
         <v>163.31299999999999</v>
       </c>
-      <c r="G59" s="11">
+      <c r="G60" s="11">
         <v>339.9</v>
       </c>
-      <c r="H59" s="11">
+      <c r="H60" s="11">
         <v>296.2</v>
       </c>
-      <c r="I59" s="8" t="s">
+      <c r="I60" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="J59" s="13">
+      <c r="J60" s="13">
         <v>46116</v>
       </c>
-      <c r="K59" s="35" t="s">
+      <c r="K60" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="L59" t="s">
+      <c r="L60" t="s">
         <v>252</v>
       </c>
-      <c r="M59" s="18">
-        <f t="shared" ref="M59" si="7">D59*1000</f>
+      <c r="M60" s="18">
+        <f t="shared" ref="M60" si="8">D60*1000</f>
         <v>83274</v>
       </c>
-      <c r="N59" s="18">
-        <f t="shared" ref="N59" si="8">E59*1000</f>
+      <c r="N60" s="18">
+        <f t="shared" ref="N60" si="9">E60*1000</f>
         <v>86000</v>
       </c>
-      <c r="O59" s="18">
-        <f t="shared" ref="O59" si="9">F59*1000</f>
+      <c r="O60" s="18">
+        <f t="shared" ref="O60" si="10">F60*1000</f>
         <v>163313</v>
       </c>
-      <c r="P59" s="18">
-        <f t="shared" ref="P59" si="10">G59*1000</f>
+      <c r="P60" s="18">
+        <f t="shared" ref="P60" si="11">G60*1000</f>
         <v>339900</v>
       </c>
-      <c r="Q59" s="18">
-        <f t="shared" ref="Q59" si="11">H59*1000</f>
+      <c r="Q60" s="18">
+        <f t="shared" ref="Q60" si="12">H60*1000</f>
         <v>296200</v>
       </c>
-      <c r="S59" s="38" t="s">
+      <c r="S60" s="34" t="s">
         <v>257</v>
       </c>
-      <c r="T59" s="31"/>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="F60" s="10"/>
-      <c r="J60" s="7"/>
-      <c r="K60" s="7"/>
+      <c r="T60" s="27"/>
     </row>
     <row r="61" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="F61" s="10"/>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
     </row>
@@ -5382,6 +5541,10 @@
     <row r="63" spans="1:29" x14ac:dyDescent="0.25">
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
+    </row>
+    <row r="64" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="J64" s="7"/>
+      <c r="K64" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16057,7 +16220,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -16069,10 +16232,10 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="27" t="s">
+      <c r="F1" s="36" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -16080,7 +16243,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
+      <c r="A2" s="35"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -16090,8 +16253,8 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
@@ -16238,22 +16401,22 @@
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="37">
         <v>2.7480000000000002</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="37">
         <v>3.282</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="37">
         <v>3.7109999999999999</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="38">
         <v>12.8</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="38">
         <v>6.69</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="37" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16261,33 +16424,33 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="28"/>
+      <c r="B10" s="37"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="38"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="37"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="28">
+      <c r="B11" s="37">
         <v>3.665</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="37">
         <v>5.46</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="37">
         <v>4.6849999999999996</v>
       </c>
-      <c r="E11" s="29">
+      <c r="E11" s="38">
         <v>18.399999999999999</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="38">
         <v>8.4499999999999993</v>
       </c>
-      <c r="G11" s="28" t="s">
+      <c r="G11" s="37" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16295,12 +16458,12 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="28"/>
+      <c r="B12" s="37"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="37"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -16444,22 +16607,22 @@
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="28">
+      <c r="B19" s="37">
         <v>4.5910000000000002</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C19" s="37">
         <v>9.8949999999999996</v>
       </c>
-      <c r="D19" s="28">
+      <c r="D19" s="37">
         <v>9.0860000000000003</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="38">
         <v>28.5</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="38">
         <v>16.399999999999999</v>
       </c>
-      <c r="G19" s="28" t="s">
+      <c r="G19" s="37" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16467,12 +16630,12 @@
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="28"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="37"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -17096,7 +17259,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="26" t="s">
+      <c r="A48" s="35" t="s">
         <v>0</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -17108,10 +17271,10 @@
       <c r="D48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="27" t="s">
+      <c r="E48" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="27" t="s">
+      <c r="F48" s="36" t="s">
         <v>6</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -17119,7 +17282,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="26"/>
+      <c r="A49" s="35"/>
       <c r="B49" s="1" t="s">
         <v>2</v>
       </c>
@@ -17129,14 +17292,30 @@
       <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="27"/>
-      <c r="F49" s="27"/>
+      <c r="E49" s="36"/>
+      <c r="F49" s="36"/>
       <c r="G49" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A48:A49"/>
+    <mergeCell ref="E48:E49"/>
+    <mergeCell ref="F48:F49"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="E1:E2"/>
     <mergeCell ref="F1:F2"/>
@@ -17145,22 +17324,6 @@
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
     <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="E48:E49"/>
-    <mergeCell ref="F48:F49"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="http://pdadb.net/index.php?m=cpu&amp;id=a6422&amp;c=samsung_s5p6422" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -17205,10 +17368,10 @@
       <c r="C1" t="s">
         <v>84</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="E1" s="37" t="s">
+      <c r="E1" s="33" t="s">
         <v>81</v>
       </c>
       <c r="F1" t="s">
@@ -20158,6 +20321,1787 @@
       </c>
       <c r="Q59" t="s">
         <v>252</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DDF9A1-601F-4A84-9995-BE5D51EA74DF}">
+  <dimension ref="A1:I61"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="23.5703125" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" customWidth="1"/>
+    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="D1" s="43" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F1" s="43" t="s">
+        <v>82</v>
+      </c>
+      <c r="G1" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B2" s="46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2" s="44">
+        <v>667</v>
+      </c>
+      <c r="D2" s="44">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="E2" s="44">
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="F2" s="44">
+        <v>0.126</v>
+      </c>
+      <c r="G2" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="48">
+        <v>40892</v>
+      </c>
+      <c r="I2" s="44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B3" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="45">
+        <v>233</v>
+      </c>
+      <c r="D3" s="45">
+        <v>1.238</v>
+      </c>
+      <c r="E3" s="45">
+        <v>1.33</v>
+      </c>
+      <c r="F3" s="45">
+        <v>2.4089999999999998</v>
+      </c>
+      <c r="G3" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="49">
+        <v>41122</v>
+      </c>
+      <c r="I3" s="45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="46" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="C4" s="44">
+        <v>600</v>
+      </c>
+      <c r="D4" s="44">
+        <v>1.04</v>
+      </c>
+      <c r="E4" s="44">
+        <v>1.6850000000000001</v>
+      </c>
+      <c r="F4" s="44">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G4" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H4" s="48">
+        <v>41487</v>
+      </c>
+      <c r="I4" s="44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="B5" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="C5" s="45">
+        <v>400</v>
+      </c>
+      <c r="D5" s="45">
+        <v>1.379</v>
+      </c>
+      <c r="E5" s="45">
+        <v>1.712</v>
+      </c>
+      <c r="F5" s="45">
+        <v>3.5000000000000003E-2</v>
+      </c>
+      <c r="G5" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="49">
+        <v>41489</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="44">
+        <v>667</v>
+      </c>
+      <c r="D6" s="44">
+        <v>1.024</v>
+      </c>
+      <c r="E6" s="44">
+        <v>1.821</v>
+      </c>
+      <c r="F6" s="44">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="G6" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H6" s="48">
+        <v>41122</v>
+      </c>
+      <c r="I6" s="44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="45">
+        <v>700</v>
+      </c>
+      <c r="D7" s="45">
+        <v>2.456</v>
+      </c>
+      <c r="E7" s="45">
+        <v>3.1059999999999999</v>
+      </c>
+      <c r="F7" s="45">
+        <v>2.0289999999999999</v>
+      </c>
+      <c r="G7" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="49"/>
+      <c r="I7" s="45" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="B8" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="44">
+        <v>800</v>
+      </c>
+      <c r="D8" s="44">
+        <v>2.7480000000000002</v>
+      </c>
+      <c r="E8" s="44">
+        <v>3.282</v>
+      </c>
+      <c r="F8" s="44">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="G8" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="48">
+        <v>41861</v>
+      </c>
+      <c r="I8" s="44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="47" t="s">
+        <v>265</v>
+      </c>
+      <c r="B9" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C9" s="45">
+        <v>750</v>
+      </c>
+      <c r="D9" s="45">
+        <v>1.7330000000000001</v>
+      </c>
+      <c r="E9" s="45">
+        <v>3.9889999999999999</v>
+      </c>
+      <c r="F9" s="45">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H9" s="49">
+        <v>46117</v>
+      </c>
+      <c r="I9" s="45" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="B10" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="C10" s="44">
+        <v>933</v>
+      </c>
+      <c r="D10" s="44">
+        <v>4.7089999999999996</v>
+      </c>
+      <c r="E10" s="44">
+        <v>5.1639999999999997</v>
+      </c>
+      <c r="F10" s="44">
+        <v>8.9160000000000004</v>
+      </c>
+      <c r="G10" s="44" t="s">
+        <v>22</v>
+      </c>
+      <c r="H10" s="48">
+        <v>41861</v>
+      </c>
+      <c r="I10" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="B11" s="47" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="45">
+        <v>1008</v>
+      </c>
+      <c r="D11" s="45">
+        <v>3.665</v>
+      </c>
+      <c r="E11" s="45">
+        <v>5.46</v>
+      </c>
+      <c r="F11" s="45">
+        <v>4.6849999999999996</v>
+      </c>
+      <c r="G11" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H11" s="49">
+        <v>41861</v>
+      </c>
+      <c r="I11" s="45" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="46" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="44">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="44">
+        <v>4.665</v>
+      </c>
+      <c r="E12" s="44">
+        <v>6.4809999999999999</v>
+      </c>
+      <c r="F12" s="44">
+        <v>5.0590000000000002</v>
+      </c>
+      <c r="G12" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H12" s="48">
+        <v>41861</v>
+      </c>
+      <c r="I12" s="44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B13" s="47" t="s">
+        <v>116</v>
+      </c>
+      <c r="C13" s="45">
+        <v>988</v>
+      </c>
+      <c r="D13" s="45">
+        <v>5.7990000000000004</v>
+      </c>
+      <c r="E13" s="45">
+        <v>6.7169999999999996</v>
+      </c>
+      <c r="F13" s="45">
+        <v>8.0549999999999997</v>
+      </c>
+      <c r="G13" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="49">
+        <v>42217</v>
+      </c>
+      <c r="I13" s="45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="B14" s="46" t="s">
+        <v>117</v>
+      </c>
+      <c r="C14" s="44">
+        <v>1200</v>
+      </c>
+      <c r="D14" s="44">
+        <v>6.21</v>
+      </c>
+      <c r="E14" s="44">
+        <v>7.0469999999999997</v>
+      </c>
+      <c r="F14" s="44">
+        <v>12.384</v>
+      </c>
+      <c r="G14" s="44" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="48">
+        <v>41797</v>
+      </c>
+      <c r="I14" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="B15" s="47" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="45">
+        <v>1666</v>
+      </c>
+      <c r="D15" s="45">
+        <v>7.2430000000000003</v>
+      </c>
+      <c r="E15" s="45">
+        <v>7.109</v>
+      </c>
+      <c r="F15" s="45">
+        <v>7.351</v>
+      </c>
+      <c r="G15" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="49">
+        <v>40269</v>
+      </c>
+      <c r="I15" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B16" s="46" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="44">
+        <v>2000</v>
+      </c>
+      <c r="D16" s="44">
+        <v>9.3940000000000001</v>
+      </c>
+      <c r="E16" s="44">
+        <v>7.5289999999999999</v>
+      </c>
+      <c r="F16" s="44">
+        <v>13.164</v>
+      </c>
+      <c r="G16" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" s="48">
+        <v>40017</v>
+      </c>
+      <c r="I16" s="44" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A17" s="47" t="s">
+        <v>149</v>
+      </c>
+      <c r="B17" s="47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="45">
+        <v>1600</v>
+      </c>
+      <c r="D17" s="45">
+        <v>7.7519999999999998</v>
+      </c>
+      <c r="E17" s="45">
+        <v>7.5789999999999997</v>
+      </c>
+      <c r="F17" s="45">
+        <v>7.0679999999999996</v>
+      </c>
+      <c r="G17" s="45" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="49">
+        <v>40026</v>
+      </c>
+      <c r="I17" s="45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B18" s="46" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="44">
+        <v>1666</v>
+      </c>
+      <c r="D18" s="44">
+        <v>9.3859999999999992</v>
+      </c>
+      <c r="E18" s="44">
+        <v>8.39</v>
+      </c>
+      <c r="F18" s="44">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="G18" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="H18" s="48">
+        <v>41496</v>
+      </c>
+      <c r="I18" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="47" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="45">
+        <v>1200</v>
+      </c>
+      <c r="D19" s="45">
+        <v>6.78</v>
+      </c>
+      <c r="E19" s="45">
+        <v>9.5239999999999991</v>
+      </c>
+      <c r="F19" s="45">
+        <v>9.1739999999999995</v>
+      </c>
+      <c r="G19" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H19" s="49">
+        <v>45298</v>
+      </c>
+      <c r="I19" s="45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="B20" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="44">
+        <v>1512</v>
+      </c>
+      <c r="D20" s="44">
+        <v>4.5910000000000002</v>
+      </c>
+      <c r="E20" s="44">
+        <v>9.8949999999999996</v>
+      </c>
+      <c r="F20" s="44">
+        <v>9.0860000000000003</v>
+      </c>
+      <c r="G20" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H20" s="48">
+        <v>42031</v>
+      </c>
+      <c r="I20" s="44" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A21" s="47" t="s">
+        <v>182</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>183</v>
+      </c>
+      <c r="C21" s="45">
+        <v>1200</v>
+      </c>
+      <c r="D21" s="45">
+        <v>8.68</v>
+      </c>
+      <c r="E21" s="45">
+        <v>10.948</v>
+      </c>
+      <c r="F21" s="45">
+        <v>10.154999999999999</v>
+      </c>
+      <c r="G21" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H21" s="49">
+        <v>45319</v>
+      </c>
+      <c r="I21" s="45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B22" s="46" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="44">
+        <v>1800</v>
+      </c>
+      <c r="D22" s="44">
+        <v>11.269</v>
+      </c>
+      <c r="E22" s="44">
+        <v>11.927</v>
+      </c>
+      <c r="F22" s="44">
+        <v>20.516999999999999</v>
+      </c>
+      <c r="G22" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="H22" s="48">
+        <v>40672</v>
+      </c>
+      <c r="I22" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="47" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23" s="45">
+        <v>2000</v>
+      </c>
+      <c r="D23" s="45">
+        <v>12.138</v>
+      </c>
+      <c r="E23" s="45">
+        <v>12.568</v>
+      </c>
+      <c r="F23" s="45">
+        <v>21.143999999999998</v>
+      </c>
+      <c r="G23" s="45" t="s">
+        <v>188</v>
+      </c>
+      <c r="H23" s="49">
+        <v>39919</v>
+      </c>
+      <c r="I23" s="45" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C24" s="44">
+        <v>1860</v>
+      </c>
+      <c r="D24" s="44">
+        <v>18.433</v>
+      </c>
+      <c r="E24" s="44">
+        <v>15.15</v>
+      </c>
+      <c r="F24" s="44">
+        <v>16.635999999999999</v>
+      </c>
+      <c r="G24" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="H24" s="48">
+        <v>41788</v>
+      </c>
+      <c r="I24" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="B25" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="C25" s="45">
+        <v>1400</v>
+      </c>
+      <c r="D25" s="45">
+        <v>14.398999999999999</v>
+      </c>
+      <c r="E25" s="45">
+        <v>15.946999999999999</v>
+      </c>
+      <c r="F25" s="45">
+        <v>17.788</v>
+      </c>
+      <c r="G25" s="45"/>
+      <c r="H25" s="49">
+        <v>45772</v>
+      </c>
+      <c r="I25" s="45" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="46" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="C26" s="44">
+        <v>1800</v>
+      </c>
+      <c r="D26" s="44">
+        <v>13.595000000000001</v>
+      </c>
+      <c r="E26" s="44">
+        <v>16.120999999999999</v>
+      </c>
+      <c r="F26" s="44">
+        <v>19.565999999999999</v>
+      </c>
+      <c r="G26" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="H26" s="48">
+        <v>40672</v>
+      </c>
+      <c r="I26" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="47" t="s">
+        <v>161</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" s="45">
+        <v>1580</v>
+      </c>
+      <c r="D27" s="45">
+        <v>19.981000000000002</v>
+      </c>
+      <c r="E27" s="45">
+        <v>16.207000000000001</v>
+      </c>
+      <c r="F27" s="45">
+        <v>18.001000000000001</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>191</v>
+      </c>
+      <c r="H27" s="49">
+        <v>41851</v>
+      </c>
+      <c r="I27" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="46" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="46" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="44">
+        <v>1299</v>
+      </c>
+      <c r="D28" s="44">
+        <v>19.050999999999998</v>
+      </c>
+      <c r="E28" s="44">
+        <v>17.286000000000001</v>
+      </c>
+      <c r="F28" s="44">
+        <v>25.289000000000001</v>
+      </c>
+      <c r="G28" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H28" s="48">
+        <v>41861</v>
+      </c>
+      <c r="I28" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="B29" s="47" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="45">
+        <v>2527</v>
+      </c>
+      <c r="D29" s="45">
+        <v>28.488</v>
+      </c>
+      <c r="E29" s="45">
+        <v>17.780999999999999</v>
+      </c>
+      <c r="F29" s="45">
+        <v>36.673000000000002</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>192</v>
+      </c>
+      <c r="H29" s="49">
+        <v>41457</v>
+      </c>
+      <c r="I29" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="44">
+        <v>1600</v>
+      </c>
+      <c r="D30" s="44">
+        <v>23.695</v>
+      </c>
+      <c r="E30" s="44">
+        <v>17.817</v>
+      </c>
+      <c r="F30" s="44">
+        <v>25.515999999999998</v>
+      </c>
+      <c r="G30" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="H30" s="48">
+        <v>44089</v>
+      </c>
+      <c r="I30" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B31" s="47" t="s">
+        <v>121</v>
+      </c>
+      <c r="C31" s="45">
+        <v>1400</v>
+      </c>
+      <c r="D31" s="45">
+        <v>18.776</v>
+      </c>
+      <c r="E31" s="45">
+        <v>17.878</v>
+      </c>
+      <c r="F31" s="45">
+        <v>29.106000000000002</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H31" s="49">
+        <v>43641</v>
+      </c>
+      <c r="I31" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="46" t="s">
+        <v>212</v>
+      </c>
+      <c r="B32" s="46" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="44">
+        <v>1500</v>
+      </c>
+      <c r="D32" s="44">
+        <v>15.319000000000001</v>
+      </c>
+      <c r="E32" s="44">
+        <v>18.061</v>
+      </c>
+      <c r="F32" s="44">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="G32" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H32" s="48">
+        <v>45561</v>
+      </c>
+      <c r="I32" s="44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A33" s="47" t="s">
+        <v>162</v>
+      </c>
+      <c r="B33" s="47" t="s">
+        <v>109</v>
+      </c>
+      <c r="C33" s="45">
+        <v>2607</v>
+      </c>
+      <c r="D33" s="45">
+        <v>18.265000000000001</v>
+      </c>
+      <c r="E33" s="45">
+        <v>18.957999999999998</v>
+      </c>
+      <c r="F33" s="45">
+        <v>31.843</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" s="49">
+        <v>41151</v>
+      </c>
+      <c r="I33" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A34" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="44">
+        <v>2100</v>
+      </c>
+      <c r="D34" s="44">
+        <v>14.395</v>
+      </c>
+      <c r="E34" s="44">
+        <v>19.298999999999999</v>
+      </c>
+      <c r="F34" s="44">
+        <v>23.132000000000001</v>
+      </c>
+      <c r="G34" s="44" t="s">
+        <v>43</v>
+      </c>
+      <c r="H34" s="48">
+        <v>40060</v>
+      </c>
+      <c r="I34" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A35" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="B35" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="C35" s="45">
+        <v>2266</v>
+      </c>
+      <c r="D35" s="45">
+        <v>28.631</v>
+      </c>
+      <c r="E35" s="45">
+        <v>19.780999999999999</v>
+      </c>
+      <c r="F35" s="45">
+        <v>31.140999999999998</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>206</v>
+      </c>
+      <c r="H35" s="49">
+        <v>42713</v>
+      </c>
+      <c r="I35" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A36" s="46" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" s="46" t="s">
+        <v>247</v>
+      </c>
+      <c r="C36" s="44">
+        <v>2400</v>
+      </c>
+      <c r="D36" s="44">
+        <v>23.448</v>
+      </c>
+      <c r="E36" s="44">
+        <v>32.408000000000001</v>
+      </c>
+      <c r="F36" s="44">
+        <v>50.741999999999997</v>
+      </c>
+      <c r="G36" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H36" s="48">
+        <v>46116</v>
+      </c>
+      <c r="I36" s="44" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A37" s="47" t="s">
+        <v>163</v>
+      </c>
+      <c r="B37" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="C37" s="45">
+        <v>2043</v>
+      </c>
+      <c r="D37" s="45">
+        <v>19.359000000000002</v>
+      </c>
+      <c r="E37" s="45">
+        <v>19.808</v>
+      </c>
+      <c r="F37" s="45">
+        <v>33.182000000000002</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>205</v>
+      </c>
+      <c r="H37" s="49">
+        <v>41919</v>
+      </c>
+      <c r="I37" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A38" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="46" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="44">
+        <v>2832</v>
+      </c>
+      <c r="D38" s="44">
+        <v>33.670999999999999</v>
+      </c>
+      <c r="E38" s="44">
+        <v>23.584</v>
+      </c>
+      <c r="F38" s="44">
+        <v>36.384</v>
+      </c>
+      <c r="G38" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="H38" s="48">
+        <v>42443</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A39" s="47" t="s">
+        <v>174</v>
+      </c>
+      <c r="B39" s="47" t="s">
+        <v>175</v>
+      </c>
+      <c r="C39" s="45">
+        <v>3066</v>
+      </c>
+      <c r="D39" s="45">
+        <v>28.776</v>
+      </c>
+      <c r="E39" s="45">
+        <v>23.881</v>
+      </c>
+      <c r="F39" s="45">
+        <v>47.396000000000001</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>203</v>
+      </c>
+      <c r="H39" s="49">
+        <v>44691</v>
+      </c>
+      <c r="I39" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A40" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="44">
+        <v>3200</v>
+      </c>
+      <c r="D40" s="44">
+        <v>37.845999999999997</v>
+      </c>
+      <c r="E40" s="44">
+        <v>23.882000000000001</v>
+      </c>
+      <c r="F40" s="44">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H40" s="48">
+        <v>41537</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A41" s="47" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41" s="47" t="s">
+        <v>132</v>
+      </c>
+      <c r="C41" s="45">
+        <v>2667</v>
+      </c>
+      <c r="D41" s="45">
+        <v>24.206</v>
+      </c>
+      <c r="E41" s="45">
+        <v>24.602</v>
+      </c>
+      <c r="F41" s="45">
+        <v>41.085000000000001</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="49">
+        <v>40683</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A42" s="46" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" s="46" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="44">
+        <v>2829</v>
+      </c>
+      <c r="D42" s="44">
+        <v>21.475999999999999</v>
+      </c>
+      <c r="E42" s="44">
+        <v>25.608000000000001</v>
+      </c>
+      <c r="F42" s="44">
+        <v>30.663</v>
+      </c>
+      <c r="G42" s="44" t="s">
+        <v>201</v>
+      </c>
+      <c r="H42" s="48">
+        <v>39896</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A43" s="47" t="s">
+        <v>167</v>
+      </c>
+      <c r="B43" s="47" t="s">
+        <v>168</v>
+      </c>
+      <c r="C43" s="45">
+        <v>2667</v>
+      </c>
+      <c r="D43" s="45">
+        <v>27.460999999999999</v>
+      </c>
+      <c r="E43" s="45">
+        <v>26.341999999999999</v>
+      </c>
+      <c r="F43" s="45">
+        <v>27.893999999999998</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="H43" s="49">
+        <v>43956</v>
+      </c>
+      <c r="I43" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A44" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="44">
+        <v>3352</v>
+      </c>
+      <c r="D44" s="44">
+        <v>28.021999999999998</v>
+      </c>
+      <c r="E44" s="44">
+        <v>32.585999999999999</v>
+      </c>
+      <c r="F44" s="44">
+        <v>44.103999999999999</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="H44" s="48">
+        <v>42315</v>
+      </c>
+      <c r="I44" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A45" s="47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B45" s="47" t="s">
+        <v>171</v>
+      </c>
+      <c r="C45" s="45">
+        <v>2300</v>
+      </c>
+      <c r="D45" s="45">
+        <v>39.049999999999997</v>
+      </c>
+      <c r="E45" s="45">
+        <v>33.215000000000003</v>
+      </c>
+      <c r="F45" s="45">
+        <v>54.26</v>
+      </c>
+      <c r="G45" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H45" s="49">
+        <v>42397</v>
+      </c>
+      <c r="I45" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A46" s="46" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="46" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="44">
+        <v>2500</v>
+      </c>
+      <c r="D46" s="44">
+        <v>40.698999999999998</v>
+      </c>
+      <c r="E46" s="44">
+        <v>37.018000000000001</v>
+      </c>
+      <c r="F46" s="44">
+        <v>52.634999999999998</v>
+      </c>
+      <c r="G46" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="H46" s="48">
+        <v>42397</v>
+      </c>
+      <c r="I46" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A47" s="47" t="s">
+        <v>141</v>
+      </c>
+      <c r="B47" s="47" t="s">
+        <v>142</v>
+      </c>
+      <c r="C47" s="45">
+        <v>2600</v>
+      </c>
+      <c r="D47" s="45">
+        <v>45.381999999999998</v>
+      </c>
+      <c r="E47" s="45">
+        <v>40.313000000000002</v>
+      </c>
+      <c r="F47" s="45">
+        <v>61.804000000000002</v>
+      </c>
+      <c r="G47" s="45" t="s">
+        <v>198</v>
+      </c>
+      <c r="H47" s="49">
+        <v>42817</v>
+      </c>
+      <c r="I47" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A48" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="44">
+        <v>2700</v>
+      </c>
+      <c r="D48" s="44">
+        <v>57.2</v>
+      </c>
+      <c r="E48" s="44">
+        <v>43.731999999999999</v>
+      </c>
+      <c r="F48" s="44">
+        <v>107.95399999999999</v>
+      </c>
+      <c r="G48" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="48">
+        <v>44155</v>
+      </c>
+      <c r="I48" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A49" s="47" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="47" t="s">
+        <v>172</v>
+      </c>
+      <c r="C49" s="45">
+        <v>2600</v>
+      </c>
+      <c r="D49" s="45">
+        <v>55.045999999999999</v>
+      </c>
+      <c r="E49" s="45">
+        <v>44.618000000000002</v>
+      </c>
+      <c r="F49" s="45">
+        <v>73.569999999999993</v>
+      </c>
+      <c r="G49" s="45" t="s">
+        <v>196</v>
+      </c>
+      <c r="H49" s="49">
+        <v>43355</v>
+      </c>
+      <c r="I49" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A50" s="46" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="46" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="44">
+        <v>2600</v>
+      </c>
+      <c r="D50" s="44">
+        <v>63.682000000000002</v>
+      </c>
+      <c r="E50" s="44">
+        <v>45.731999999999999</v>
+      </c>
+      <c r="F50" s="44">
+        <v>68.159000000000006</v>
+      </c>
+      <c r="G50" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="H50" s="48">
+        <v>43146</v>
+      </c>
+      <c r="I50" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A51" s="47" t="s">
+        <v>128</v>
+      </c>
+      <c r="B51" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="C51" s="45">
+        <v>2500</v>
+      </c>
+      <c r="D51" s="45">
+        <v>50.423000000000002</v>
+      </c>
+      <c r="E51" s="45">
+        <v>46.116999999999997</v>
+      </c>
+      <c r="F51" s="45">
+        <v>70.039000000000001</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H51" s="49">
+        <v>43146</v>
+      </c>
+      <c r="I51" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A52" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" s="44">
+        <v>2112</v>
+      </c>
+      <c r="D52" s="44">
+        <v>61.249000000000002</v>
+      </c>
+      <c r="E52" s="44">
+        <v>46.226999999999997</v>
+      </c>
+      <c r="F52" s="44">
+        <v>113.619</v>
+      </c>
+      <c r="G52" s="44" t="s">
+        <v>218</v>
+      </c>
+      <c r="H52" s="48">
+        <v>45298</v>
+      </c>
+      <c r="I52" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A53" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B53" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="C53" s="45">
+        <v>3700</v>
+      </c>
+      <c r="D53" s="45">
+        <v>68.150000000000006</v>
+      </c>
+      <c r="E53" s="45">
+        <v>48.103000000000002</v>
+      </c>
+      <c r="F53" s="45">
+        <v>118.447</v>
+      </c>
+      <c r="G53" s="45"/>
+      <c r="H53" s="49">
+        <v>45773</v>
+      </c>
+      <c r="I53" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A54" s="46" t="s">
+        <v>234</v>
+      </c>
+      <c r="B54" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54" s="44">
+        <v>2295</v>
+      </c>
+      <c r="D54" s="44">
+        <v>59.665999999999997</v>
+      </c>
+      <c r="E54" s="44">
+        <v>49.441000000000003</v>
+      </c>
+      <c r="F54" s="44">
+        <v>116.922</v>
+      </c>
+      <c r="G54" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="H54" s="48">
+        <v>45298</v>
+      </c>
+      <c r="I54" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A55" s="47" t="s">
+        <v>208</v>
+      </c>
+      <c r="B55" s="47" t="s">
+        <v>209</v>
+      </c>
+      <c r="C55" s="45">
+        <v>3700</v>
+      </c>
+      <c r="D55" s="45">
+        <v>62.206000000000003</v>
+      </c>
+      <c r="E55" s="45">
+        <v>49.951000000000001</v>
+      </c>
+      <c r="F55" s="45">
+        <v>112.593</v>
+      </c>
+      <c r="G55" s="45" t="s">
+        <v>207</v>
+      </c>
+      <c r="H55" s="49">
+        <v>45561</v>
+      </c>
+      <c r="I55" s="45" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A56" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="44">
+        <v>4160</v>
+      </c>
+      <c r="D56" s="44">
+        <v>77.174000000000007</v>
+      </c>
+      <c r="E56" s="44">
+        <v>56.761000000000003</v>
+      </c>
+      <c r="F56" s="44">
+        <v>138.00299999999999</v>
+      </c>
+      <c r="G56" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="H56" s="48">
+        <v>45211</v>
+      </c>
+      <c r="I56" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57" s="46" t="s">
+        <v>246</v>
+      </c>
+      <c r="B57" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="C57" s="44">
+        <v>3090</v>
+      </c>
+      <c r="D57" s="44">
+        <v>63.435000000000002</v>
+      </c>
+      <c r="E57" s="44">
+        <v>66.734999999999999</v>
+      </c>
+      <c r="F57" s="44">
+        <v>143.465</v>
+      </c>
+      <c r="G57" s="44"/>
+      <c r="H57" s="48">
+        <v>46116</v>
+      </c>
+      <c r="I57" s="44" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58" s="47" t="s">
+        <v>220</v>
+      </c>
+      <c r="B58" s="47" t="s">
+        <v>219</v>
+      </c>
+      <c r="C58" s="45">
+        <v>3200</v>
+      </c>
+      <c r="D58" s="45">
+        <v>66.938999999999993</v>
+      </c>
+      <c r="E58" s="45">
+        <v>79.733000000000004</v>
+      </c>
+      <c r="F58" s="45">
+        <v>216.304</v>
+      </c>
+      <c r="G58" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H58" s="49">
+        <v>45561</v>
+      </c>
+      <c r="I58" s="45" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="46" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="46" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="44">
+        <v>4700</v>
+      </c>
+      <c r="D59" s="44">
+        <v>104.52500000000001</v>
+      </c>
+      <c r="E59" s="44">
+        <v>85.01</v>
+      </c>
+      <c r="F59" s="44">
+        <v>264.86900000000003</v>
+      </c>
+      <c r="G59" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="H59" s="48">
+        <v>45561</v>
+      </c>
+      <c r="I59" s="44" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="47" t="s">
+        <v>253</v>
+      </c>
+      <c r="B60" s="47" t="s">
+        <v>254</v>
+      </c>
+      <c r="C60" s="45">
+        <v>3210</v>
+      </c>
+      <c r="D60" s="45">
+        <v>83.274000000000001</v>
+      </c>
+      <c r="E60" s="45">
+        <v>86</v>
+      </c>
+      <c r="F60" s="45">
+        <v>163.31299999999999</v>
+      </c>
+      <c r="G60" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="H60" s="49">
+        <v>46116</v>
+      </c>
+      <c r="I60" s="45" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B61" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C61" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>80</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>81</v>
+      </c>
+      <c r="F61" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>83</v>
+      </c>
+      <c r="H61" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="I61" s="44" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/nbench/list2026.xlsx
+++ b/nbench/list2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\archive\github\benchmark\nbench\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C9BA65-6DF8-4DC5-AC07-62E853870D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E47D8A1-FAEC-44A2-A457-7A44A36D207F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6990" yWindow="30" windowWidth="26505" windowHeight="15705" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1731" uniqueCount="269">
   <si>
     <t>CPU</t>
   </si>
@@ -849,6 +849,9 @@
   </si>
   <si>
     <t>6.12.74, gcc 14.3.0</t>
+  </si>
+  <si>
+    <t>__Integer Index__</t>
   </si>
 </sst>
 </file>
@@ -937,7 +940,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1028,18 +1031,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6F8FA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -1084,7 +1075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1154,6 +1145,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1166,31 +1160,19 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="16" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="10" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1652,7 +1634,7 @@
       <c r="J2" s="13">
         <v>40892</v>
       </c>
-      <c r="K2" s="41" t="s">
+      <c r="K2" s="37" t="s">
         <v>228</v>
       </c>
       <c r="M2" s="18">
@@ -1783,7 +1765,7 @@
       <c r="J4" s="13">
         <v>41487</v>
       </c>
-      <c r="K4" s="41" t="s">
+      <c r="K4" s="37" t="s">
         <v>228</v>
       </c>
       <c r="M4" s="18">
@@ -1849,7 +1831,7 @@
       <c r="J5" s="13">
         <v>41489</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="35" t="s">
         <v>229</v>
       </c>
       <c r="M5" s="18">
@@ -1915,7 +1897,7 @@
       <c r="J6" s="13">
         <v>41122</v>
       </c>
-      <c r="K6" s="41" t="s">
+      <c r="K6" s="37" t="s">
         <v>228</v>
       </c>
       <c r="M6" s="18">
@@ -1979,7 +1961,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="13"/>
-      <c r="K7" s="41" t="s">
+      <c r="K7" s="37" t="s">
         <v>226</v>
       </c>
       <c r="M7" s="18">
@@ -2045,7 +2027,7 @@
       <c r="J8" s="13">
         <v>41861</v>
       </c>
-      <c r="K8" s="40" t="s">
+      <c r="K8" s="36" t="s">
         <v>227</v>
       </c>
       <c r="M8" s="18">
@@ -2111,7 +2093,7 @@
       <c r="J9" s="13">
         <v>46117</v>
       </c>
-      <c r="K9" s="39" t="s">
+      <c r="K9" s="35" t="s">
         <v>264</v>
       </c>
       <c r="L9" t="s">
@@ -2246,7 +2228,7 @@
       <c r="J11" s="13">
         <v>41861</v>
       </c>
-      <c r="K11" s="40" t="s">
+      <c r="K11" s="36" t="s">
         <v>227</v>
       </c>
       <c r="M11" s="18">
@@ -2312,7 +2294,7 @@
       <c r="J12" s="13">
         <v>41861</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K12" s="36" t="s">
         <v>227</v>
       </c>
       <c r="M12" s="18">
@@ -2842,7 +2824,7 @@
       <c r="J20" s="13">
         <v>42031</v>
       </c>
-      <c r="K20" s="40" t="s">
+      <c r="K20" s="36" t="s">
         <v>227</v>
       </c>
       <c r="M20" s="18">
@@ -16220,7 +16202,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -16232,10 +16214,10 @@
       <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -16243,7 +16225,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="35"/>
+      <c r="A2" s="38"/>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
@@ -16253,8 +16235,8 @@
       <c r="D2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
       <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
@@ -16401,22 +16383,22 @@
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="40">
         <v>2.7480000000000002</v>
       </c>
-      <c r="C9" s="37">
+      <c r="C9" s="40">
         <v>3.282</v>
       </c>
-      <c r="D9" s="37">
+      <c r="D9" s="40">
         <v>3.7109999999999999</v>
       </c>
-      <c r="E9" s="38">
+      <c r="E9" s="41">
         <v>12.8</v>
       </c>
-      <c r="F9" s="38">
+      <c r="F9" s="41">
         <v>6.69</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="40" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16424,33 +16406,33 @@
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="37"/>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="41"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="40"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="40">
         <v>3.665</v>
       </c>
-      <c r="C11" s="37">
+      <c r="C11" s="40">
         <v>5.46</v>
       </c>
-      <c r="D11" s="37">
+      <c r="D11" s="40">
         <v>4.6849999999999996</v>
       </c>
-      <c r="E11" s="38">
+      <c r="E11" s="41">
         <v>18.399999999999999</v>
       </c>
-      <c r="F11" s="38">
+      <c r="F11" s="41">
         <v>8.4499999999999993</v>
       </c>
-      <c r="G11" s="37" t="s">
+      <c r="G11" s="40" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16458,12 +16440,12 @@
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="37"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="37"/>
+      <c r="B12" s="40"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="41"/>
+      <c r="F12" s="41"/>
+      <c r="G12" s="40"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
@@ -16607,22 +16589,22 @@
       <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="37">
+      <c r="B19" s="40">
         <v>4.5910000000000002</v>
       </c>
-      <c r="C19" s="37">
+      <c r="C19" s="40">
         <v>9.8949999999999996</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="40">
         <v>9.0860000000000003</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E19" s="41">
         <v>28.5</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F19" s="41">
         <v>16.399999999999999</v>
       </c>
-      <c r="G19" s="37" t="s">
+      <c r="G19" s="40" t="s">
         <v>10</v>
       </c>
     </row>
@@ -16630,12 +16612,12 @@
       <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="38"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="37"/>
+      <c r="B20" s="40"/>
+      <c r="C20" s="40"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="40"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
@@ -17259,7 +17241,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="35" t="s">
+      <c r="A48" s="38" t="s">
         <v>0</v>
       </c>
       <c r="B48" s="1" t="s">
@@ -17271,10 +17253,10 @@
       <c r="D48" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E48" s="36" t="s">
+      <c r="E48" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="F48" s="36" t="s">
+      <c r="F48" s="39" t="s">
         <v>6</v>
       </c>
       <c r="G48" s="1" t="s">
@@ -17282,7 +17264,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="35"/>
+      <c r="A49" s="38"/>
       <c r="B49" s="1" t="s">
         <v>2</v>
       </c>
@@ -17292,14 +17274,30 @@
       <c r="D49" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E49" s="36"/>
-      <c r="F49" s="36"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
       <c r="G49" s="1" t="s">
         <v>8</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="E1:E2"/>
+    <mergeCell ref="F1:F2"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
     <mergeCell ref="A48:A49"/>
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="F48:F49"/>
@@ -17308,22 +17306,6 @@
     <mergeCell ref="D19:D20"/>
     <mergeCell ref="E19:E20"/>
     <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="E1:E2"/>
-    <mergeCell ref="F1:F2"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F9:F10"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A3" r:id="rId1" display="http://pdadb.net/index.php?m=cpu&amp;id=a6422&amp;c=samsung_s5p6422" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -20330,20 +20312,21 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9DDF9A1-601F-4A84-9995-BE5D51EA74DF}">
-  <dimension ref="A1:I61"/>
+  <dimension ref="A1:K61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" customWidth="1"/>
     <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="42.75" x14ac:dyDescent="0.25">
       <c r="A1" s="42" t="s">
         <v>78</v>
       </c>
@@ -20357,55 +20340,62 @@
         <v>80</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>81</v>
+        <v>268</v>
       </c>
       <c r="F1" s="43" t="s">
         <v>82</v>
       </c>
       <c r="G1" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="H1" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="I1" s="43" t="s">
         <v>83</v>
       </c>
-      <c r="H1" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="I1" s="43" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="46" t="s">
+      <c r="K1" s="43" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="44" t="s">
         <v>85</v>
       </c>
-      <c r="C2" s="44">
+      <c r="C2" s="45">
         <v>667</v>
       </c>
-      <c r="D2" s="44">
+      <c r="D2" s="45">
         <v>0.54100000000000004</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="45" t="str">
+        <f>CONCATENATE("__", K2, "__")</f>
+        <v>__0.959__</v>
+      </c>
+      <c r="F2" s="45">
+        <v>0.126</v>
+      </c>
+      <c r="G2" s="46">
+        <v>40892</v>
+      </c>
+      <c r="H2" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="I2" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="45">
         <v>0.95899999999999996</v>
       </c>
-      <c r="F2" s="44">
-        <v>0.126</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="48">
-        <v>40892</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="47" t="s">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="44" t="s">
         <v>148</v>
       </c>
       <c r="C3" s="45">
@@ -20414,56 +20404,64 @@
       <c r="D3" s="45">
         <v>1.238</v>
       </c>
-      <c r="E3" s="45">
-        <v>1.33</v>
+      <c r="E3" s="45" t="str">
+        <f t="shared" ref="E3:E60" si="0">CONCATENATE("__", K3, "__")</f>
+        <v>__1.33__</v>
       </c>
       <c r="F3" s="45">
         <v>2.4089999999999998</v>
       </c>
-      <c r="G3" s="45" t="s">
+      <c r="G3" s="46">
+        <v>41122</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I3" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="49">
-        <v>41122</v>
-      </c>
-      <c r="I3" s="45" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="46" t="s">
+      <c r="K3" s="45">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="44" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="44">
+      <c r="C4" s="45">
         <v>600</v>
       </c>
-      <c r="D4" s="44">
+      <c r="D4" s="45">
         <v>1.04</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__1.685__</v>
+      </c>
+      <c r="F4" s="45">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="G4" s="46">
+        <v>41487</v>
+      </c>
+      <c r="H4" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="I4" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K4" s="45">
         <v>1.6850000000000001</v>
       </c>
-      <c r="F4" s="44">
-        <v>0.22800000000000001</v>
-      </c>
-      <c r="G4" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4" s="48">
-        <v>41487</v>
-      </c>
-      <c r="I4" s="44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="47" t="s">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="B5" s="47" t="s">
+      <c r="B5" s="44" t="s">
         <v>91</v>
       </c>
       <c r="C5" s="45">
@@ -20472,56 +20470,64 @@
       <c r="D5" s="45">
         <v>1.379</v>
       </c>
-      <c r="E5" s="45">
-        <v>1.712</v>
+      <c r="E5" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__1.712__</v>
       </c>
       <c r="F5" s="45">
         <v>3.5000000000000003E-2</v>
       </c>
-      <c r="G5" s="45" t="s">
+      <c r="G5" s="46">
+        <v>41489</v>
+      </c>
+      <c r="H5" s="45" t="s">
+        <v>229</v>
+      </c>
+      <c r="I5" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="49">
-        <v>41489</v>
-      </c>
-      <c r="I5" s="45" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="46" t="s">
+      <c r="K5" s="45">
+        <v>1.712</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="44" t="s">
         <v>147</v>
       </c>
-      <c r="C6" s="44">
+      <c r="C6" s="45">
         <v>667</v>
       </c>
-      <c r="D6" s="44">
+      <c r="D6" s="45">
         <v>1.024</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__1.821__</v>
+      </c>
+      <c r="F6" s="45">
+        <v>0.23799999999999999</v>
+      </c>
+      <c r="G6" s="46">
+        <v>41122</v>
+      </c>
+      <c r="H6" s="45" t="s">
+        <v>228</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K6" s="45">
         <v>1.821</v>
       </c>
-      <c r="F6" s="44">
-        <v>0.23799999999999999</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H6" s="48">
-        <v>41122</v>
-      </c>
-      <c r="I6" s="44" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="47" t="s">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="B7" s="47" t="s">
+      <c r="B7" s="44" t="s">
         <v>93</v>
       </c>
       <c r="C7" s="45">
@@ -20530,54 +20536,62 @@
       <c r="D7" s="45">
         <v>2.456</v>
       </c>
-      <c r="E7" s="45">
-        <v>3.1059999999999999</v>
+      <c r="E7" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__3.106__</v>
       </c>
       <c r="F7" s="45">
         <v>2.0289999999999999</v>
       </c>
-      <c r="G7" s="45" t="s">
+      <c r="G7" s="46"/>
+      <c r="H7" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="I7" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H7" s="49"/>
-      <c r="I7" s="45" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="46" t="s">
+      <c r="K7" s="45">
+        <v>3.1059999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="44" t="s">
         <v>95</v>
       </c>
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="44" t="s">
         <v>143</v>
       </c>
-      <c r="C8" s="44">
+      <c r="C8" s="45">
         <v>800</v>
       </c>
-      <c r="D8" s="44">
+      <c r="D8" s="45">
         <v>2.7480000000000002</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__3.282__</v>
+      </c>
+      <c r="F8" s="45">
+        <v>3.7109999999999999</v>
+      </c>
+      <c r="G8" s="46">
+        <v>41861</v>
+      </c>
+      <c r="H8" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="I8" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K8" s="45">
         <v>3.282</v>
       </c>
-      <c r="F8" s="44">
-        <v>3.7109999999999999</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H8" s="48">
-        <v>41861</v>
-      </c>
-      <c r="I8" s="44" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="47" t="s">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="44" t="s">
         <v>265</v>
       </c>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="44" t="s">
         <v>266</v>
       </c>
       <c r="C9" s="45">
@@ -20586,56 +20600,64 @@
       <c r="D9" s="45">
         <v>1.7330000000000001</v>
       </c>
-      <c r="E9" s="45">
-        <v>3.9889999999999999</v>
+      <c r="E9" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__3.989__</v>
       </c>
       <c r="F9" s="45">
         <v>0.25</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="46">
+        <v>46117</v>
+      </c>
+      <c r="H9" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="I9" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="49">
-        <v>46117</v>
-      </c>
-      <c r="I9" s="45" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="46" t="s">
+      <c r="K9" s="45">
+        <v>3.9889999999999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="44" t="s">
         <v>96</v>
       </c>
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="44" t="s">
         <v>159</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="45">
         <v>933</v>
       </c>
-      <c r="D10" s="44">
+      <c r="D10" s="45">
         <v>4.7089999999999996</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__5.164__</v>
+      </c>
+      <c r="F10" s="45">
+        <v>8.9160000000000004</v>
+      </c>
+      <c r="G10" s="46">
+        <v>41861</v>
+      </c>
+      <c r="H10" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I10" s="45" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" s="45">
         <v>5.1639999999999997</v>
       </c>
-      <c r="F10" s="44">
-        <v>8.9160000000000004</v>
-      </c>
-      <c r="G10" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="48">
-        <v>41861</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="47" t="s">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="44" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="44" t="s">
         <v>144</v>
       </c>
       <c r="C11" s="45">
@@ -20644,56 +20666,64 @@
       <c r="D11" s="45">
         <v>3.665</v>
       </c>
-      <c r="E11" s="45">
-        <v>5.46</v>
+      <c r="E11" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__5.46__</v>
       </c>
       <c r="F11" s="45">
         <v>4.6849999999999996</v>
       </c>
-      <c r="G11" s="45" t="s">
+      <c r="G11" s="46">
+        <v>41861</v>
+      </c>
+      <c r="H11" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H11" s="49">
+      <c r="K11" s="45">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="45">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="45">
+        <v>4.665</v>
+      </c>
+      <c r="E12" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__6.481__</v>
+      </c>
+      <c r="F12" s="45">
+        <v>5.0590000000000002</v>
+      </c>
+      <c r="G12" s="46">
         <v>41861</v>
       </c>
-      <c r="I11" s="45" t="s">
+      <c r="H12" s="45" t="s">
         <v>227</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="46" t="s">
-        <v>115</v>
-      </c>
-      <c r="C12" s="44">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="44">
-        <v>4.665</v>
-      </c>
-      <c r="E12" s="44">
+      <c r="I12" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K12" s="45">
         <v>6.4809999999999999</v>
       </c>
-      <c r="F12" s="44">
-        <v>5.0590000000000002</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H12" s="48">
-        <v>41861</v>
-      </c>
-      <c r="I12" s="44" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="47" t="s">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="44" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="47" t="s">
+      <c r="B13" s="44" t="s">
         <v>116</v>
       </c>
       <c r="C13" s="45">
@@ -20702,56 +20732,64 @@
       <c r="D13" s="45">
         <v>5.7990000000000004</v>
       </c>
-      <c r="E13" s="45">
-        <v>6.7169999999999996</v>
+      <c r="E13" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__6.717__</v>
       </c>
       <c r="F13" s="45">
         <v>8.0549999999999997</v>
       </c>
-      <c r="G13" s="45" t="s">
+      <c r="G13" s="46">
+        <v>42217</v>
+      </c>
+      <c r="H13" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="I13" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H13" s="49">
-        <v>42217</v>
-      </c>
-      <c r="I13" s="45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="46" t="s">
+      <c r="K13" s="45">
+        <v>6.7169999999999996</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="46" t="s">
+      <c r="B14" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="45">
         <v>1200</v>
       </c>
-      <c r="D14" s="44">
+      <c r="D14" s="45">
         <v>6.21</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__7.047__</v>
+      </c>
+      <c r="F14" s="45">
+        <v>12.384</v>
+      </c>
+      <c r="G14" s="46">
+        <v>41797</v>
+      </c>
+      <c r="H14" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I14" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14" s="45">
         <v>7.0469999999999997</v>
       </c>
-      <c r="F14" s="44">
-        <v>12.384</v>
-      </c>
-      <c r="G14" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="H14" s="48">
-        <v>41797</v>
-      </c>
-      <c r="I14" s="44" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="47" t="s">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="44" t="s">
         <v>153</v>
       </c>
-      <c r="B15" s="47" t="s">
+      <c r="B15" s="44" t="s">
         <v>119</v>
       </c>
       <c r="C15" s="45">
@@ -20760,56 +20798,64 @@
       <c r="D15" s="45">
         <v>7.2430000000000003</v>
       </c>
-      <c r="E15" s="45">
-        <v>7.109</v>
+      <c r="E15" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__7.109__</v>
       </c>
       <c r="F15" s="45">
         <v>7.351</v>
       </c>
-      <c r="G15" s="45" t="s">
+      <c r="G15" s="46">
+        <v>40269</v>
+      </c>
+      <c r="H15" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="H15" s="49">
-        <v>40269</v>
-      </c>
-      <c r="I15" s="45" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="46" t="s">
+      <c r="K15" s="45">
+        <v>7.109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="44" t="s">
         <v>154</v>
       </c>
-      <c r="B16" s="46" t="s">
+      <c r="B16" s="44" t="s">
         <v>102</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="45">
         <v>2000</v>
       </c>
-      <c r="D16" s="44">
+      <c r="D16" s="45">
         <v>9.3940000000000001</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__7.529__</v>
+      </c>
+      <c r="F16" s="45">
+        <v>13.164</v>
+      </c>
+      <c r="G16" s="46">
+        <v>40017</v>
+      </c>
+      <c r="H16" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I16" s="45" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" s="45">
         <v>7.5289999999999999</v>
       </c>
-      <c r="F16" s="44">
-        <v>13.164</v>
-      </c>
-      <c r="G16" s="44" t="s">
-        <v>35</v>
-      </c>
-      <c r="H16" s="48">
-        <v>40017</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="47" t="s">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="44" t="s">
         <v>149</v>
       </c>
-      <c r="B17" s="47" t="s">
+      <c r="B17" s="44" t="s">
         <v>118</v>
       </c>
       <c r="C17" s="45">
@@ -20818,56 +20864,64 @@
       <c r="D17" s="45">
         <v>7.7519999999999998</v>
       </c>
-      <c r="E17" s="45">
-        <v>7.5789999999999997</v>
+      <c r="E17" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__7.579__</v>
       </c>
       <c r="F17" s="45">
         <v>7.0679999999999996</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="G17" s="46">
+        <v>40026</v>
+      </c>
+      <c r="H17" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I17" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="H17" s="49">
-        <v>40026</v>
-      </c>
-      <c r="I17" s="45" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="46" t="s">
+      <c r="K17" s="45">
+        <v>7.5789999999999997</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="44" t="s">
         <v>155</v>
       </c>
-      <c r="B18" s="46" t="s">
+      <c r="B18" s="44" t="s">
         <v>101</v>
       </c>
-      <c r="C18" s="44">
+      <c r="C18" s="45">
         <v>1666</v>
       </c>
-      <c r="D18" s="44">
+      <c r="D18" s="45">
         <v>9.3859999999999992</v>
       </c>
-      <c r="E18" s="44">
+      <c r="E18" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__8.39__</v>
+      </c>
+      <c r="F18" s="45">
+        <v>7.3129999999999997</v>
+      </c>
+      <c r="G18" s="46">
+        <v>41496</v>
+      </c>
+      <c r="H18" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I18" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="K18" s="45">
         <v>8.39</v>
       </c>
-      <c r="F18" s="44">
-        <v>7.3129999999999997</v>
-      </c>
-      <c r="G18" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="H18" s="48">
-        <v>41496</v>
-      </c>
-      <c r="I18" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="44" t="s">
         <v>215</v>
       </c>
       <c r="C19" s="45">
@@ -20876,56 +20930,64 @@
       <c r="D19" s="45">
         <v>6.78</v>
       </c>
-      <c r="E19" s="45">
-        <v>9.5239999999999991</v>
+      <c r="E19" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__9.524__</v>
       </c>
       <c r="F19" s="45">
         <v>9.1739999999999995</v>
       </c>
-      <c r="G19" s="45" t="s">
+      <c r="G19" s="46">
+        <v>45298</v>
+      </c>
+      <c r="H19" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="I19" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H19" s="49">
-        <v>45298</v>
-      </c>
-      <c r="I19" s="45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="46" t="s">
+      <c r="K19" s="45">
+        <v>9.5239999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="44" t="s">
         <v>100</v>
       </c>
-      <c r="B20" s="46" t="s">
+      <c r="B20" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="C20" s="44">
+      <c r="C20" s="45">
         <v>1512</v>
       </c>
-      <c r="D20" s="44">
+      <c r="D20" s="45">
         <v>4.5910000000000002</v>
       </c>
-      <c r="E20" s="44">
+      <c r="E20" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__9.895__</v>
+      </c>
+      <c r="F20" s="45">
+        <v>9.0860000000000003</v>
+      </c>
+      <c r="G20" s="46">
+        <v>42031</v>
+      </c>
+      <c r="H20" s="45" t="s">
+        <v>227</v>
+      </c>
+      <c r="I20" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K20" s="45">
         <v>9.8949999999999996</v>
       </c>
-      <c r="F20" s="44">
-        <v>9.0860000000000003</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H20" s="48">
-        <v>42031</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="44" t="s">
         <v>182</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="44" t="s">
         <v>183</v>
       </c>
       <c r="C21" s="45">
@@ -20934,56 +20996,64 @@
       <c r="D21" s="45">
         <v>8.68</v>
       </c>
-      <c r="E21" s="45">
-        <v>10.948</v>
+      <c r="E21" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__10.948__</v>
       </c>
       <c r="F21" s="45">
         <v>10.154999999999999</v>
       </c>
-      <c r="G21" s="45" t="s">
+      <c r="G21" s="46">
+        <v>45319</v>
+      </c>
+      <c r="H21" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="I21" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H21" s="49">
-        <v>45319</v>
-      </c>
-      <c r="I21" s="45" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="46" t="s">
+      <c r="K21" s="45">
+        <v>10.948</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B22" s="46" t="s">
+      <c r="B22" s="44" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="44">
+      <c r="C22" s="45">
         <v>1800</v>
       </c>
-      <c r="D22" s="44">
+      <c r="D22" s="45">
         <v>11.269</v>
       </c>
-      <c r="E22" s="44">
+      <c r="E22" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__11.927__</v>
+      </c>
+      <c r="F22" s="45">
+        <v>20.516999999999999</v>
+      </c>
+      <c r="G22" s="46">
+        <v>40672</v>
+      </c>
+      <c r="H22" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I22" s="45" t="s">
+        <v>187</v>
+      </c>
+      <c r="K22" s="45">
         <v>11.927</v>
       </c>
-      <c r="F22" s="44">
-        <v>20.516999999999999</v>
-      </c>
-      <c r="G22" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="H22" s="48">
-        <v>40672</v>
-      </c>
-      <c r="I22" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="44" t="s">
         <v>156</v>
       </c>
-      <c r="B23" s="47" t="s">
+      <c r="B23" s="44" t="s">
         <v>104</v>
       </c>
       <c r="C23" s="45">
@@ -20992,56 +21062,64 @@
       <c r="D23" s="45">
         <v>12.138</v>
       </c>
-      <c r="E23" s="45">
-        <v>12.568</v>
+      <c r="E23" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__12.568__</v>
       </c>
       <c r="F23" s="45">
         <v>21.143999999999998</v>
       </c>
-      <c r="G23" s="45" t="s">
+      <c r="G23" s="46">
+        <v>39919</v>
+      </c>
+      <c r="H23" s="45" t="s">
+        <v>225</v>
+      </c>
+      <c r="I23" s="45" t="s">
         <v>188</v>
       </c>
-      <c r="H23" s="49">
-        <v>39919</v>
-      </c>
-      <c r="I23" s="45" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="46" t="s">
+      <c r="K23" s="45">
+        <v>12.568</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="44" t="s">
         <v>158</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="44" t="s">
         <v>106</v>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="45">
         <v>1860</v>
       </c>
-      <c r="D24" s="44">
+      <c r="D24" s="45">
         <v>18.433</v>
       </c>
-      <c r="E24" s="44">
+      <c r="E24" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__15.15__</v>
+      </c>
+      <c r="F24" s="45">
+        <v>16.635999999999999</v>
+      </c>
+      <c r="G24" s="46">
+        <v>41788</v>
+      </c>
+      <c r="H24" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I24" s="45" t="s">
+        <v>189</v>
+      </c>
+      <c r="K24" s="45">
         <v>15.15</v>
       </c>
-      <c r="F24" s="44">
-        <v>16.635999999999999</v>
-      </c>
-      <c r="G24" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="H24" s="48">
-        <v>41788</v>
-      </c>
-      <c r="I24" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="44" t="s">
         <v>232</v>
       </c>
       <c r="C25" s="45">
@@ -21050,54 +21128,62 @@
       <c r="D25" s="45">
         <v>14.398999999999999</v>
       </c>
-      <c r="E25" s="45">
-        <v>15.946999999999999</v>
+      <c r="E25" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__15.947__</v>
       </c>
       <c r="F25" s="45">
         <v>17.788</v>
       </c>
-      <c r="G25" s="45"/>
-      <c r="H25" s="49">
+      <c r="G25" s="46">
         <v>45772</v>
       </c>
-      <c r="I25" s="45" t="s">
+      <c r="H25" s="45" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="46" t="s">
+      <c r="I25" s="45"/>
+      <c r="K25" s="45">
+        <v>15.946999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="44" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="46" t="s">
+      <c r="B26" s="44" t="s">
         <v>160</v>
       </c>
-      <c r="C26" s="44">
+      <c r="C26" s="45">
         <v>1800</v>
       </c>
-      <c r="D26" s="44">
+      <c r="D26" s="45">
         <v>13.595000000000001</v>
       </c>
-      <c r="E26" s="44">
+      <c r="E26" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__16.121__</v>
+      </c>
+      <c r="F26" s="45">
+        <v>19.565999999999999</v>
+      </c>
+      <c r="G26" s="46">
+        <v>40672</v>
+      </c>
+      <c r="H26" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I26" s="45" t="s">
+        <v>190</v>
+      </c>
+      <c r="K26" s="45">
         <v>16.120999999999999</v>
       </c>
-      <c r="F26" s="44">
-        <v>19.565999999999999</v>
-      </c>
-      <c r="G26" s="44" t="s">
-        <v>190</v>
-      </c>
-      <c r="H26" s="48">
-        <v>40672</v>
-      </c>
-      <c r="I26" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="47" t="s">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="44" t="s">
         <v>161</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="44" t="s">
         <v>107</v>
       </c>
       <c r="C27" s="45">
@@ -21106,56 +21192,64 @@
       <c r="D27" s="45">
         <v>19.981000000000002</v>
       </c>
-      <c r="E27" s="45">
-        <v>16.207000000000001</v>
+      <c r="E27" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__16.207__</v>
       </c>
       <c r="F27" s="45">
         <v>18.001000000000001</v>
       </c>
-      <c r="G27" s="45" t="s">
+      <c r="G27" s="46">
+        <v>41851</v>
+      </c>
+      <c r="H27" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I27" s="45" t="s">
         <v>191</v>
       </c>
-      <c r="H27" s="49">
-        <v>41851</v>
-      </c>
-      <c r="I27" s="45" t="s">
+      <c r="K27" s="45">
+        <v>16.207000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="45">
+        <v>1299</v>
+      </c>
+      <c r="D28" s="45">
+        <v>19.050999999999998</v>
+      </c>
+      <c r="E28" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__17.286__</v>
+      </c>
+      <c r="F28" s="45">
+        <v>25.289000000000001</v>
+      </c>
+      <c r="G28" s="46">
+        <v>41861</v>
+      </c>
+      <c r="H28" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="46" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="C28" s="44">
-        <v>1299</v>
-      </c>
-      <c r="D28" s="44">
-        <v>19.050999999999998</v>
-      </c>
-      <c r="E28" s="44">
+      <c r="I28" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K28" s="45">
         <v>17.286000000000001</v>
       </c>
-      <c r="F28" s="44">
-        <v>25.289000000000001</v>
-      </c>
-      <c r="G28" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H28" s="48">
-        <v>41861</v>
-      </c>
-      <c r="I28" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="47" t="s">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="44" t="s">
         <v>110</v>
       </c>
       <c r="C29" s="45">
@@ -21164,56 +21258,64 @@
       <c r="D29" s="45">
         <v>28.488</v>
       </c>
-      <c r="E29" s="45">
-        <v>17.780999999999999</v>
+      <c r="E29" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__17.781__</v>
       </c>
       <c r="F29" s="45">
         <v>36.673000000000002</v>
       </c>
-      <c r="G29" s="45" t="s">
+      <c r="G29" s="46">
+        <v>41457</v>
+      </c>
+      <c r="H29" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I29" s="45" t="s">
         <v>192</v>
       </c>
-      <c r="H29" s="49">
-        <v>41457</v>
-      </c>
-      <c r="I29" s="45" t="s">
+      <c r="K29" s="45">
+        <v>17.780999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="45">
+        <v>1600</v>
+      </c>
+      <c r="D30" s="45">
+        <v>23.695</v>
+      </c>
+      <c r="E30" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__17.817__</v>
+      </c>
+      <c r="F30" s="45">
+        <v>25.515999999999998</v>
+      </c>
+      <c r="G30" s="46">
+        <v>44089</v>
+      </c>
+      <c r="H30" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="46" t="s">
-        <v>113</v>
-      </c>
-      <c r="B30" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="C30" s="44">
-        <v>1600</v>
-      </c>
-      <c r="D30" s="44">
-        <v>23.695</v>
-      </c>
-      <c r="E30" s="44">
+      <c r="I30" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="K30" s="45">
         <v>17.817</v>
       </c>
-      <c r="F30" s="44">
-        <v>25.515999999999998</v>
-      </c>
-      <c r="G30" s="44" t="s">
-        <v>210</v>
-      </c>
-      <c r="H30" s="48">
-        <v>44089</v>
-      </c>
-      <c r="I30" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="47" t="s">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="B31" s="47" t="s">
+      <c r="B31" s="44" t="s">
         <v>121</v>
       </c>
       <c r="C31" s="45">
@@ -21222,56 +21324,64 @@
       <c r="D31" s="45">
         <v>18.776</v>
       </c>
-      <c r="E31" s="45">
-        <v>17.878</v>
+      <c r="E31" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__17.878__</v>
       </c>
       <c r="F31" s="45">
         <v>29.106000000000002</v>
       </c>
-      <c r="G31" s="45" t="s">
+      <c r="G31" s="46">
+        <v>43641</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I31" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H31" s="49">
-        <v>43641</v>
-      </c>
-      <c r="I31" s="45" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="46" t="s">
+      <c r="K31" s="45">
+        <v>17.878</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="C32" s="44">
+      <c r="C32" s="45">
         <v>1500</v>
       </c>
-      <c r="D32" s="44">
+      <c r="D32" s="45">
         <v>15.319000000000001</v>
       </c>
-      <c r="E32" s="44">
+      <c r="E32" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__18.061__</v>
+      </c>
+      <c r="F32" s="45">
+        <v>34.619999999999997</v>
+      </c>
+      <c r="G32" s="46">
+        <v>45561</v>
+      </c>
+      <c r="H32" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K32" s="45">
         <v>18.061</v>
       </c>
-      <c r="F32" s="44">
-        <v>34.619999999999997</v>
-      </c>
-      <c r="G32" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H32" s="48">
-        <v>45561</v>
-      </c>
-      <c r="I32" s="44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="47" t="s">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="44" t="s">
         <v>162</v>
       </c>
-      <c r="B33" s="47" t="s">
+      <c r="B33" s="44" t="s">
         <v>109</v>
       </c>
       <c r="C33" s="45">
@@ -21280,56 +21390,64 @@
       <c r="D33" s="45">
         <v>18.265000000000001</v>
       </c>
-      <c r="E33" s="45">
-        <v>18.957999999999998</v>
+      <c r="E33" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__18.958__</v>
       </c>
       <c r="F33" s="45">
         <v>31.843</v>
       </c>
-      <c r="G33" s="45" t="s">
+      <c r="G33" s="46">
+        <v>41151</v>
+      </c>
+      <c r="H33" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I33" s="45" t="s">
         <v>193</v>
       </c>
-      <c r="H33" s="49">
-        <v>41151</v>
-      </c>
-      <c r="I33" s="45" t="s">
+      <c r="K33" s="45">
+        <v>18.957999999999998</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="B34" s="44" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="45">
+        <v>2100</v>
+      </c>
+      <c r="D34" s="45">
+        <v>14.395</v>
+      </c>
+      <c r="E34" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__19.299__</v>
+      </c>
+      <c r="F34" s="45">
+        <v>23.132000000000001</v>
+      </c>
+      <c r="G34" s="46">
+        <v>40060</v>
+      </c>
+      <c r="H34" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="46" t="s">
-        <v>157</v>
-      </c>
-      <c r="B34" s="46" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="44">
-        <v>2100</v>
-      </c>
-      <c r="D34" s="44">
-        <v>14.395</v>
-      </c>
-      <c r="E34" s="44">
+      <c r="I34" s="45" t="s">
+        <v>43</v>
+      </c>
+      <c r="K34" s="45">
         <v>19.298999999999999</v>
       </c>
-      <c r="F34" s="44">
-        <v>23.132000000000001</v>
-      </c>
-      <c r="G34" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" s="48">
-        <v>40060</v>
-      </c>
-      <c r="I34" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="47" t="s">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="44" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="47" t="s">
+      <c r="B35" s="44" t="s">
         <v>134</v>
       </c>
       <c r="C35" s="45">
@@ -21338,56 +21456,64 @@
       <c r="D35" s="45">
         <v>28.631</v>
       </c>
-      <c r="E35" s="45">
-        <v>19.780999999999999</v>
+      <c r="E35" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__19.781__</v>
       </c>
       <c r="F35" s="45">
         <v>31.140999999999998</v>
       </c>
-      <c r="G35" s="45" t="s">
+      <c r="G35" s="46">
+        <v>42713</v>
+      </c>
+      <c r="H35" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I35" s="45" t="s">
         <v>206</v>
       </c>
-      <c r="H35" s="49">
-        <v>42713</v>
-      </c>
-      <c r="I35" s="45" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="46" t="s">
+      <c r="K35" s="45">
+        <v>19.780999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="B36" s="46" t="s">
+      <c r="B36" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="C36" s="44">
+      <c r="C36" s="45">
         <v>2400</v>
       </c>
-      <c r="D36" s="44">
+      <c r="D36" s="45">
         <v>23.448</v>
       </c>
-      <c r="E36" s="44">
+      <c r="E36" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__32.408__</v>
+      </c>
+      <c r="F36" s="45">
+        <v>50.741999999999997</v>
+      </c>
+      <c r="G36" s="46">
+        <v>46116</v>
+      </c>
+      <c r="H36" s="45" t="s">
+        <v>224</v>
+      </c>
+      <c r="I36" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K36" s="45">
         <v>32.408000000000001</v>
       </c>
-      <c r="F36" s="44">
-        <v>50.741999999999997</v>
-      </c>
-      <c r="G36" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H36" s="48">
-        <v>46116</v>
-      </c>
-      <c r="I36" s="44" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="47" t="s">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="44" t="s">
         <v>163</v>
       </c>
-      <c r="B37" s="47" t="s">
+      <c r="B37" s="44" t="s">
         <v>164</v>
       </c>
       <c r="C37" s="45">
@@ -21396,56 +21522,64 @@
       <c r="D37" s="45">
         <v>19.359000000000002</v>
       </c>
-      <c r="E37" s="45">
-        <v>19.808</v>
+      <c r="E37" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__19.808__</v>
       </c>
       <c r="F37" s="45">
         <v>33.182000000000002</v>
       </c>
-      <c r="G37" s="45" t="s">
+      <c r="G37" s="46">
+        <v>41919</v>
+      </c>
+      <c r="H37" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I37" s="45" t="s">
         <v>205</v>
       </c>
-      <c r="H37" s="49">
-        <v>41919</v>
-      </c>
-      <c r="I37" s="45" t="s">
+      <c r="K37" s="45">
+        <v>19.808</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="B38" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="C38" s="45">
+        <v>2832</v>
+      </c>
+      <c r="D38" s="45">
+        <v>33.670999999999999</v>
+      </c>
+      <c r="E38" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__23.584__</v>
+      </c>
+      <c r="F38" s="45">
+        <v>36.384</v>
+      </c>
+      <c r="G38" s="46">
+        <v>42443</v>
+      </c>
+      <c r="H38" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="B38" s="46" t="s">
-        <v>133</v>
-      </c>
-      <c r="C38" s="44">
-        <v>2832</v>
-      </c>
-      <c r="D38" s="44">
-        <v>33.670999999999999</v>
-      </c>
-      <c r="E38" s="44">
+      <c r="I38" s="45" t="s">
+        <v>204</v>
+      </c>
+      <c r="K38" s="45">
         <v>23.584</v>
       </c>
-      <c r="F38" s="44">
-        <v>36.384</v>
-      </c>
-      <c r="G38" s="44" t="s">
-        <v>204</v>
-      </c>
-      <c r="H38" s="48">
-        <v>42443</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="47" t="s">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="B39" s="47" t="s">
+      <c r="B39" s="44" t="s">
         <v>175</v>
       </c>
       <c r="C39" s="45">
@@ -21454,56 +21588,64 @@
       <c r="D39" s="45">
         <v>28.776</v>
       </c>
-      <c r="E39" s="45">
-        <v>23.881</v>
+      <c r="E39" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__23.881__</v>
       </c>
       <c r="F39" s="45">
         <v>47.396000000000001</v>
       </c>
-      <c r="G39" s="45" t="s">
+      <c r="G39" s="46">
+        <v>44691</v>
+      </c>
+      <c r="H39" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I39" s="45" t="s">
         <v>203</v>
       </c>
-      <c r="H39" s="49">
-        <v>44691</v>
-      </c>
-      <c r="I39" s="45" t="s">
+      <c r="K39" s="45">
+        <v>23.881</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="C40" s="45">
+        <v>3200</v>
+      </c>
+      <c r="D40" s="45">
+        <v>37.845999999999997</v>
+      </c>
+      <c r="E40" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__23.882__</v>
+      </c>
+      <c r="F40" s="45">
+        <v>47.436999999999998</v>
+      </c>
+      <c r="G40" s="46">
+        <v>41537</v>
+      </c>
+      <c r="H40" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="46" t="s">
-        <v>150</v>
-      </c>
-      <c r="B40" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="C40" s="44">
-        <v>3200</v>
-      </c>
-      <c r="D40" s="44">
-        <v>37.845999999999997</v>
-      </c>
-      <c r="E40" s="44">
+      <c r="I40" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K40" s="45">
         <v>23.882000000000001</v>
       </c>
-      <c r="F40" s="44">
-        <v>47.436999999999998</v>
-      </c>
-      <c r="G40" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H40" s="48">
-        <v>41537</v>
-      </c>
-      <c r="I40" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="47" t="s">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="44" t="s">
         <v>151</v>
       </c>
-      <c r="B41" s="47" t="s">
+      <c r="B41" s="44" t="s">
         <v>132</v>
       </c>
       <c r="C41" s="45">
@@ -21512,56 +21654,64 @@
       <c r="D41" s="45">
         <v>24.206</v>
       </c>
-      <c r="E41" s="45">
-        <v>24.602</v>
+      <c r="E41" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__24.602__</v>
       </c>
       <c r="F41" s="45">
         <v>41.085000000000001</v>
       </c>
-      <c r="G41" s="45" t="s">
+      <c r="G41" s="46">
+        <v>40683</v>
+      </c>
+      <c r="H41" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I41" s="45" t="s">
         <v>202</v>
       </c>
-      <c r="H41" s="49">
-        <v>40683</v>
-      </c>
-      <c r="I41" s="45" t="s">
+      <c r="K41" s="45">
+        <v>24.602</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="44" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="C42" s="45">
+        <v>2829</v>
+      </c>
+      <c r="D42" s="45">
+        <v>21.475999999999999</v>
+      </c>
+      <c r="E42" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__25.608__</v>
+      </c>
+      <c r="F42" s="45">
+        <v>30.663</v>
+      </c>
+      <c r="G42" s="46">
+        <v>39896</v>
+      </c>
+      <c r="H42" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="46" t="s">
-        <v>186</v>
-      </c>
-      <c r="B42" s="46" t="s">
-        <v>114</v>
-      </c>
-      <c r="C42" s="44">
-        <v>2829</v>
-      </c>
-      <c r="D42" s="44">
-        <v>21.475999999999999</v>
-      </c>
-      <c r="E42" s="44">
+      <c r="I42" s="45" t="s">
+        <v>201</v>
+      </c>
+      <c r="K42" s="45">
         <v>25.608000000000001</v>
       </c>
-      <c r="F42" s="44">
-        <v>30.663</v>
-      </c>
-      <c r="G42" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="H42" s="48">
-        <v>39896</v>
-      </c>
-      <c r="I42" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="47" t="s">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="44" t="s">
         <v>167</v>
       </c>
-      <c r="B43" s="47" t="s">
+      <c r="B43" s="44" t="s">
         <v>168</v>
       </c>
       <c r="C43" s="45">
@@ -21570,56 +21720,64 @@
       <c r="D43" s="45">
         <v>27.460999999999999</v>
       </c>
-      <c r="E43" s="45">
-        <v>26.341999999999999</v>
+      <c r="E43" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__26.342__</v>
       </c>
       <c r="F43" s="45">
         <v>27.893999999999998</v>
       </c>
-      <c r="G43" s="45" t="s">
+      <c r="G43" s="46">
+        <v>43956</v>
+      </c>
+      <c r="H43" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I43" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="H43" s="49">
-        <v>43956</v>
-      </c>
-      <c r="I43" s="45" t="s">
+      <c r="K43" s="45">
+        <v>26.341999999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="C44" s="45">
+        <v>3352</v>
+      </c>
+      <c r="D44" s="45">
+        <v>28.021999999999998</v>
+      </c>
+      <c r="E44" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__32.586__</v>
+      </c>
+      <c r="F44" s="45">
+        <v>44.103999999999999</v>
+      </c>
+      <c r="G44" s="46">
+        <v>42315</v>
+      </c>
+      <c r="H44" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="B44" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="C44" s="44">
-        <v>3352</v>
-      </c>
-      <c r="D44" s="44">
-        <v>28.021999999999998</v>
-      </c>
-      <c r="E44" s="44">
+      <c r="I44" s="45" t="s">
+        <v>200</v>
+      </c>
+      <c r="K44" s="45">
         <v>32.585999999999999</v>
       </c>
-      <c r="F44" s="44">
-        <v>44.103999999999999</v>
-      </c>
-      <c r="G44" s="44" t="s">
-        <v>200</v>
-      </c>
-      <c r="H44" s="48">
-        <v>42315</v>
-      </c>
-      <c r="I44" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="47" t="s">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="44" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="47" t="s">
+      <c r="B45" s="44" t="s">
         <v>171</v>
       </c>
       <c r="C45" s="45">
@@ -21628,56 +21786,64 @@
       <c r="D45" s="45">
         <v>39.049999999999997</v>
       </c>
-      <c r="E45" s="45">
-        <v>33.215000000000003</v>
+      <c r="E45" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__33.215__</v>
       </c>
       <c r="F45" s="45">
         <v>54.26</v>
       </c>
-      <c r="G45" s="45" t="s">
+      <c r="G45" s="46">
+        <v>42397</v>
+      </c>
+      <c r="H45" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I45" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H45" s="49">
+      <c r="K45" s="45">
+        <v>33.215000000000003</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="C46" s="45">
+        <v>2500</v>
+      </c>
+      <c r="D46" s="45">
+        <v>40.698999999999998</v>
+      </c>
+      <c r="E46" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__37.018__</v>
+      </c>
+      <c r="F46" s="45">
+        <v>52.634999999999998</v>
+      </c>
+      <c r="G46" s="46">
         <v>42397</v>
       </c>
-      <c r="I45" s="45" t="s">
+      <c r="H46" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="46" t="s">
-        <v>139</v>
-      </c>
-      <c r="B46" s="46" t="s">
-        <v>140</v>
-      </c>
-      <c r="C46" s="44">
-        <v>2500</v>
-      </c>
-      <c r="D46" s="44">
-        <v>40.698999999999998</v>
-      </c>
-      <c r="E46" s="44">
+      <c r="I46" s="45" t="s">
+        <v>199</v>
+      </c>
+      <c r="K46" s="45">
         <v>37.018000000000001</v>
       </c>
-      <c r="F46" s="44">
-        <v>52.634999999999998</v>
-      </c>
-      <c r="G46" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="H46" s="48">
-        <v>42397</v>
-      </c>
-      <c r="I46" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="47" t="s">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="44" t="s">
         <v>141</v>
       </c>
-      <c r="B47" s="47" t="s">
+      <c r="B47" s="44" t="s">
         <v>142</v>
       </c>
       <c r="C47" s="45">
@@ -21686,56 +21852,64 @@
       <c r="D47" s="45">
         <v>45.381999999999998</v>
       </c>
-      <c r="E47" s="45">
-        <v>40.313000000000002</v>
+      <c r="E47" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__40.313__</v>
       </c>
       <c r="F47" s="45">
         <v>61.804000000000002</v>
       </c>
-      <c r="G47" s="45" t="s">
+      <c r="G47" s="46">
+        <v>42817</v>
+      </c>
+      <c r="H47" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I47" s="45" t="s">
         <v>198</v>
       </c>
-      <c r="H47" s="49">
-        <v>42817</v>
-      </c>
-      <c r="I47" s="45" t="s">
+      <c r="K47" s="45">
+        <v>40.313000000000002</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="44" t="s">
+        <v>173</v>
+      </c>
+      <c r="B48" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="C48" s="45">
+        <v>2700</v>
+      </c>
+      <c r="D48" s="45">
+        <v>57.2</v>
+      </c>
+      <c r="E48" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__43.732__</v>
+      </c>
+      <c r="F48" s="45">
+        <v>107.95399999999999</v>
+      </c>
+      <c r="G48" s="46">
+        <v>44155</v>
+      </c>
+      <c r="H48" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="46" t="s">
-        <v>173</v>
-      </c>
-      <c r="B48" s="46" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" s="44">
-        <v>2700</v>
-      </c>
-      <c r="D48" s="44">
-        <v>57.2</v>
-      </c>
-      <c r="E48" s="44">
+      <c r="I48" s="45" t="s">
+        <v>197</v>
+      </c>
+      <c r="K48" s="45">
         <v>43.731999999999999</v>
       </c>
-      <c r="F48" s="44">
-        <v>107.95399999999999</v>
-      </c>
-      <c r="G48" s="44" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48" s="48">
-        <v>44155</v>
-      </c>
-      <c r="I48" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="47" t="s">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="B49" s="47" t="s">
+      <c r="B49" s="44" t="s">
         <v>172</v>
       </c>
       <c r="C49" s="45">
@@ -21744,56 +21918,64 @@
       <c r="D49" s="45">
         <v>55.045999999999999</v>
       </c>
-      <c r="E49" s="45">
-        <v>44.618000000000002</v>
+      <c r="E49" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__44.618__</v>
       </c>
       <c r="F49" s="45">
         <v>73.569999999999993</v>
       </c>
-      <c r="G49" s="45" t="s">
+      <c r="G49" s="46">
+        <v>43355</v>
+      </c>
+      <c r="H49" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I49" s="45" t="s">
         <v>196</v>
       </c>
-      <c r="H49" s="49">
-        <v>43355</v>
-      </c>
-      <c r="I49" s="45" t="s">
+      <c r="K49" s="45">
+        <v>44.618000000000002</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="B50" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="C50" s="45">
+        <v>2600</v>
+      </c>
+      <c r="D50" s="45">
+        <v>63.682000000000002</v>
+      </c>
+      <c r="E50" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__45.732__</v>
+      </c>
+      <c r="F50" s="45">
+        <v>68.159000000000006</v>
+      </c>
+      <c r="G50" s="46">
+        <v>43146</v>
+      </c>
+      <c r="H50" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="C50" s="44">
-        <v>2600</v>
-      </c>
-      <c r="D50" s="44">
-        <v>63.682000000000002</v>
-      </c>
-      <c r="E50" s="44">
+      <c r="I50" s="45" t="s">
+        <v>10</v>
+      </c>
+      <c r="K50" s="45">
         <v>45.731999999999999</v>
       </c>
-      <c r="F50" s="44">
-        <v>68.159000000000006</v>
-      </c>
-      <c r="G50" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="H50" s="48">
-        <v>43146</v>
-      </c>
-      <c r="I50" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="47" t="s">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="B51" s="47" t="s">
+      <c r="B51" s="44" t="s">
         <v>125</v>
       </c>
       <c r="C51" s="45">
@@ -21802,56 +21984,64 @@
       <c r="D51" s="45">
         <v>50.423000000000002</v>
       </c>
-      <c r="E51" s="45">
-        <v>46.116999999999997</v>
+      <c r="E51" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__46.117__</v>
       </c>
       <c r="F51" s="45">
         <v>70.039000000000001</v>
       </c>
-      <c r="G51" s="45" t="s">
+      <c r="G51" s="46">
+        <v>43146</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I51" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H51" s="49">
-        <v>43146</v>
-      </c>
-      <c r="I51" s="45" t="s">
+      <c r="K51" s="45">
+        <v>46.116999999999997</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="B52" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="C52" s="45">
+        <v>2112</v>
+      </c>
+      <c r="D52" s="45">
+        <v>61.249000000000002</v>
+      </c>
+      <c r="E52" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__46.227__</v>
+      </c>
+      <c r="F52" s="45">
+        <v>113.619</v>
+      </c>
+      <c r="G52" s="46">
+        <v>45298</v>
+      </c>
+      <c r="H52" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="B52" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="C52" s="44">
-        <v>2112</v>
-      </c>
-      <c r="D52" s="44">
-        <v>61.249000000000002</v>
-      </c>
-      <c r="E52" s="44">
+      <c r="I52" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="K52" s="45">
         <v>46.226999999999997</v>
       </c>
-      <c r="F52" s="44">
-        <v>113.619</v>
-      </c>
-      <c r="G52" s="44" t="s">
-        <v>218</v>
-      </c>
-      <c r="H52" s="48">
-        <v>45298</v>
-      </c>
-      <c r="I52" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A53" s="47" t="s">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="44" t="s">
         <v>236</v>
       </c>
-      <c r="B53" s="47" t="s">
+      <c r="B53" s="44" t="s">
         <v>237</v>
       </c>
       <c r="C53" s="45">
@@ -21860,54 +22050,62 @@
       <c r="D53" s="45">
         <v>68.150000000000006</v>
       </c>
-      <c r="E53" s="45">
-        <v>48.103000000000002</v>
+      <c r="E53" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__48.103__</v>
       </c>
       <c r="F53" s="45">
         <v>118.447</v>
       </c>
-      <c r="G53" s="45"/>
-      <c r="H53" s="49">
+      <c r="G53" s="46">
         <v>45773</v>
       </c>
-      <c r="I53" s="45" t="s">
+      <c r="H53" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54" s="46" t="s">
+      <c r="I53" s="45"/>
+      <c r="K53" s="45">
+        <v>48.103000000000002</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="44" t="s">
         <v>234</v>
       </c>
-      <c r="B54" s="46" t="s">
+      <c r="B54" s="44" t="s">
         <v>233</v>
       </c>
-      <c r="C54" s="44">
+      <c r="C54" s="45">
         <v>2295</v>
       </c>
-      <c r="D54" s="44">
+      <c r="D54" s="45">
         <v>59.665999999999997</v>
       </c>
-      <c r="E54" s="44">
+      <c r="E54" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__49.441__</v>
+      </c>
+      <c r="F54" s="45">
+        <v>116.922</v>
+      </c>
+      <c r="G54" s="46">
+        <v>45298</v>
+      </c>
+      <c r="H54" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I54" s="45" t="s">
+        <v>235</v>
+      </c>
+      <c r="K54" s="45">
         <v>49.441000000000003</v>
       </c>
-      <c r="F54" s="44">
-        <v>116.922</v>
-      </c>
-      <c r="G54" s="44" t="s">
-        <v>235</v>
-      </c>
-      <c r="H54" s="48">
-        <v>45298</v>
-      </c>
-      <c r="I54" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="47" t="s">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="B55" s="47" t="s">
+      <c r="B55" s="44" t="s">
         <v>209</v>
       </c>
       <c r="C55" s="45">
@@ -21916,83 +22114,95 @@
       <c r="D55" s="45">
         <v>62.206000000000003</v>
       </c>
-      <c r="E55" s="45">
-        <v>49.951000000000001</v>
+      <c r="E55" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__49.951__</v>
       </c>
       <c r="F55" s="45">
         <v>112.593</v>
       </c>
-      <c r="G55" s="45" t="s">
+      <c r="G55" s="46">
+        <v>45561</v>
+      </c>
+      <c r="H55" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I55" s="45" t="s">
         <v>207</v>
       </c>
-      <c r="H55" s="49">
-        <v>45561</v>
-      </c>
-      <c r="I55" s="45" t="s">
+      <c r="K55" s="45">
+        <v>49.951000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="B56" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="C56" s="45">
+        <v>4160</v>
+      </c>
+      <c r="D56" s="45">
+        <v>77.174000000000007</v>
+      </c>
+      <c r="E56" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__56.761__</v>
+      </c>
+      <c r="F56" s="45">
+        <v>138.00299999999999</v>
+      </c>
+      <c r="G56" s="46">
+        <v>45211</v>
+      </c>
+      <c r="H56" s="45" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56" s="46" t="s">
-        <v>177</v>
-      </c>
-      <c r="B56" s="46" t="s">
-        <v>178</v>
-      </c>
-      <c r="C56" s="44">
-        <v>4160</v>
-      </c>
-      <c r="D56" s="44">
-        <v>77.174000000000007</v>
-      </c>
-      <c r="E56" s="44">
+      <c r="I56" s="45" t="s">
+        <v>195</v>
+      </c>
+      <c r="K56" s="45">
         <v>56.761000000000003</v>
       </c>
-      <c r="F56" s="44">
-        <v>138.00299999999999</v>
-      </c>
-      <c r="G56" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="H56" s="48">
-        <v>45211</v>
-      </c>
-      <c r="I56" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="46" t="s">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="44" t="s">
         <v>246</v>
       </c>
-      <c r="B57" s="46" t="s">
+      <c r="B57" s="44" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="44">
+      <c r="C57" s="45">
         <v>3090</v>
       </c>
-      <c r="D57" s="44">
+      <c r="D57" s="45">
         <v>63.435000000000002</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__66.735__</v>
+      </c>
+      <c r="F57" s="45">
+        <v>143.465</v>
+      </c>
+      <c r="G57" s="46">
+        <v>46116</v>
+      </c>
+      <c r="H57" s="45" t="s">
+        <v>250</v>
+      </c>
+      <c r="I57" s="45"/>
+      <c r="K57" s="45">
         <v>66.734999999999999</v>
       </c>
-      <c r="F57" s="44">
-        <v>143.465</v>
-      </c>
-      <c r="G57" s="44"/>
-      <c r="H57" s="48">
-        <v>46116</v>
-      </c>
-      <c r="I57" s="44" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58" s="47" t="s">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="44" t="s">
         <v>220</v>
       </c>
-      <c r="B58" s="47" t="s">
+      <c r="B58" s="44" t="s">
         <v>219</v>
       </c>
       <c r="C58" s="45">
@@ -22001,56 +22211,64 @@
       <c r="D58" s="45">
         <v>66.938999999999993</v>
       </c>
-      <c r="E58" s="45">
-        <v>79.733000000000004</v>
+      <c r="E58" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__79.733__</v>
       </c>
       <c r="F58" s="45">
         <v>216.304</v>
       </c>
-      <c r="G58" s="45" t="s">
+      <c r="G58" s="46">
+        <v>45561</v>
+      </c>
+      <c r="H58" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="I58" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H58" s="49">
+      <c r="K58" s="45">
+        <v>79.733000000000004</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="44" t="s">
+        <v>184</v>
+      </c>
+      <c r="B59" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="C59" s="45">
+        <v>4700</v>
+      </c>
+      <c r="D59" s="45">
+        <v>104.52500000000001</v>
+      </c>
+      <c r="E59" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__85.011__</v>
+      </c>
+      <c r="F59" s="45">
+        <v>264.86900000000003</v>
+      </c>
+      <c r="G59" s="46">
         <v>45561</v>
       </c>
-      <c r="I58" s="45" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="46" t="s">
-        <v>184</v>
-      </c>
-      <c r="B59" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="C59" s="44">
-        <v>4700</v>
-      </c>
-      <c r="D59" s="44">
-        <v>104.52500000000001</v>
-      </c>
-      <c r="E59" s="44">
-        <v>85.01</v>
-      </c>
-      <c r="F59" s="44">
-        <v>264.86900000000003</v>
-      </c>
-      <c r="G59" s="44" t="s">
+      <c r="H59" s="45" t="s">
+        <v>223</v>
+      </c>
+      <c r="I59" s="45" t="s">
         <v>194</v>
       </c>
-      <c r="H59" s="48">
-        <v>45561</v>
-      </c>
-      <c r="I59" s="44" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="47" t="s">
+      <c r="K59" s="45">
+        <v>85.010999999999996</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="44" t="s">
         <v>253</v>
       </c>
-      <c r="B60" s="47" t="s">
+      <c r="B60" s="44" t="s">
         <v>254</v>
       </c>
       <c r="C60" s="45">
@@ -22059,49 +22277,53 @@
       <c r="D60" s="45">
         <v>83.274000000000001</v>
       </c>
-      <c r="E60" s="45">
-        <v>86</v>
+      <c r="E60" s="45" t="str">
+        <f t="shared" si="0"/>
+        <v>__86.001__</v>
       </c>
       <c r="F60" s="45">
         <v>163.31299999999999</v>
       </c>
-      <c r="G60" s="45" t="s">
+      <c r="G60" s="46">
+        <v>46116</v>
+      </c>
+      <c r="H60" s="45" t="s">
+        <v>255</v>
+      </c>
+      <c r="I60" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="H60" s="49">
-        <v>46116</v>
-      </c>
-      <c r="I60" s="45" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="K60" s="45">
+        <v>86.001000000000005</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" ht="28.5" x14ac:dyDescent="0.25">
       <c r="A61" s="42" t="s">
         <v>78</v>
       </c>
       <c r="B61" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C61" s="44" t="s">
+      <c r="C61" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="45" t="s">
         <v>80</v>
       </c>
       <c r="E61" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="F61" s="44" t="s">
+      <c r="F61" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="G61" s="44" t="s">
+      <c r="G61" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="H61" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="I61" s="45" t="s">
         <v>83</v>
-      </c>
-      <c r="H61" s="43" t="s">
-        <v>181</v>
-      </c>
-      <c r="I61" s="44" t="s">
-        <v>238</v>
       </c>
     </row>
   </sheetData>
